--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PKK-U</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KuPS Akatemia</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KPV</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Inter 2</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>PKK-U</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SJK 2</t>
+          <t>KuPS Akatemia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>9.800000000000001</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,31 +1610,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>KPV</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>FC Inter 2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.28</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>SJK 2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>1.45</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>TPV</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.52</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>1.43</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>1.51</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Shaanxi Union FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.84</v>
+        <v>1.29</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -1102,31 +1102,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="I3" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PKK-U</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KuPS Akatemia</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KPV</t>
+          <t>PKK-U</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Inter 2</t>
+          <t>KuPS Akatemia</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>KPV</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SJK 2</t>
+          <t>FC Inter 2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>9.4</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>SJK 2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28</v>
+        <v>1.51</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>TPV</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.43</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>2.84</v>
       </c>
       <c r="H10" t="n">
-        <v>1.23</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>1.51</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>1.23</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -3388,239 +3388,493 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:00:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>National Bank</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Al Ittihad (EGY)</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>2.02</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="G13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I13" t="n">
         <v>5.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>3.05</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>3.45</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.56</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-05-27 03:50:21</t>
+      <c r="Q13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="H3" t="n">
         <v>3.45</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1377,10 +1377,10 @@
         <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
         <v>5.1</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>1.51</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>TPV</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.43</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.23</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>12.5</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
         <v>3.1</v>
@@ -3409,7 +3409,7 @@
         <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
         <v>3.15</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
         <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,13 +860,13 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
         <v>1.04</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q2" t="n">
         <v>1.29</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Shanghai Port FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PKK-U</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KuPS Akatemia</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KPV</t>
+          <t>PKK-U</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Inter 2</t>
+          <t>KuPS Akatemia</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>KPV</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SJK 2</t>
+          <t>FC Inter 2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.47</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>SJK 2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>2.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="H9" t="n">
-        <v>1.23</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>1.51</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>TPV</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,493 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:20:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>National Bank</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Al Ittihad (EGY)</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" t="n">
         <v>2.16</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
         <v>4.3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>5.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>3.15</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>3.5</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.42</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-05-27 08:10:09</t>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.29</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G3" t="n">
         <v>2.64</v>
@@ -1135,22 +1135,22 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.64</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.56</v>
@@ -1159,7 +1159,7 @@
         <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
         <v>1.61</v>
@@ -1180,7 +1180,7 @@
         <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1189,7 +1189,7 @@
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -1219,52 +1219,52 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>8</v>
       </c>
       <c r="AV3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AW3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
         <v>11.5</v>
@@ -1276,65 +1276,65 @@
         <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
         <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>18.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
         <v>2.78</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PKK-U</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KuPS Akatemia</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1891,219 +1891,219 @@
         <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KPV</t>
+          <t>JBK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Inter 2</t>
+          <t>FF Jaro II</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
         <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>PKK-U</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SJK 2</t>
+          <t>KuPS Akatemia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.47</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>KPV</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>FC Inter 2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>SJK 2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H10" t="n">
-        <v>1.23</v>
+        <v>7.6</v>
       </c>
       <c r="I10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="H12" t="n">
-        <v>2.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>TPV</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,261 +3874,1023 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KaPa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JaPS</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:29:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Egyptian Premier</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:29:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>National Bank</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Al Ittihad (EGY)</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="F16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H16" t="n">
         <v>4.3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>5.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-05-27 10:20:06</t>
+      <c r="J16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:29:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SK Super Nova</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rigas Futbola Skola</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K17" t="n">
+        <v>950</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>970</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
@@ -1138,7 +1138,7 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
         <v>2.28</v>
@@ -1159,10 +1159,10 @@
         <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1177,7 +1177,7 @@
         <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1201,10 +1201,10 @@
         <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
@@ -1213,7 +1213,7 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
@@ -1228,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
         <v>16</v>
@@ -1252,89 +1252,89 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
         <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="n">
         <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
         <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>18.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
         <v>2.78</v>
@@ -1383,212 +1383,212 @@
         <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
         <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
         <v>3.15</v>
@@ -1634,19 +1634,19 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
         <v>1.68</v>
@@ -1655,194 +1655,194 @@
         <v>2.22</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,19 +1897,19 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
         <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2142,7 +2142,7 @@
         <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="n">
         <v>100</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I8" t="n">
-        <v>100</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>1.62</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>7.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J10" t="n">
         <v>5.1</v>
@@ -2907,212 +2907,212 @@
         <v>6.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
         <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
         <v>2.26</v>
@@ -3158,222 +3158,222 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="G12" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="H12" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>2.32</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3908,234 +3908,234 @@
         <v>2.56</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="n">
         <v>2.76</v>
       </c>
       <c r="I14" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
         <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
         <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>1.51</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,498 +4399,3546 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sarpsborg</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Danish 2nd Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fremad Amager</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Skive</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K18" t="n">
+        <v>950</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Danish 2nd Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Naestved</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K19" t="n">
+        <v>950</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>180</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>44</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>50</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>National Bank</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al Ittihad (EGY)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>50</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>21</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Latvian Virsliga</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>SK Super Nova</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Rigas Futbola Skola</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F22" t="n">
         <v>1.04</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G22" t="n">
         <v>100</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H22" t="n">
         <v>1.04</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I22" t="n">
         <v>100</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J22" t="n">
         <v>1.02</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K22" t="n">
         <v>950</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Riteriai</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FK Suduva</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X24" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Valerenga</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kfum Oslo</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Aalesunds</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ham-Kam</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X27" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Orgryte</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>23</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>29</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ29" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
+      <c r="CA29" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-05-27 12:29:40</t>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB43"/>
+  <dimension ref="A1:CB45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -890,22 +890,22 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
         <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
         <v>8.199999999999999</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
         <v>3.1</v>
@@ -1631,13 +1631,13 @@
         <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1652,13 +1652,13 @@
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.9</v>
@@ -1670,7 +1670,7 @@
         <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1748,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="AX5" t="n">
         <v>13</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA5" t="n">
         <v>48</v>
@@ -1775,7 +1775,7 @@
         <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
         <v>32</v>
@@ -1784,19 +1784,19 @@
         <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>8.4</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>8</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O6" t="n">
         <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
         <v>1.11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="O7" t="n">
         <v>1.1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
         <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>5.3</v>
@@ -2396,7 +2396,7 @@
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.18</v>
@@ -2423,7 +2423,7 @@
         <v>1.91</v>
       </c>
       <c r="T8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U8" t="n">
         <v>2.68</v>
@@ -2546,7 +2546,7 @@
         <v>5.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2919,10 +2919,10 @@
         <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.69</v>
@@ -2937,7 +2937,7 @@
         <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
         <v>3.3</v>
@@ -3045,7 +3045,7 @@
         <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
         <v>4.9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="n">
         <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
         <v>3.75</v>
@@ -3675,46 +3675,46 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
         <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
         <v>14</v>
@@ -3735,34 +3735,34 @@
         <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
         <v>48</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13" t="n">
         <v>14.5</v>
@@ -3771,7 +3771,7 @@
         <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
@@ -3810,25 +3810,25 @@
         <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN13" t="n">
         <v>5.7</v>
@@ -3840,16 +3840,16 @@
         <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BR13" t="n">
         <v>32</v>
       </c>
       <c r="BS13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
         <v>4.6</v>
@@ -3858,23 +3858,23 @@
         <v>22</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.43</v>
       </c>
       <c r="G15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K15" t="n">
         <v>5.1</v>
@@ -4207,10 +4207,10 @@
         <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X15" t="n">
         <v>17.5</v>
@@ -4270,13 +4270,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>5.7</v>
@@ -4285,10 +4285,10 @@
         <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4297,10 +4297,10 @@
         <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
         <v>9.4</v>
@@ -4309,16 +4309,16 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
         <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4437,16 +4437,16 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O16" t="n">
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="G17" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.21</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S17" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
         <v>38</v>
@@ -4730,10 +4730,10 @@
         <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AB17" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
@@ -4745,152 +4745,152 @@
         <v>970</v>
       </c>
       <c r="AF17" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AG17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
         <v>28</v>
       </c>
       <c r="AJ17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>4.9</v>
       </c>
       <c r="AP17" t="n">
         <v>5.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AR17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW17" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AX17" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>5.1</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG17" t="n">
         <v>2.78</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.96</v>
       </c>
       <c r="BH17" t="n">
         <v>5.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
         <v>5</v>
       </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>5.2</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
         <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.41</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K19" t="n">
         <v>4</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.31</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>1.28</v>
@@ -5220,16 +5220,16 @@
         <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
@@ -5241,10 +5241,10 @@
         <v>28</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
         <v>12.5</v>
@@ -5253,25 +5253,25 @@
         <v>25</v>
       </c>
       <c r="AF19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH19" t="n">
         <v>21</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -5307,7 +5307,7 @@
         <v>16.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AY19" t="n">
         <v>14.5</v>
@@ -5316,31 +5316,31 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.800000000000001</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>4.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -5689,46 +5689,46 @@
         <v>1.89</v>
       </c>
       <c r="H21" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
         <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -5737,176 +5737,176 @@
         <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
         <v>2.24</v>
@@ -5979,7 +5979,7 @@
         <v>2.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U22" t="n">
         <v>2.42</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G23" t="n">
         <v>1.65</v>
@@ -6305,10 +6305,10 @@
         <v>21</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -6332,7 +6332,7 @@
         <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
         <v>12</v>
@@ -6344,13 +6344,13 @@
         <v>18.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
         <v>4.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,103 +6436,103 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SK Super Nova</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>19.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="I24" t="n">
-        <v>110</v>
+        <v>1.37</v>
       </c>
       <c r="J24" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
@@ -6550,61 +6550,61 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6646,7 +6646,7 @@
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,103 +6690,103 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>SK Super Nova</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>19.5</v>
+        <v>110</v>
       </c>
       <c r="H25" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>1.37</v>
+        <v>110</v>
       </c>
       <c r="J25" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>1.28</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.92</v>
+        <v>1.17</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -6804,67 +6804,67 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
@@ -6900,7 +6900,7 @@
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -7485,13 +7485,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O28" t="n">
         <v>1.19</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
         <v>1.19</v>
@@ -7500,7 +7500,7 @@
         <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="n">
         <v>1.61</v>
       </c>
       <c r="I30" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J30" t="n">
         <v>4.9</v>
       </c>
       <c r="K30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.2</v>
@@ -7999,10 +7999,10 @@
         <v>1.15</v>
       </c>
       <c r="P30" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R30" t="n">
         <v>1.76</v>
@@ -8011,124 +8011,124 @@
         <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U30" t="n">
         <v>2.5</v>
       </c>
       <c r="V30" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Y30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH30" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF30" t="n">
+      <c r="AI30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK30" t="n">
         <v>60</v>
       </c>
-      <c r="AG30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>65</v>
-      </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO30" t="n">
         <v>5.8</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BD30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF30" t="n">
         <v>32</v>
       </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG30" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH30" t="n">
         <v>5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H31" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -8244,13 +8244,13 @@
         <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P31" t="n">
         <v>2.12</v>
@@ -8265,73 +8265,73 @@
         <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="n">
         <v>18</v>
       </c>
-      <c r="Y31" t="n">
-        <v>23</v>
-      </c>
       <c r="Z31" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB31" t="n">
         <v>9.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF31" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
         <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
         <v>60</v>
       </c>
       <c r="AP31" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>15.5</v>
@@ -8340,49 +8340,49 @@
         <v>30</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AX31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY31" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY31" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8406,7 +8406,7 @@
         <v>6</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP31" t="n">
         <v>16.5</v>
@@ -8424,7 +8424,7 @@
         <v>11.5</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
@@ -8439,21 +8439,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA31" t="n">
         <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,239 +8468,239 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="H32" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="O32" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="T32" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="X32" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
         <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
         <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BJ32" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN32" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>4</v>
+        <v>1.29</v>
       </c>
       <c r="BP32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT32" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ32" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -8722,239 +8722,239 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK33" t="n">
         <v>5.1</v>
       </c>
-      <c r="G33" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO33" t="n">
         <v>3.75</v>
       </c>
-      <c r="K33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X33" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="BP33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ33" t="n">
+      <c r="BU33" t="n">
         <v>6</v>
       </c>
-      <c r="AR33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN33" t="n">
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
         <v>8.6</v>
       </c>
-      <c r="BO33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -8976,239 +8976,239 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.34</v>
+        <v>5.1</v>
       </c>
       <c r="G34" t="n">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="H34" t="n">
-        <v>2.96</v>
+        <v>1.77</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="J34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.55</v>
       </c>
-      <c r="K34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4</v>
-      </c>
       <c r="O34" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="T34" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="U34" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="V34" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="W34" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y34" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AA34" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AB34" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC34" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP34" t="n">
+      <c r="BD34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS34" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX34" t="n">
+      <c r="BT34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV34" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>25</v>
-      </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX34" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ34" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -9230,37 +9230,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="G35" t="n">
-        <v>1.89</v>
+        <v>2.54</v>
       </c>
       <c r="H35" t="n">
-        <v>4.5</v>
+        <v>2.96</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K35" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N35" t="n">
         <v>4</v>
@@ -9269,207 +9269,207 @@
         <v>1.28</v>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="W35" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW35" t="n">
         <v>1.03</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
         <v>1.03</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="BJ35" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.65</v>
+        <v>4.9</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.88</v>
+        <v>9.4</v>
       </c>
       <c r="BN35" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP35" t="n">
         <v>18</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="BR35" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.79</v>
+        <v>7.6</v>
       </c>
       <c r="BT35" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BU35" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.82</v>
+        <v>7.2</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.83</v>
+        <v>8</v>
       </c>
       <c r="BZ35" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.76</v>
+        <v>7.2</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9484,239 +9484,239 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="G36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W36" t="n">
         <v>2.12</v>
       </c>
-      <c r="H36" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K36" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS36" t="n">
         <v>1.79</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BR36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS36" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.31</v>
+        <v>5.1</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -9738,31 +9738,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="G37" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="H37" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="I37" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="n">
         <v>3.3</v>
       </c>
       <c r="K37" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,22 +9771,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="O37" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R37" t="n">
         <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9795,10 +9795,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="W37" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9909,68 +9909,68 @@
         <v>1.01</v>
       </c>
       <c r="BH37" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
         <v>1.54</v>
@@ -10043,10 +10043,10 @@
         <v>1.54</v>
       </c>
       <c r="T38" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
@@ -10058,7 +10058,7 @@
         <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
@@ -10067,10 +10067,10 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -10079,25 +10079,25 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK38" t="n">
         <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
@@ -10109,52 +10109,52 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
         <v>1.84</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V39" t="n">
         <v>1.37</v>
@@ -10333,7 +10333,7 @@
         <v>50</v>
       </c>
       <c r="AF39" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG39" t="n">
         <v>12.5</v>
@@ -10372,7 +10372,7 @@
         <v>17</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT39" t="n">
         <v>8</v>
@@ -10384,7 +10384,7 @@
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX39" t="n">
         <v>12.5</v>
@@ -10396,25 +10396,25 @@
         <v>14</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF39" t="n">
         <v>19</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH39" t="n">
         <v>3.25</v>
@@ -10426,13 +10426,13 @@
         <v>10.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN39" t="n">
         <v>5.4</v>
@@ -10444,13 +10444,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR39" t="n">
         <v>36</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT39" t="n">
         <v>6.8</v>
@@ -10462,23 +10462,23 @@
         <v>29</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX39" t="n">
         <v>44</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ39" t="n">
         <v>34</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="G40" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H40" t="n">
         <v>3.25</v>
@@ -10542,7 +10542,7 @@
         <v>1.59</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R40" t="n">
         <v>1.22</v>
@@ -10560,7 +10560,7 @@
         <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10617,52 +10617,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
         <v>3.7</v>
       </c>
       <c r="L41" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
@@ -10793,10 +10793,10 @@
         <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R41" t="n">
         <v>1.23</v>
@@ -10808,7 +10808,7 @@
         <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V41" t="n">
         <v>1.39</v>
@@ -10820,43 +10820,43 @@
         <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE41" t="n">
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL41" t="n">
         <v>1000</v>
@@ -10871,52 +10871,52 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -10940,7 +10940,7 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
         <v>1000</v>
@@ -10952,13 +10952,13 @@
         <v>26</v>
       </c>
       <c r="BQ41" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
         <v>50</v>
       </c>
       <c r="BS41" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
         <v>8.800000000000001</v>
@@ -10970,23 +10970,23 @@
         <v>40</v>
       </c>
       <c r="BW41" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
         <v>48</v>
       </c>
       <c r="CA41" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="O42" t="n">
         <v>1.11</v>
@@ -11125,52 +11125,52 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -11379,52 +11379,52 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,515 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K44" t="n">
+        <v>950</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB44" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Peruvian Primera Division</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Atletico Grau</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Cesar Vallejo Moquegua</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X45" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB45" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB45"/>
+  <dimension ref="A1:CB48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
         <v>2.8</v>
@@ -1138,7 +1138,7 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
         <v>2.28</v>
@@ -1162,7 +1162,7 @@
         <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1282,16 +1282,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO3" t="n">
         <v>4.5</v>
@@ -1300,13 +1300,13 @@
         <v>17</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>6.6</v>
@@ -1318,23 +1318,23 @@
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
         <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>18.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
         <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN4" t="n">
         <v>55</v>
@@ -1482,19 +1482,19 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1506,25 +1506,25 @@
         <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1718,7 +1718,7 @@
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
         <v>32</v>
@@ -1748,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
         <v>13</v>
@@ -1775,7 +1775,7 @@
         <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
         <v>32</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -1885,7 +1885,7 @@
         <v>110</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O6" t="n">
         <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v>1.91</v>
       </c>
       <c r="T8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U8" t="n">
         <v>2.68</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.15</v>
@@ -2665,13 +2665,13 @@
         <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
         <v>1.27</v>
       </c>
       <c r="R9" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
         <v>1.64</v>
@@ -2680,13 +2680,13 @@
         <v>1.53</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>65</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
@@ -2922,7 +2922,7 @@
         <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.69</v>
@@ -2931,13 +2931,13 @@
         <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
         <v>3.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>1.86</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
         <v>6.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>3.75</v>
@@ -3684,13 +3684,13 @@
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
         <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.7</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
         <v>1.53</v>
@@ -3944,7 +3944,7 @@
         <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.46</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
         <v>8.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>32</v>
@@ -4252,7 +4252,7 @@
         <v>14</v>
       </c>
       <c r="AK15" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
         <v>55</v>
@@ -4270,25 +4270,25 @@
         <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT15" t="n">
         <v>6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.7</v>
       </c>
       <c r="AU15" t="n">
         <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4297,10 +4297,10 @@
         <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
         <v>9.4</v>
@@ -4309,16 +4309,16 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF15" t="n">
         <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4342,16 +4342,16 @@
         <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BP15" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BR15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS15" t="n">
         <v>1.79</v>
@@ -4378,11 +4378,11 @@
         <v>26</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4437,16 +4437,16 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I17" t="n">
         <v>1.46</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>1.21</v>
@@ -4697,22 +4697,22 @@
         <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
         <v>1.78</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
         <v>3.15</v>
@@ -4760,7 +4760,7 @@
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL17" t="n">
         <v>75</v>
@@ -4769,118 +4769,118 @@
         <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO17" t="n">
         <v>4.9</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU17" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AV17" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
         <v>4.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
         <v>6</v>
       </c>
-      <c r="BD17" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BH17" t="n">
         <v>5.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="BT17" t="n">
         <v>4.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -5181,16 +5181,16 @@
         <v>4.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.31</v>
@@ -5217,19 +5217,19 @@
         <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
         <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
@@ -5316,7 +5316,7 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
         <v>4.4</v>
@@ -5328,13 +5328,13 @@
         <v>4.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF19" t="n">
         <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
@@ -5376,7 +5376,7 @@
         <v>5</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV19" t="n">
         <v>14</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Valerenga</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.58</v>
       </c>
-      <c r="G23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="U23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X23" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK23" t="n">
         <v>5.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CA23" t="n">
         <v>6.4</v>
       </c>
-      <c r="J23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,175 +6436,175 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Valerenga</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>19.5</v>
+        <v>1.65</v>
       </c>
       <c r="H24" t="n">
-        <v>1.31</v>
+        <v>5.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.37</v>
+        <v>6.4</v>
       </c>
       <c r="J24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.5</v>
       </c>
-      <c r="K24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG24" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6646,7 +6646,7 @@
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O25" t="n">
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q25" t="n">
         <v>1.17</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>1.63</v>
@@ -7270,7 +7270,7 @@
         <v>25</v>
       </c>
       <c r="AA27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB27" t="n">
         <v>8.4</v>
@@ -7282,7 +7282,7 @@
         <v>19</v>
       </c>
       <c r="AE27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
         <v>18.5</v>
@@ -7306,7 +7306,7 @@
         <v>95</v>
       </c>
       <c r="AM27" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="n">
         <v>70</v>
@@ -7324,19 +7324,19 @@
         <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
         <v>5.7</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV27" t="n">
         <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -7348,31 +7348,31 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="n">
         <v>2.56</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="BJ27" t="n">
         <v>12.5</v>
@@ -7390,7 +7390,7 @@
         <v>5.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP27" t="n">
         <v>27</v>
@@ -7408,7 +7408,7 @@
         <v>6.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BV27" t="n">
         <v>38</v>
@@ -7423,14 +7423,14 @@
         <v>10</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA27" t="n">
         <v>10</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -7485,13 +7485,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="O28" t="n">
         <v>1.19</v>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
         <v>1.19</v>
@@ -7500,7 +7500,7 @@
         <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>110</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>950</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,239 +7960,239 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.1</v>
+        <v>1.49</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="I30" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="K30" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>2.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.48</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V30" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="W30" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="n">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="AA30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE30" t="n">
         <v>20</v>
       </c>
-      <c r="AB30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AF30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.5</v>
+        <v>48</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AP30" t="n">
-        <v>25</v>
+        <v>3.75</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12.5</v>
+        <v>2.98</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>15.5</v>
+        <v>3.35</v>
       </c>
       <c r="AT30" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="AX30" t="n">
-        <v>42</v>
+        <v>4.3</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>4.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="BA30" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="BB30" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>48</v>
+        <v>4.4</v>
       </c>
       <c r="BD30" t="n">
-        <v>42</v>
+        <v>4.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>55</v>
+        <v>4.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>32</v>
+        <v>4.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="BH30" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="BV30" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G31" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H31" t="n">
         <v>4.5</v>
@@ -8241,40 +8241,40 @@
         <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P31" t="n">
         <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R31" t="n">
         <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U31" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V31" t="n">
         <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X31" t="n">
         <v>17</v>
@@ -8286,7 +8286,7 @@
         <v>38</v>
       </c>
       <c r="AA31" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB31" t="n">
         <v>9.6</v>
@@ -8295,7 +8295,7 @@
         <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE31" t="n">
         <v>60</v>
@@ -8307,19 +8307,19 @@
         <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ31" t="n">
         <v>19.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM31" t="n">
         <v>100</v>
@@ -8331,7 +8331,7 @@
         <v>60</v>
       </c>
       <c r="AP31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AQ31" t="n">
         <v>15.5</v>
@@ -8346,10 +8346,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
         <v>50</v>
@@ -8370,10 +8370,10 @@
         <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
         <v>14.5</v>
@@ -8382,31 +8382,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BJ31" t="n">
         <v>13.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BN31" t="n">
         <v>6</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.65</v>
+        <v>1.35</v>
       </c>
       <c r="BP31" t="n">
         <v>16.5</v>
@@ -8415,10 +8415,10 @@
         <v>8.4</v>
       </c>
       <c r="BR31" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BT31" t="n">
         <v>11.5</v>
@@ -8430,23 +8430,23 @@
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BZ31" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -8468,31 +8468,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="G32" t="n">
         <v>2.52</v>
       </c>
       <c r="H32" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K32" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8501,22 +8501,22 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="O32" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.26</v>
+        <v>1.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>1.26</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -8525,10 +8525,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8639,68 +8639,68 @@
         <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BN32" t="n">
         <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BT32" t="n">
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
         <v>4.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -8767,7 +8767,7 @@
         <v>1.81</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
         <v>3.2</v>
@@ -8896,7 +8896,7 @@
         <v>3.75</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="BJ33" t="n">
         <v>10</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
         <v>6.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV34" t="n">
         <v>7.6</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
         <v>3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -9308,16 +9308,16 @@
         <v>13.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35" t="n">
         <v>16</v>
       </c>
       <c r="AE35" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF35" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG35" t="n">
         <v>13.5</v>
@@ -9329,19 +9329,19 @@
         <v>48</v>
       </c>
       <c r="AJ35" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK35" t="n">
         <v>29</v>
       </c>
       <c r="AL35" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM35" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO35" t="n">
         <v>34</v>
@@ -9410,7 +9410,7 @@
         <v>9.4</v>
       </c>
       <c r="BK35" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9422,7 +9422,7 @@
         <v>5.7</v>
       </c>
       <c r="BO35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP35" t="n">
         <v>18</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.28</v>
@@ -9529,10 +9529,10 @@
         <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9676,7 +9676,7 @@
         <v>6.4</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP36" t="n">
         <v>18</v>
@@ -9694,7 +9694,7 @@
         <v>11.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>5.1</v>
+        <v>1.61</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -9738,31 +9738,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="G37" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="H37" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="K37" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,22 +9771,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="O37" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="R37" t="n">
         <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9795,10 +9795,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9909,68 +9909,68 @@
         <v>1.01</v>
       </c>
       <c r="BH37" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -9992,31 +9992,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="G38" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="H38" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J38" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10025,40 +10025,40 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="O38" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="R38" t="n">
         <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W38" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
@@ -10067,10 +10067,10 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -10079,25 +10079,25 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
         <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
@@ -10121,10 +10121,10 @@
         <v>1.03</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU38" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV38" t="n">
         <v>1.03</v>
@@ -10133,19 +10133,19 @@
         <v>1.03</v>
       </c>
       <c r="AX38" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AY38" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA38" t="n">
         <v>1.03</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC38" t="n">
         <v>1.03</v>
@@ -10163,68 +10163,68 @@
         <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BN38" t="n">
         <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -10246,239 +10246,239 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6</v>
+        <v>1.54</v>
       </c>
       <c r="H39" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="L39" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O39" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.12</v>
+        <v>1.54</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
-        <v>3.85</v>
+        <v>1.54</v>
       </c>
       <c r="T39" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="X39" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="Z39" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>17</v>
       </c>
-      <c r="AE39" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>14</v>
-      </c>
       <c r="BA39" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA39" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -10500,239 +10500,239 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="H40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.25</v>
       </c>
-      <c r="I40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1.59</v>
-      </c>
       <c r="O40" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P40" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V40" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.37</v>
+        <v>5.3</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.37</v>
+        <v>10</v>
       </c>
       <c r="BN40" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="BP40" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.37</v>
+        <v>6.8</v>
       </c>
       <c r="BR40" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT40" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.37</v>
+        <v>5.5</v>
       </c>
       <c r="BV40" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.37</v>
+        <v>7.8</v>
       </c>
       <c r="BX40" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.37</v>
+        <v>8.6</v>
       </c>
       <c r="BZ40" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA40" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -10778,13 +10778,13 @@
         <v>3.3</v>
       </c>
       <c r="K41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
         <v>3.15</v>
@@ -10793,28 +10793,28 @@
         <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R41" t="n">
         <v>1.23</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V41" t="n">
         <v>1.39</v>
       </c>
       <c r="W41" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10883,10 +10883,10 @@
         <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU41" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV41" t="n">
         <v>8.800000000000001</v>
@@ -10928,65 +10928,65 @@
         <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BJ41" t="n">
         <v>13.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BP41" t="n">
         <v>26</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BR41" t="n">
         <v>50</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BT41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU41" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV41" t="n">
         <v>40</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BZ41" t="n">
         <v>48</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -11573,10 +11573,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,769 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Nublense</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB46" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K48" t="n">
+        <v>950</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB48" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
@@ -1135,7 +1135,7 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
@@ -1144,22 +1144,22 @@
         <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
         <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
         <v>1.64</v>
@@ -1192,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>17.5</v>
@@ -1228,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
         <v>16</v>
@@ -1252,22 +1252,22 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
         <v>20</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>19.5</v>
@@ -1482,7 +1482,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>5.7</v>
@@ -1494,7 +1494,7 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1506,28 +1506,28 @@
         <v>19</v>
       </c>
       <c r="BA4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BI4" t="n">
         <v>1.75</v>
@@ -1536,7 +1536,7 @@
         <v>15.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
         <v>30</v>
@@ -1566,7 +1566,7 @@
         <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>50</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1664,13 +1664,13 @@
         <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1685,22 +1685,22 @@
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
       </c>
       <c r="AF5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>21</v>
@@ -1724,7 +1724,7 @@
         <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP5" t="n">
         <v>8.4</v>
@@ -1733,13 +1733,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
         <v>48</v>
@@ -1772,10 +1772,10 @@
         <v>42</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
         <v>32</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,7 +1799,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO5" t="n">
         <v>4</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>6.6</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2154,19 +2154,19 @@
         <v>1.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>1.43</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J10" t="n">
         <v>5.3</v>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
@@ -2922,7 +2922,7 @@
         <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
         <v>1.69</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
         <v>3.85</v>
@@ -3194,7 +3194,7 @@
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3203,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
         <v>110</v>
@@ -3248,7 +3248,7 @@
         <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="n">
         <v>8.800000000000001</v>
@@ -3320,13 +3320,13 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP11" t="n">
         <v>18</v>
@@ -3338,35 +3338,35 @@
         <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT11" t="n">
         <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
         <v>8.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.64</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H12" t="n">
         <v>4.1</v>
@@ -3409,7 +3409,7 @@
         <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
         <v>5.4</v>
@@ -3448,7 +3448,7 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.75</v>
@@ -3699,7 +3699,7 @@
         <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
         <v>1.57</v>
@@ -3816,7 +3816,7 @@
         <v>3.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.199999999999999</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
         <v>1.53</v>
@@ -3944,7 +3944,7 @@
         <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
         <v>1.46</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
         <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE15" t="n">
         <v>200</v>
@@ -4270,10 +4270,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
         <v>6.6</v>
@@ -4288,7 +4288,7 @@
         <v>5.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4297,10 +4297,10 @@
         <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
         <v>9.4</v>
@@ -4312,7 +4312,7 @@
         <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
         <v>6.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G19" t="n">
         <v>4.2</v>
@@ -5184,10 +5184,10 @@
         <v>1.99</v>
       </c>
       <c r="I19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.28</v>
@@ -5223,7 +5223,7 @@
         <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W19" t="n">
         <v>1.31</v>
@@ -5241,7 +5241,7 @@
         <v>28</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
@@ -5307,7 +5307,7 @@
         <v>16.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY19" t="n">
         <v>14.5</v>
@@ -5319,7 +5319,7 @@
         <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC19" t="n">
         <v>4.3</v>
@@ -5340,7 +5340,7 @@
         <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.800000000000001</v>
@@ -5376,7 +5376,7 @@
         <v>5</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BV19" t="n">
         <v>14</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
         <v>2.24</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
         <v>5.4</v>
@@ -6275,7 +6275,7 @@
         <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -6323,7 +6323,7 @@
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY23" t="n">
         <v>19</v>
@@ -6341,13 +6341,13 @@
         <v>48</v>
       </c>
       <c r="BD23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE23" t="n">
         <v>55</v>
       </c>
       <c r="BF23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG23" t="n">
         <v>5.2</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -6559,10 +6559,10 @@
         <v>21</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT24" t="n">
         <v>9.6</v>
@@ -6586,7 +6586,7 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB24" t="n">
         <v>12</v>
@@ -6598,13 +6598,13 @@
         <v>18.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF24" t="n">
         <v>4.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -6702,16 +6702,16 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H25" t="n">
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -6750,7 +6750,7 @@
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>3.55</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -7115,68 +7115,68 @@
         <v>6</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="BJ26" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.79</v>
+        <v>14</v>
       </c>
       <c r="BN26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU26" t="n">
         <v>6</v>
       </c>
-      <c r="BO26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.74</v>
+        <v>11.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.76</v>
+        <v>12</v>
       </c>
       <c r="BZ26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.73</v>
+        <v>11</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.49</v>
+        <v>7.2</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="I30" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="J30" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.31</v>
@@ -7993,7 +7993,7 @@
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.29</v>
@@ -8017,7 +8017,7 @@
         <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="W30" t="n">
         <v>1.05</v>
@@ -8029,7 +8029,7 @@
         <v>8.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AA30" t="n">
         <v>970</v>
@@ -8077,58 +8077,58 @@
         <v>8</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AR30" t="n">
         <v>2.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AW30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -8223,25 +8223,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G31" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -8256,7 +8256,7 @@
         <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R31" t="n">
         <v>1.42</v>
@@ -8268,34 +8268,34 @@
         <v>1.81</v>
       </c>
       <c r="U31" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="X31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA31" t="n">
         <v>110</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>60</v>
@@ -8307,13 +8307,13 @@
         <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
         <v>19.5</v>
@@ -8325,7 +8325,7 @@
         <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO31" t="n">
         <v>60</v>
@@ -8340,7 +8340,7 @@
         <v>30</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT31" t="n">
         <v>8.800000000000001</v>
@@ -8349,7 +8349,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW31" t="n">
         <v>50</v>
@@ -8376,77 +8376,77 @@
         <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH31" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.74</v>
+        <v>3.35</v>
       </c>
       <c r="BJ31" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.54</v>
+        <v>7.4</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.74</v>
+        <v>14</v>
       </c>
       <c r="BN31" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP31" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BQ31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT31" t="n">
         <v>8.4</v>
       </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BT31" t="n">
+      <c r="BU31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
         <v>11.5</v>
       </c>
-      <c r="BU31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.69</v>
+        <v>12</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
         <v>3.75</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="BJ33" t="n">
         <v>10</v>
@@ -8932,7 +8932,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU33" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
         <v>3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -9410,7 +9410,7 @@
         <v>9.4</v>
       </c>
       <c r="BK35" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9428,7 +9428,7 @@
         <v>18</v>
       </c>
       <c r="BQ35" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BR35" t="n">
         <v>30</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -9511,10 +9511,10 @@
         <v>4.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
         <v>4.1</v>
@@ -9532,13 +9532,13 @@
         <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V36" t="n">
         <v>1.25</v>
@@ -9547,176 +9547,176 @@
         <v>2.12</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
         <v>970</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR36" t="n">
         <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD36" t="n">
         <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG36" t="n">
         <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="BJ36" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.88</v>
+        <v>14.5</v>
       </c>
       <c r="BN36" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP36" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="BR36" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.79</v>
+        <v>10</v>
       </c>
       <c r="BT36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW36" t="n">
         <v>11.5</v>
       </c>
-      <c r="BU36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BV36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.83</v>
+        <v>12</v>
       </c>
       <c r="BZ36" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.76</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -9750,16 +9750,16 @@
         <v>2.24</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H37" t="n">
         <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J37" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
         <v>4.4</v>
@@ -9795,10 +9795,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="G39" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H39" t="n">
         <v>6.8</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="J39" t="n">
         <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
         <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T40" t="n">
         <v>1.84</v>
@@ -10605,7 +10605,7 @@
         <v>30</v>
       </c>
       <c r="AL40" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM40" t="n">
         <v>130</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -10799,10 +10799,10 @@
         <v>2.14</v>
       </c>
       <c r="R41" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11797,7 @@
         <v>4.1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -12069,10 +12069,10 @@
         <v>1.87</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="T46" t="n">
         <v>1.69</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H47" t="n">
         <v>4.2</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K48" t="n">
         <v>950</v>
@@ -12649,52 +12649,52 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -857,106 +857,106 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
         <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -965,122 +965,122 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.02</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
         <v>1.02</v>
@@ -1144,13 +1144,13 @@
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1371,25 +1371,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>1.25</v>
@@ -1401,76 +1401,76 @@
         <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
         <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
@@ -1482,7 +1482,7 @@
         <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
         <v>1.01</v>
@@ -1506,7 +1506,7 @@
         <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
@@ -1518,7 +1518,7 @@
         <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1527,13 +1527,13 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1545,25 +1545,25 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
@@ -1581,14 +1581,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I5" t="n">
         <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1649,7 +1649,7 @@
         <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.68</v>
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX5" t="n">
         <v>16</v>
@@ -1760,19 +1760,19 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
         <v>12.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
         <v>1.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB6" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX6" t="n">
+      <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO6" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU6" t="n">
         <v>5.6</v>
       </c>
-      <c r="BA6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.69</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.71</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.71</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2127,52 +2127,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
         <v>1.45</v>
@@ -2184,7 +2184,7 @@
         <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -2205,7 +2205,7 @@
         <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -2217,37 +2217,37 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR7" t="n">
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>48</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
@@ -2256,101 +2256,101 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG7" t="n">
         <v>26</v>
       </c>
-      <c r="BD7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>32</v>
-      </c>
       <c r="BH7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.42</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
         <v>5.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.09</v>
       </c>
       <c r="G8" t="n">
-        <v>970</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
         <v>110</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2432,7 +2432,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.37</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H9" t="n">
         <v>8.199999999999999</v>
@@ -2653,13 +2653,13 @@
         <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
@@ -2668,7 +2668,7 @@
         <v>2.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.69</v>
@@ -2680,7 +2680,7 @@
         <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
         <v>1.11</v>
@@ -2692,13 +2692,13 @@
         <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB9" t="n">
         <v>13.5</v>
@@ -2710,7 +2710,7 @@
         <v>38</v>
       </c>
       <c r="AE9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2719,19 +2719,19 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
         <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
@@ -2740,70 +2740,70 @@
         <v>5.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
         <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC9" t="n">
         <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
@@ -2815,25 +2815,25 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
@@ -2851,14 +2851,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="J10" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.15</v>
@@ -2919,31 +2919,31 @@
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R10" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
@@ -2952,13 +2952,13 @@
         <v>15.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AD10" t="n">
         <v>13.5</v>
@@ -2967,94 +2967,94 @@
         <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
         <v>25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AK10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
         <v>70</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>60</v>
       </c>
       <c r="AO10" t="n">
         <v>3.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY10" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AZ10" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB10" t="n">
         <v>7.2</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BC10" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BD10" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3063,10 +3063,10 @@
         <v>5.1</v>
       </c>
       <c r="BL10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>14</v>
@@ -3075,28 +3075,28 @@
         <v>5.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV10" t="n">
         <v>7.8</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX10" t="n">
         <v>16</v>
@@ -3105,14 +3105,14 @@
         <v>6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3146,37 +3146,37 @@
         <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
         <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -3185,13 +3185,13 @@
         <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.76</v>
@@ -3230,7 +3230,7 @@
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
         <v>32</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3651,28 +3651,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.18</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>3.45</v>
@@ -3681,13 +3681,13 @@
         <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q13" t="n">
         <v>1.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S13" t="n">
         <v>1.87</v>
@@ -3702,7 +3702,7 @@
         <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="X13" t="n">
         <v>55</v>
@@ -3729,7 +3729,7 @@
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
         <v>14</v>
@@ -3741,7 +3741,7 @@
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
         <v>18</v>
@@ -3753,64 +3753,64 @@
         <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AO13" t="n">
         <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV13" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AW13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="AX13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY13" t="n">
         <v>3.45</v>
       </c>
-      <c r="AV13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="n">
         <v>5.7</v>
@@ -3822,13 +3822,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BL13" t="n">
         <v>65</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN13" t="n">
         <v>5.3</v>
@@ -3840,41 +3840,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR13" t="n">
         <v>17.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BX13" t="n">
         <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ13" t="n">
         <v>10.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
         <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3944,31 +3944,31 @@
         <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
         <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
         <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z14" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA14" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AB14" t="n">
         <v>7.6</v>
@@ -3977,7 +3977,7 @@
         <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE14" t="n">
         <v>200</v>
@@ -3995,7 +3995,7 @@
         <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK14" t="n">
         <v>18</v>
@@ -4004,131 +4004,131 @@
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
         <v>320</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR14" t="n">
         <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA14" t="n">
         <v>6.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
         <v>3.95</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="BJ14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.89</v>
+        <v>2.64</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BP14" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.89</v>
+        <v>9.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.89</v>
+        <v>9.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.76</v>
+        <v>14</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I16" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
         <v>7.6</v>
@@ -4437,37 +4437,37 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P16" t="n">
         <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4479,7 +4479,7 @@
         <v>970</v>
       </c>
       <c r="AB16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
@@ -4491,16 +4491,16 @@
         <v>970</v>
       </c>
       <c r="AF16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
@@ -4509,70 +4509,70 @@
         <v>100</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>85</v>
       </c>
       <c r="AO16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX16" t="n">
         <v>4.9</v>
       </c>
-      <c r="AP16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="AY16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="n">
         <v>5.3</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="I17" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="J17" t="n">
         <v>1.09</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -4697,28 +4697,28 @@
         <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
         <v>2.18</v>
       </c>
       <c r="T17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V17" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="X17" t="n">
         <v>30</v>
@@ -4730,7 +4730,7 @@
         <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB17" t="n">
         <v>25</v>
@@ -4742,10 +4742,10 @@
         <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG17" t="n">
         <v>970</v>
@@ -4757,73 +4757,73 @@
         <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK17" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
         <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO17" t="n">
         <v>970</v>
       </c>
       <c r="AP17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BA17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF17" t="n">
         <v>4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.75</v>
       </c>
       <c r="BG17" t="n">
         <v>3.1</v>
@@ -4838,59 +4838,59 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4924,91 +4924,91 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I18" t="n">
         <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
         <v>25</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
         <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
         <v>46</v>
@@ -5017,22 +5017,22 @@
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
@@ -5041,7 +5041,7 @@
         <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU18" t="n">
         <v>6.2</v>
@@ -5056,49 +5056,49 @@
         <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
         <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG18" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.18</v>
+        <v>5.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="BN18" t="n">
         <v>5.7</v>
@@ -5107,16 +5107,16 @@
         <v>4.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
         <v>6.2</v>
@@ -5128,23 +5128,23 @@
         <v>22</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.54</v>
+        <v>9</v>
       </c>
       <c r="BX18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.64</v>
+        <v>10.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.58</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
         <v>4.1</v>
@@ -5187,7 +5187,7 @@
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
         <v>5.4</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
@@ -5208,7 +5208,7 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
@@ -5226,7 +5226,7 @@
         <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>2.44</v>
       </c>
       <c r="I20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.42</v>
@@ -5453,7 +5453,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
@@ -5462,7 +5462,7 @@
         <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1.35</v>
@@ -5471,7 +5471,7 @@
         <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U20" t="n">
         <v>2.16</v>
@@ -5483,10 +5483,10 @@
         <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
         <v>19</v>
@@ -5537,25 +5537,25 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR20" t="n">
         <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
         <v>21</v>
@@ -5564,28 +5564,28 @@
         <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG20" t="n">
         <v>17</v>
@@ -5594,7 +5594,7 @@
         <v>3.75</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ20" t="n">
         <v>11</v>
@@ -5621,7 +5621,7 @@
         <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5689,70 +5689,70 @@
         <v>4.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I21" t="n">
         <v>2.06</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
         <v>1.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U21" t="n">
         <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W21" t="n">
         <v>1.31</v>
       </c>
       <c r="X21" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA21" t="n">
         <v>28</v>
       </c>
       <c r="AB21" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
         <v>12.5</v>
@@ -5761,10 +5761,10 @@
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG21" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AH21" t="n">
         <v>21</v>
@@ -5773,10 +5773,10 @@
         <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL21" t="n">
         <v>55</v>
@@ -5788,16 +5788,16 @@
         <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP21" t="n">
         <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS21" t="n">
         <v>19</v>
@@ -5809,52 +5809,52 @@
         <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5869,13 +5869,13 @@
         <v>5.7</v>
       </c>
       <c r="BP21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ21" t="n">
         <v>8</v>
       </c>
       <c r="BR21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS21" t="n">
         <v>8.4</v>
@@ -5890,13 +5890,13 @@
         <v>14</v>
       </c>
       <c r="BW21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX21" t="n">
         <v>27</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
         <v>5.2</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
         <v>5</v>
@@ -5961,28 +5961,28 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T22" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U22" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V22" t="n">
         <v>1.24</v>
@@ -6015,7 +6015,7 @@
         <v>60</v>
       </c>
       <c r="AF22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG22" t="n">
         <v>12.5</v>
@@ -6045,79 +6045,79 @@
         <v>40</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC22" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD22" t="n">
         <v>18.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL22" t="n">
         <v>75</v>
       </c>
       <c r="BM22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO22" t="n">
         <v>3.95</v>
@@ -6126,41 +6126,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR22" t="n">
         <v>19</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV22" t="n">
         <v>34</v>
       </c>
       <c r="BW22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX22" t="n">
         <v>34</v>
       </c>
       <c r="BY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6203,10 +6203,10 @@
         <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
@@ -6230,13 +6230,13 @@
         <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T23" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -6245,13 +6245,13 @@
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AA23" t="n">
         <v>110</v>
@@ -6260,19 +6260,19 @@
         <v>11.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>18.5</v>
@@ -6281,16 +6281,16 @@
         <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="n">
         <v>9.800000000000001</v>
@@ -6299,55 +6299,55 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV23" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>38</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
         <v>38</v>
       </c>
       <c r="BB23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC23" t="n">
         <v>15</v>
       </c>
-      <c r="BC23" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD23" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BE23" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
         <v>34</v>
@@ -6356,19 +6356,19 @@
         <v>4.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>9.4</v>
       </c>
       <c r="BN23" t="n">
         <v>4.9</v>
@@ -6380,41 +6380,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT23" t="n">
         <v>8.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>18.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I24" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -6469,28 +6469,28 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
         <v>2.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T24" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
@@ -6562,31 +6562,31 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV24" t="n">
         <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX24" t="n">
         <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB24" t="n">
         <v>20</v>
@@ -6595,13 +6595,13 @@
         <v>15.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG24" t="n">
         <v>20</v>
@@ -6610,7 +6610,7 @@
         <v>4.3</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ24" t="n">
         <v>9.199999999999999</v>
@@ -6622,7 +6622,7 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24" t="n">
         <v>5.5</v>
@@ -6640,10 +6640,10 @@
         <v>25</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU24" t="n">
         <v>5.5</v>
@@ -6652,23 +6652,23 @@
         <v>26</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>18.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="G25" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
         <v>5.4</v>
@@ -6720,19 +6720,19 @@
         <v>1.21</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R25" t="n">
         <v>1.76</v>
@@ -6741,16 +6741,16 @@
         <v>2.16</v>
       </c>
       <c r="T25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="W25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>32</v>
@@ -6759,34 +6759,34 @@
         <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
         <v>10.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF25" t="n">
         <v>55</v>
       </c>
       <c r="AG25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ25" t="n">
         <v>140</v>
@@ -6804,10 +6804,10 @@
         <v>44</v>
       </c>
       <c r="AO25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ25" t="n">
         <v>12.5</v>
@@ -6831,10 +6831,10 @@
         <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>16</v>
@@ -6843,22 +6843,22 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BC25" t="n">
         <v>48</v>
       </c>
       <c r="BD25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE25" t="n">
         <v>55</v>
       </c>
       <c r="BF25" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH25" t="n">
         <v>5</v>
@@ -6870,34 +6870,34 @@
         <v>9</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP25" t="n">
         <v>36</v>
       </c>
       <c r="BQ25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR25" t="n">
         <v>36</v>
       </c>
       <c r="BS25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU25" t="n">
         <v>3.75</v>
@@ -6912,17 +6912,17 @@
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>11.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6983,7 +6983,7 @@
         <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q26" t="n">
         <v>1.52</v>
@@ -7010,13 +7010,13 @@
         <v>28</v>
       </c>
       <c r="Y26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA26" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB26" t="n">
         <v>15.5</v>
@@ -7025,10 +7025,10 @@
         <v>13.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
         <v>15</v>
@@ -7067,53 +7067,53 @@
         <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY26" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>7.8</v>
       </c>
       <c r="AZ26" t="n">
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB26" t="n">
         <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
         <v>18.5</v>
       </c>
       <c r="BE26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG26" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7207,16 +7207,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G27" t="n">
         <v>970</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I27" t="n">
-        <v>970</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>1.01</v>
@@ -7255,7 +7255,7 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7470,10 +7470,10 @@
         <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.5</v>
@@ -7485,16 +7485,16 @@
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P28" t="n">
         <v>1.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
         <v>1.23</v>
@@ -7509,10 +7509,10 @@
         <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X28" t="n">
         <v>10.5</v>
@@ -7584,19 +7584,19 @@
         <v>3.65</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AW28" t="n">
         <v>6</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ28" t="n">
         <v>5.2</v>
@@ -7638,53 +7638,53 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>15.5</v>
+        <v>3.55</v>
       </c>
       <c r="BN28" t="n">
         <v>4.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT28" t="n">
         <v>7.8</v>
       </c>
       <c r="BU28" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>13</v>
+        <v>3.4</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7718,10 +7718,10 @@
         <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="n">
         <v>3.75</v>
@@ -7730,13 +7730,13 @@
         <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="L29" t="n">
         <v>1.58</v>
       </c>
       <c r="M29" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N29" t="n">
         <v>2.3</v>
@@ -7748,37 +7748,37 @@
         <v>1.43</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
         <v>1.15</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U29" t="n">
         <v>1.67</v>
       </c>
       <c r="V29" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z29" t="n">
         <v>25</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
         <v>8.199999999999999</v>
@@ -7790,7 +7790,7 @@
         <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF29" t="n">
         <v>18</v>
@@ -7805,76 +7805,76 @@
         <v>110</v>
       </c>
       <c r="AJ29" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK29" t="n">
         <v>55</v>
       </c>
       <c r="AL29" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM29" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO29" t="n">
         <v>110</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AQ29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT29" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS29" t="n">
+      <c r="AU29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>5.4</v>
       </c>
-      <c r="AT29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU29" t="n">
+      <c r="BA29" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BB29" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="n">
         <v>2.5</v>
@@ -7898,16 +7898,16 @@
         <v>5.4</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ29" t="n">
         <v>10</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS29" t="n">
         <v>12.5</v>
@@ -7925,20 +7925,20 @@
         <v>11</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY29" t="n">
         <v>13</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA29" t="n">
         <v>13</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8477,55 +8477,55 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.49</v>
+        <v>8.4</v>
       </c>
       <c r="G32" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="H32" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="J32" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="K32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V32" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="W32" t="n">
         <v>1.05</v>
@@ -8543,7 +8543,7 @@
         <v>970</v>
       </c>
       <c r="AB32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AC32" t="n">
         <v>970</v>
@@ -8558,13 +8558,13 @@
         <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI32" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
         <v>1000</v>
@@ -8582,61 +8582,61 @@
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AR32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="AT32" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.65</v>
+        <v>1.91</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.1</v>
+        <v>2.04</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8678,7 +8678,7 @@
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G33" t="n">
         <v>1.88</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.96</v>
-      </c>
       <c r="H33" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.3</v>
@@ -8755,61 +8755,61 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P33" t="n">
         <v>2.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R33" t="n">
         <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U33" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
         <v>1.27</v>
       </c>
       <c r="W33" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X33" t="n">
         <v>16</v>
       </c>
       <c r="Y33" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB33" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AC33" t="n">
         <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
@@ -8824,16 +8824,16 @@
         <v>21</v>
       </c>
       <c r="AK33" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM33" t="n">
         <v>95</v>
       </c>
       <c r="AN33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO33" t="n">
         <v>55</v>
@@ -8842,31 +8842,31 @@
         <v>14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS33" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW33" t="n">
-        <v>48</v>
+        <v>8.6</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
         <v>17.5</v>
@@ -8881,80 +8881,80 @@
         <v>17</v>
       </c>
       <c r="BD33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE33" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG33" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BH33" t="n">
         <v>3.65</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.6</v>
       </c>
       <c r="BK33" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ33" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU33" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA33" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G34" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H34" t="n">
         <v>4.6</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>3.8</v>
       </c>
       <c r="K34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
         <v>1.3</v>
@@ -9009,49 +9009,49 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W34" t="n">
         <v>2.1</v>
       </c>
       <c r="X34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="n">
         <v>22</v>
       </c>
       <c r="Z34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA34" t="n">
         <v>130</v>
       </c>
       <c r="AB34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC34" t="n">
         <v>970</v>
@@ -9063,7 +9063,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG34" t="n">
         <v>12.5</v>
@@ -9108,7 +9108,7 @@
         <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV34" t="n">
         <v>13.5</v>
@@ -9117,13 +9117,13 @@
         <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
         <v>1.01</v>
@@ -9141,7 +9141,7 @@
         <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG34" t="n">
         <v>1.01</v>
@@ -9150,7 +9150,7 @@
         <v>3.7</v>
       </c>
       <c r="BI34" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.6</v>
@@ -9168,7 +9168,7 @@
         <v>4.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP34" t="n">
         <v>12.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G35" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H35" t="n">
         <v>4.1</v>
@@ -9251,13 +9251,13 @@
         <v>4.7</v>
       </c>
       <c r="J35" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K35" t="n">
         <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -9272,7 +9272,7 @@
         <v>2.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R35" t="n">
         <v>1.39</v>
@@ -9284,10 +9284,10 @@
         <v>1.75</v>
       </c>
       <c r="U35" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V35" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
         <v>2.02</v>
@@ -9299,7 +9299,7 @@
         <v>17.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="n">
         <v>110</v>
@@ -9404,65 +9404,65 @@
         <v>3.7</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BJ35" t="n">
         <v>10</v>
       </c>
       <c r="BK35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN35" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO35" t="n">
         <v>3.75</v>
       </c>
       <c r="BP35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BR35" t="n">
         <v>28</v>
       </c>
       <c r="BS35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ35" t="n">
         <v>23</v>
       </c>
       <c r="CA35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G36" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H36" t="n">
         <v>1.77</v>
@@ -9508,10 +9508,10 @@
         <v>3.8</v>
       </c>
       <c r="K36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
@@ -9520,22 +9520,22 @@
         <v>3.6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T36" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.88</v>
       </c>
       <c r="U36" t="n">
         <v>1.99</v>
@@ -9586,13 +9586,13 @@
         <v>160</v>
       </c>
       <c r="AK36" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL36" t="n">
         <v>80</v>
       </c>
       <c r="AM36" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN36" t="n">
         <v>110</v>
@@ -9607,19 +9607,19 @@
         <v>7.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS36" t="n">
         <v>14</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU36" t="n">
         <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AW36" t="n">
         <v>7.2</v>
@@ -9634,7 +9634,7 @@
         <v>15</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BB36" t="n">
         <v>6.8</v>
@@ -9643,10 +9643,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF36" t="n">
         <v>10</v>
@@ -9655,10 +9655,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ36" t="n">
         <v>10.5</v>
@@ -9670,7 +9670,7 @@
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN36" t="n">
         <v>8.6</v>
@@ -9706,17 +9706,17 @@
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ36" t="n">
         <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G37" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H37" t="n">
         <v>2.96</v>
@@ -9759,13 +9759,13 @@
         <v>3.35</v>
       </c>
       <c r="J37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K37" t="n">
         <v>3.85</v>
       </c>
       <c r="L37" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
@@ -9795,10 +9795,10 @@
         <v>2.26</v>
       </c>
       <c r="V37" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X37" t="n">
         <v>18.5</v>
@@ -9867,7 +9867,7 @@
         <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
@@ -9912,10 +9912,10 @@
         <v>3.75</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK37" t="n">
         <v>5</v>
@@ -9924,10 +9924,10 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO37" t="n">
         <v>4.3</v>
@@ -9963,14 +9963,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA37" t="n">
         <v>7.4</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -10001,163 +10001,163 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>1.59</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P38" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Q38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.96</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V38" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W38" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H39" t="n">
         <v>3.05</v>
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
         <v>1.26</v>
       </c>
       <c r="P39" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
         <v>1.26</v>
       </c>
       <c r="R39" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
-        <v>2.88</v>
+        <v>1.26</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10420,7 +10420,7 @@
         <v>4.6</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -10509,230 +10509,230 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="G40" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H40" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J40" t="n">
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N40" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="O40" t="n">
         <v>1.31</v>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V40" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W40" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
         <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.31</v>
+        <v>5.3</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.31</v>
+        <v>2.64</v>
       </c>
       <c r="BN40" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="BP40" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BR40" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.31</v>
+        <v>7.8</v>
       </c>
       <c r="BT40" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BV40" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.31</v>
+        <v>8.6</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.31</v>
+        <v>7.4</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v>6.8</v>
       </c>
       <c r="I41" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="J41" t="n">
         <v>4.4</v>
@@ -10799,7 +10799,7 @@
         <v>1.54</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="S41" t="n">
         <v>1.54</v>
@@ -10808,13 +10808,13 @@
         <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10829,7 +10829,7 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC41" t="n">
         <v>18</v>
@@ -10841,7 +10841,7 @@
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG41" t="n">
         <v>15</v>
@@ -10859,7 +10859,7 @@
         <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM41" t="n">
         <v>1000</v>
@@ -10874,7 +10874,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
         <v>1.03</v>
@@ -10883,7 +10883,7 @@
         <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU41" t="n">
         <v>1.01</v>
@@ -10895,25 +10895,25 @@
         <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AY41" t="n">
         <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA41" t="n">
         <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC41" t="n">
         <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
         <v>1.03</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -11017,230 +11017,230 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="H42" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J42" t="n">
         <v>2.96</v>
       </c>
       <c r="K42" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="R42" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>1.33</v>
+        <v>3.8</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V42" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W42" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z42" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AA42" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG42" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD42" t="n">
+      <c r="AH42" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE42" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>25</v>
-      </c>
       <c r="AI42" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ42" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL42" t="n">
         <v>46</v>
       </c>
-      <c r="AK42" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>55</v>
-      </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN42" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AO42" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2.38</v>
+        <v>5.2</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.56</v>
+        <v>19</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.66</v>
+        <v>7.2</v>
       </c>
       <c r="AX42" t="n">
-        <v>2.46</v>
+        <v>11</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.38</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.52</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="BB42" t="n">
-        <v>2.64</v>
+        <v>22</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.66</v>
+        <v>7.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF42" t="n">
-        <v>2.56</v>
+        <v>17.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.68</v>
+        <v>7.2</v>
       </c>
       <c r="BH42" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BJ42" t="n">
         <v>10.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN42" t="n">
         <v>5.4</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP42" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ42" t="n">
         <v>6.6</v>
       </c>
       <c r="BR42" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS42" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT42" t="n">
         <v>6.8</v>
       </c>
       <c r="BU42" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW42" t="n">
-        <v>2.34</v>
+        <v>7.6</v>
       </c>
       <c r="BX42" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY42" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA42" t="n">
         <v>7.8</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -11277,10 +11277,10 @@
         <v>2.5</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J43" t="n">
         <v>3.3</v>
@@ -11289,13 +11289,13 @@
         <v>3.55</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>1.4</v>
@@ -11304,197 +11304,197 @@
         <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="U43" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W43" t="n">
         <v>1.67</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB43" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH43" t="n">
         <v>19</v>
       </c>
-      <c r="AG43" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>22</v>
-      </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ43" t="n">
         <v>40</v>
       </c>
       <c r="AK43" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA43" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR43" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BJ43" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM43" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BN43" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BP43" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BR43" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BT43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV43" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BZ43" t="n">
-        <v>48</v>
-      </c>
-      <c r="CA43" t="n">
-        <v>1.47</v>
-      </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -12033,16 +12033,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G46" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I46" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J46" t="n">
         <v>1.04</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -12290,10 +12290,10 @@
         <v>1.63</v>
       </c>
       <c r="G47" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I47" t="n">
         <v>7.6</v>
@@ -12305,7 +12305,7 @@
         <v>4.1</v>
       </c>
       <c r="L47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -12407,7 +12407,7 @@
         <v>3.45</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AU47" t="n">
         <v>3.5</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -12544,227 +12544,227 @@
         <v>2.94</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H48" t="n">
         <v>2.4</v>
       </c>
       <c r="I48" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K48" t="n">
         <v>3.8</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M48" t="n">
         <v>1.06</v>
       </c>
       <c r="N48" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="O48" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P48" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R48" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="T48" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U48" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W48" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG48" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z48" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD48" t="n">
+      <c r="AH48" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG48" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE48" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV48" t="n">
+      <c r="BH48" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW48" t="n">
         <v>8</v>
       </c>
-      <c r="AW48" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI48" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
         <v>1.58</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -13052,13 +13052,13 @@
         <v>1.04</v>
       </c>
       <c r="G50" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H50" t="n">
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J50" t="n">
         <v>1.03</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -13303,16 +13303,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G51" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="H51" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>3.3</v>
@@ -13354,19 +13354,19 @@
         <v>1.23</v>
       </c>
       <c r="W51" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="X51" t="n">
         <v>13</v>
       </c>
       <c r="Y51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA51" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB51" t="n">
         <v>8.6</v>
@@ -13375,10 +13375,10 @@
         <v>9.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AF51" t="n">
         <v>13.5</v>
@@ -13387,7 +13387,7 @@
         <v>13</v>
       </c>
       <c r="AH51" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI51" t="n">
         <v>110</v>
@@ -13402,13 +13402,13 @@
         <v>60</v>
       </c>
       <c r="AM51" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN51" t="n">
         <v>24</v>
       </c>
       <c r="AO51" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP51" t="n">
         <v>9.199999999999999</v>
@@ -13417,10 +13417,10 @@
         <v>11.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT51" t="n">
         <v>6.4</v>
@@ -13432,7 +13432,7 @@
         <v>16.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX51" t="n">
         <v>9.4</v>
@@ -13441,28 +13441,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD51" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE51" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF51" t="n">
         <v>14</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH51" t="n">
         <v>3.1</v>
@@ -13474,22 +13474,22 @@
         <v>11.5</v>
       </c>
       <c r="BK51" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN51" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO51" t="n">
         <v>3.45</v>
       </c>
       <c r="BP51" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ51" t="n">
         <v>6.2</v>
@@ -13498,35 +13498,35 @@
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT51" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA51" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW51" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA51" t="n">
-        <v>8</v>
-      </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -13557,16 +13557,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G52" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H52" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I52" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J52" t="n">
         <v>3.55</v>
@@ -13581,37 +13581,37 @@
         <v>1.07</v>
       </c>
       <c r="N52" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
         <v>1.34</v>
       </c>
       <c r="P52" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R52" t="n">
         <v>1.32</v>
       </c>
       <c r="S52" t="n">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="T52" t="n">
         <v>1.65</v>
       </c>
       <c r="U52" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
         <v>1.74</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.45</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.96</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.08</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.86</v>
-      </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG2" t="n">
         <v>13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH2" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BI2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO2" t="n">
         <v>3.4</v>
       </c>
-      <c r="AR2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.53</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.53</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
         <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>2.44</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1159,7 +1159,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1374,13 +1374,13 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1395,16 +1395,16 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
         <v>1.7</v>
@@ -1413,7 +1413,7 @@
         <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
@@ -1452,7 +1452,7 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>25</v>
@@ -1467,128 +1467,128 @@
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO4" t="n">
         <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BN4" t="n">
         <v>4.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
         <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BZ4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1646,13 +1646,13 @@
         <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
@@ -1667,7 +1667,7 @@
         <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
         <v>1.66</v>
@@ -1688,7 +1688,7 @@
         <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX5" t="n">
         <v>16</v>
@@ -1760,25 +1760,25 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
         <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="n">
         <v>4.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.82</v>
@@ -1915,10 +1915,10 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
         <v>1.37</v>
@@ -1936,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
         <v>8.6</v>
@@ -1987,7 +1987,7 @@
         <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>7.2</v>
@@ -1999,13 +1999,13 @@
         <v>3.75</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>4.9</v>
@@ -2014,13 +2014,13 @@
         <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
         <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
         <v>7.2</v>
@@ -2029,7 +2029,7 @@
         <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
@@ -2038,7 +2038,7 @@
         <v>2.58</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2157,7 +2157,7 @@
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.22</v>
@@ -2166,7 +2166,7 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.87</v>
@@ -2175,10 +2175,10 @@
         <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -2193,7 +2193,7 @@
         <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -2220,22 +2220,22 @@
         <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.4</v>
@@ -2244,10 +2244,10 @@
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
@@ -2259,22 +2259,22 @@
         <v>34</v>
       </c>
       <c r="AX7" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB7" t="n">
         <v>32</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>9.199999999999999</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
         <v>110</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2432,7 +2432,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2659,16 +2659,16 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
         <v>1.69</v>
@@ -2677,10 +2677,10 @@
         <v>2.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
         <v>1.11</v>
@@ -2737,22 +2737,22 @@
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO9" t="n">
         <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
         <v>9</v>
@@ -2764,7 +2764,7 @@
         <v>4.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
         <v>8</v>
@@ -2776,7 +2776,7 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
         <v>9.6</v>
@@ -2785,16 +2785,16 @@
         <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
         <v>3.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="n">
         <v>4.9</v>
@@ -2806,13 +2806,13 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
@@ -2824,41 +2824,41 @@
         <v>8.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
         <v>21</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
         <v>12.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>11</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I10" t="n">
         <v>1.37</v>
       </c>
       <c r="J10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K10" t="n">
         <v>7.6</v>
@@ -2919,10 +2919,10 @@
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R10" t="n">
         <v>2.16</v>
@@ -2997,7 +2997,7 @@
         <v>3.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>5.7</v>
@@ -3054,49 +3054,49 @@
         <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
         <v>14</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP10" t="n">
         <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>44</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
         <v>5</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV10" t="n">
         <v>7.8</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX10" t="n">
         <v>16</v>
@@ -3105,14 +3105,14 @@
         <v>6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CA10" t="n">
         <v>4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
         <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.43</v>
@@ -3170,13 +3170,13 @@
         <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
         <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -3191,10 +3191,10 @@
         <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3257,10 +3257,10 @@
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>6.4</v>
@@ -3272,19 +3272,19 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -3293,16 +3293,16 @@
         <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
         <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
         <v>1.65</v>
@@ -3660,7 +3660,7 @@
         <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
@@ -3681,7 +3681,7 @@
         <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="Q13" t="n">
         <v>1.35</v>
@@ -3699,7 +3699,7 @@
         <v>2.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>2.54</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="G14" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I14" t="n">
+      <c r="AZ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP14" t="n">
         <v>10.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="BQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU14" t="n">
         <v>5.2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>420</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
         <v>8.4</v>
       </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA14" t="n">
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA14" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>14</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4183,16 +4183,16 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4413,55 +4413,55 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="G16" t="n">
         <v>9.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="I16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
         <v>1.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="W16" t="n">
         <v>1.12</v>
@@ -4518,97 +4518,97 @@
         <v>85</v>
       </c>
       <c r="AO16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AP16" t="n">
         <v>5</v>
       </c>
-      <c r="AP16" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AQ16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR16" t="n">
         <v>4</v>
       </c>
-      <c r="AR16" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV16" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AW16" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AX16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY16" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5</v>
-      </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BT16" t="n">
         <v>4.6</v>
@@ -4620,7 +4620,7 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4632,11 +4632,11 @@
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
         <v>2.82</v>
@@ -4933,10 +4933,10 @@
         <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
         <v>1.31</v>
@@ -4960,7 +4960,7 @@
         <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
         <v>1.69</v>
@@ -4972,7 +4972,7 @@
         <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -5175,230 +5175,230 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.12</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BT19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>2.58</v>
+        <v>4.8</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
         <v>2.44</v>
@@ -5453,13 +5453,13 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
@@ -5468,7 +5468,7 @@
         <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
         <v>1.78</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -5692,13 +5692,13 @@
         <v>1.99</v>
       </c>
       <c r="I21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J21" t="n">
         <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>1.31</v>
@@ -5707,13 +5707,13 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>1.86</v>
@@ -5725,13 +5725,13 @@
         <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="W21" t="n">
         <v>1.31</v>
@@ -5755,7 +5755,7 @@
         <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -5788,10 +5788,10 @@
         <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.4</v>
@@ -5800,7 +5800,7 @@
         <v>11.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -5809,13 +5809,13 @@
         <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
         <v>17.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AY21" t="n">
         <v>14</v>
@@ -5824,22 +5824,22 @@
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
         <v>11</v>
@@ -5857,7 +5857,7 @@
         <v>5</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM21" t="n">
         <v>9.6</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
         <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.22</v>
@@ -5967,7 +5967,7 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
         <v>1.5</v>
@@ -5982,7 +5982,7 @@
         <v>1.57</v>
       </c>
       <c r="U22" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V22" t="n">
         <v>1.24</v>
@@ -6006,7 +6006,7 @@
         <v>16.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>23</v>
@@ -6045,16 +6045,16 @@
         <v>40</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT22" t="n">
         <v>12.5</v>
@@ -6066,7 +6066,7 @@
         <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -6078,7 +6078,7 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB22" t="n">
         <v>16</v>
@@ -6090,13 +6090,13 @@
         <v>18.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF22" t="n">
         <v>5.7</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH22" t="n">
         <v>4.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
         <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -6215,7 +6215,7 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.23</v>
@@ -6224,16 +6224,16 @@
         <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
         <v>2.34</v>
@@ -6263,7 +6263,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
@@ -6293,13 +6293,13 @@
         <v>85</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>16.5</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU23" t="n">
         <v>8.6</v>
@@ -6326,22 +6326,22 @@
         <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
         <v>38</v>
       </c>
       <c r="BB23" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BE23" t="n">
         <v>34</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -6451,13 +6451,13 @@
         <v>2.22</v>
       </c>
       <c r="H24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I24" t="n">
         <v>3.65</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
         <v>4.2</v>
@@ -6484,7 +6484,7 @@
         <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
         <v>1.61</v>
@@ -6508,7 +6508,7 @@
         <v>29</v>
       </c>
       <c r="AA24" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB24" t="n">
         <v>13.5</v>
@@ -6565,7 +6565,7 @@
         <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
         <v>8.4</v>
@@ -6583,7 +6583,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
         <v>6.6</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>4.9</v>
       </c>
       <c r="K25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.21</v>
@@ -6723,16 +6723,16 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R25" t="n">
         <v>1.76</v>
@@ -6741,13 +6741,13 @@
         <v>2.16</v>
       </c>
       <c r="T25" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U25" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V25" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="W25" t="n">
         <v>1.22</v>
@@ -6759,13 +6759,13 @@
         <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
         <v>22</v>
       </c>
       <c r="AB25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC25" t="n">
         <v>12.5</v>
@@ -6774,7 +6774,7 @@
         <v>10.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
         <v>55</v>
@@ -6786,7 +6786,7 @@
         <v>17.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ25" t="n">
         <v>140</v>
@@ -6795,16 +6795,16 @@
         <v>60</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO25" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AP25" t="n">
         <v>26</v>
@@ -6834,31 +6834,31 @@
         <v>42</v>
       </c>
       <c r="AY25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
         <v>40</v>
       </c>
       <c r="BC25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BD25" t="n">
         <v>42</v>
       </c>
       <c r="BE25" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BF25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH25" t="n">
         <v>5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -6956,22 +6956,22 @@
         <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H26" t="n">
         <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
@@ -6983,22 +6983,22 @@
         <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R26" t="n">
         <v>1.66</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -7007,7 +7007,7 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="Y26" t="n">
         <v>34</v>
@@ -7019,10 +7019,10 @@
         <v>150</v>
       </c>
       <c r="AB26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD26" t="n">
         <v>27</v>
@@ -7031,10 +7031,10 @@
         <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -7061,28 +7061,28 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.3</v>
+        <v>42</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -7091,92 +7091,92 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BF26" t="n">
         <v>5.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.9</v>
+        <v>36</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -7207,16 +7207,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="G27" t="n">
         <v>970</v>
       </c>
       <c r="H27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>1.01</v>
@@ -7252,10 +7252,10 @@
         <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G28" t="n">
         <v>2.14</v>
@@ -7470,7 +7470,7 @@
         <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>3.25</v>
@@ -7485,13 +7485,13 @@
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
         <v>1.46</v>
       </c>
       <c r="P28" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
         <v>2.38</v>
@@ -7530,7 +7530,7 @@
         <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>22</v>
@@ -7569,19 +7569,19 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -7590,7 +7590,7 @@
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AX28" t="n">
         <v>9</v>
@@ -7599,28 +7599,28 @@
         <v>8.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BH28" t="n">
         <v>2.92</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H29" t="n">
         <v>3.3</v>
@@ -7733,10 +7733,10 @@
         <v>3.05</v>
       </c>
       <c r="L29" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M29" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N29" t="n">
         <v>2.3</v>
@@ -7745,7 +7745,7 @@
         <v>1.62</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -7754,7 +7754,7 @@
         <v>1.15</v>
       </c>
       <c r="S29" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
         <v>2.28</v>
@@ -7781,7 +7781,7 @@
         <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC29" t="n">
         <v>8</v>
@@ -7790,7 +7790,7 @@
         <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
         <v>18</v>
@@ -7823,28 +7823,28 @@
         <v>110</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
         <v>16.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT29" t="n">
         <v>3.65</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AV29" t="n">
         <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX29" t="n">
         <v>12</v>
@@ -7853,28 +7853,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF29" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF29" t="n">
-        <v>6</v>
-      </c>
       <c r="BG29" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="n">
         <v>2.5</v>
@@ -7898,7 +7898,7 @@
         <v>5.4</v>
       </c>
       <c r="BO29" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP29" t="n">
         <v>26</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>21</v>
@@ -8492,7 +8492,7 @@
         <v>5.5</v>
       </c>
       <c r="K32" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.32</v>
@@ -8519,10 +8519,10 @@
         <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="U32" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V32" t="n">
         <v>4</v>
@@ -8603,7 +8603,7 @@
         <v>1.86</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="AW32" t="n">
         <v>1.91</v>
@@ -8636,13 +8636,13 @@
         <v>2.1</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -8734,19 +8734,19 @@
         <v>1.85</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H33" t="n">
         <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.3</v>
@@ -8767,19 +8767,19 @@
         <v>1.87</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
         <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U33" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
         <v>2.12</v>
@@ -8788,7 +8788,7 @@
         <v>16</v>
       </c>
       <c r="Y33" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
         <v>36</v>
@@ -8803,7 +8803,7 @@
         <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE33" t="n">
         <v>60</v>
@@ -8812,7 +8812,7 @@
         <v>14</v>
       </c>
       <c r="AG33" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
         <v>19</v>
@@ -8821,7 +8821,7 @@
         <v>60</v>
       </c>
       <c r="AJ33" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK33" t="n">
         <v>19</v>
@@ -8830,13 +8830,13 @@
         <v>34</v>
       </c>
       <c r="AM33" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN33" t="n">
         <v>11.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP33" t="n">
         <v>14</v>
@@ -8845,10 +8845,10 @@
         <v>16.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT33" t="n">
         <v>9.199999999999999</v>
@@ -8860,13 +8860,13 @@
         <v>16</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
         <v>17.5</v>
@@ -8884,13 +8884,13 @@
         <v>30</v>
       </c>
       <c r="BE33" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF33" t="n">
         <v>10</v>
       </c>
       <c r="BG33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH33" t="n">
         <v>3.65</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G34" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H34" t="n">
         <v>4.6</v>
@@ -9012,7 +9012,7 @@
         <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
         <v>2.02</v>
@@ -9021,7 +9021,7 @@
         <v>1.86</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
         <v>3.15</v>
@@ -9030,7 +9030,7 @@
         <v>1.8</v>
       </c>
       <c r="U34" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V34" t="n">
         <v>1.25</v>
@@ -9117,10 +9117,10 @@
         <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
         <v>1.01</v>
@@ -9129,7 +9129,7 @@
         <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
         <v>13.5</v>
@@ -9141,7 +9141,7 @@
         <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
         <v>1.01</v>
@@ -9150,7 +9150,7 @@
         <v>3.7</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.6</v>
@@ -9168,7 +9168,7 @@
         <v>4.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP34" t="n">
         <v>12.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -9242,22 +9242,22 @@
         <v>1.87</v>
       </c>
       <c r="G35" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H35" t="n">
         <v>4.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -9269,25 +9269,25 @@
         <v>1.28</v>
       </c>
       <c r="P35" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
         <v>1.86</v>
       </c>
       <c r="R35" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
         <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U35" t="n">
         <v>2.08</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
         <v>2.02</v>
@@ -9362,13 +9362,13 @@
         <v>7.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV35" t="n">
         <v>13.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
         <v>9.4</v>
@@ -9380,7 +9380,7 @@
         <v>14</v>
       </c>
       <c r="BA35" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
         <v>16.5</v>
@@ -9428,7 +9428,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR35" t="n">
         <v>28</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H36" t="n">
         <v>1.77</v>
@@ -9511,7 +9511,7 @@
         <v>4.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
@@ -9526,13 +9526,13 @@
         <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R36" t="n">
         <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T36" t="n">
         <v>1.9</v>
@@ -9547,10 +9547,10 @@
         <v>1.21</v>
       </c>
       <c r="X36" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z36" t="n">
         <v>11</v>
@@ -9598,7 +9598,7 @@
         <v>110</v>
       </c>
       <c r="AO36" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AP36" t="n">
         <v>10.5</v>
@@ -9607,7 +9607,7 @@
         <v>7.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS36" t="n">
         <v>14</v>
@@ -9622,10 +9622,10 @@
         <v>9</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY36" t="n">
         <v>15</v>
@@ -9634,13 +9634,13 @@
         <v>15</v>
       </c>
       <c r="BA36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD36" t="n">
         <v>10</v>
@@ -9649,10 +9649,10 @@
         <v>10.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH36" t="n">
         <v>3.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -9750,13 +9750,13 @@
         <v>2.34</v>
       </c>
       <c r="G37" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>3.55</v>
@@ -9780,7 +9780,7 @@
         <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R37" t="n">
         <v>1.4</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -10007,19 +10007,19 @@
         <v>2.32</v>
       </c>
       <c r="H38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I38" t="n">
         <v>4.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.6</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M38" t="n">
         <v>1.09</v>
@@ -10031,16 +10031,16 @@
         <v>1.39</v>
       </c>
       <c r="P38" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R38" t="n">
         <v>1.28</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T38" t="n">
         <v>1.89</v>
@@ -10052,49 +10052,49 @@
         <v>1.31</v>
       </c>
       <c r="W38" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X38" t="n">
         <v>14</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA38" t="n">
         <v>100</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE38" t="n">
         <v>65</v>
       </c>
       <c r="AF38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG38" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG38" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH38" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI38" t="n">
         <v>80</v>
       </c>
       <c r="AJ38" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK38" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL38" t="n">
         <v>55</v>
@@ -10103,7 +10103,7 @@
         <v>150</v>
       </c>
       <c r="AN38" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AO38" t="n">
         <v>80</v>
@@ -10118,7 +10118,7 @@
         <v>19.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT38" t="n">
         <v>6.4</v>
@@ -10130,7 +10130,7 @@
         <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX38" t="n">
         <v>9.800000000000001</v>
@@ -10142,7 +10142,7 @@
         <v>14</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB38" t="n">
         <v>21</v>
@@ -10151,70 +10151,70 @@
         <v>19</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF38" t="n">
         <v>15.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.37</v>
+        <v>6.2</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.37</v>
+        <v>13.5</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.37</v>
+        <v>3.75</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.37</v>
+        <v>8</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.37</v>
+        <v>5.3</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="BZ38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -10255,230 +10255,230 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H39" t="n">
         <v>3.05</v>
       </c>
       <c r="I39" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J39" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K39" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
         <v>1.26</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="S39" t="n">
-        <v>1.26</v>
+        <v>2.96</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W39" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH39" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.29</v>
+        <v>5.2</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="BN39" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.29</v>
+        <v>3.8</v>
       </c>
       <c r="BP39" t="n">
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.29</v>
+        <v>7</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.29</v>
+        <v>2.62</v>
       </c>
       <c r="BT39" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.29</v>
+        <v>4.2</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.29</v>
+        <v>7.8</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.29</v>
+        <v>7.8</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -10509,19 +10509,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G40" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H40" t="n">
         <v>4.4</v>
       </c>
       <c r="I40" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K40" t="n">
         <v>4.2</v>
@@ -10551,7 +10551,7 @@
         <v>3.25</v>
       </c>
       <c r="T40" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U40" t="n">
         <v>2.02</v>
@@ -10566,46 +10566,46 @@
         <v>18.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA40" t="n">
         <v>140</v>
       </c>
       <c r="AB40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG40" t="n">
         <v>11</v>
       </c>
-      <c r="AC40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI40" t="n">
         <v>70</v>
       </c>
       <c r="AJ40" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK40" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM40" t="n">
         <v>130</v>
@@ -10614,7 +10614,7 @@
         <v>15</v>
       </c>
       <c r="AO40" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP40" t="n">
         <v>11</v>
@@ -10623,25 +10623,25 @@
         <v>12</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT40" t="n">
         <v>6.6</v>
       </c>
       <c r="AU40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW40" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV40" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AX40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY40" t="n">
         <v>7.6</v>
@@ -10650,31 +10650,31 @@
         <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB40" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH40" t="n">
         <v>3.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="BJ40" t="n">
         <v>10.5</v>
@@ -10686,7 +10686,7 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BN40" t="n">
         <v>4.7</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -10766,217 +10766,217 @@
         <v>1.31</v>
       </c>
       <c r="G41" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="H41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT41" t="n">
         <v>6.8</v>
       </c>
-      <c r="I41" t="n">
-        <v>110</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="AU41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH41" t="n">
         <v>4.4</v>
       </c>
-      <c r="K41" t="n">
-        <v>11</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="BI41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ41" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC41" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ41" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
         <v>2.04</v>
@@ -11131,7 +11131,7 @@
         <v>5.2</v>
       </c>
       <c r="AR42" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS42" t="n">
         <v>7.6</v>
@@ -11161,7 +11161,7 @@
         <v>7.6</v>
       </c>
       <c r="BB42" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BC42" t="n">
         <v>20</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H43" t="n">
         <v>3.3</v>
@@ -11295,7 +11295,7 @@
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O43" t="n">
         <v>1.4</v>
@@ -11334,7 +11334,7 @@
         <v>25</v>
       </c>
       <c r="AA43" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB43" t="n">
         <v>9.6</v>
@@ -11361,7 +11361,7 @@
         <v>60</v>
       </c>
       <c r="AJ43" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK43" t="n">
         <v>29</v>
@@ -11388,7 +11388,7 @@
         <v>20</v>
       </c>
       <c r="AS43" t="n">
-        <v>44</v>
+        <v>7.4</v>
       </c>
       <c r="AT43" t="n">
         <v>8</v>
@@ -11400,7 +11400,7 @@
         <v>11.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AX43" t="n">
         <v>13</v>
@@ -11412,43 +11412,43 @@
         <v>15</v>
       </c>
       <c r="BA43" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD43" t="n">
         <v>30</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF43" t="n">
         <v>20</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BJ43" t="n">
         <v>10.5</v>
       </c>
       <c r="BK43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN43" t="n">
         <v>5.4</v>
@@ -11457,44 +11457,44 @@
         <v>4</v>
       </c>
       <c r="BP43" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ43" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT43" t="n">
         <v>6.8</v>
       </c>
       <c r="BU43" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N44" t="n">
         <v>1.05</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -11800,7 +11800,7 @@
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N45" t="n">
         <v>1.05</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
         <v>1.13</v>
       </c>
       <c r="S46" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.63</v>
       </c>
       <c r="G47" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H47" t="n">
         <v>6.4</v>
@@ -12299,10 +12299,10 @@
         <v>7.6</v>
       </c>
       <c r="J47" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.45</v>
@@ -12338,7 +12338,7 @@
         <v>1.15</v>
       </c>
       <c r="W47" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X47" t="n">
         <v>970</v>
@@ -12359,7 +12359,7 @@
         <v>970</v>
       </c>
       <c r="AD47" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE47" t="n">
         <v>1000</v>
@@ -12383,7 +12383,7 @@
         <v>24</v>
       </c>
       <c r="AL47" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM47" t="n">
         <v>1000</v>
@@ -12401,13 +12401,13 @@
         <v>4.5</v>
       </c>
       <c r="AR47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT47" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.25</v>
       </c>
       <c r="AU47" t="n">
         <v>3.5</v>
@@ -12416,37 +12416,37 @@
         <v>3.15</v>
       </c>
       <c r="AW47" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AX47" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AY47" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BA47" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BB47" t="n">
         <v>4.4</v>
       </c>
       <c r="BC47" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD47" t="n">
         <v>3.3</v>
       </c>
       <c r="BE47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G48" t="n">
         <v>3.3</v>
@@ -12550,10 +12550,10 @@
         <v>2.4</v>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J48" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K48" t="n">
         <v>3.8</v>
@@ -12574,7 +12574,7 @@
         <v>1.97</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R48" t="n">
         <v>1.38</v>
@@ -12610,7 +12610,7 @@
         <v>13.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD48" t="n">
         <v>12</v>
@@ -12619,31 +12619,31 @@
         <v>27</v>
       </c>
       <c r="AF48" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG48" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH48" t="n">
         <v>17.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ48" t="n">
         <v>55</v>
       </c>
       <c r="AK48" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL48" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM48" t="n">
         <v>90</v>
       </c>
       <c r="AN48" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO48" t="n">
         <v>21</v>
@@ -12670,7 +12670,7 @@
         <v>10</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AX48" t="n">
         <v>1.03</v>
@@ -12691,7 +12691,7 @@
         <v>1.01</v>
       </c>
       <c r="BD48" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -12795,22 +12795,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G49" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H49" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K49" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -13049,16 +13049,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G50" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H50" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I50" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J50" t="n">
         <v>1.03</v>
@@ -13073,13 +13073,13 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O50" t="n">
         <v>1.28</v>
       </c>
       <c r="P50" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q50" t="n">
         <v>1.28</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>3.3</v>
@@ -13333,7 +13333,7 @@
         <v>1.44</v>
       </c>
       <c r="P51" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q51" t="n">
         <v>2.3</v>
@@ -13369,7 +13369,7 @@
         <v>150</v>
       </c>
       <c r="AB51" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC51" t="n">
         <v>9.4</v>
@@ -13417,10 +13417,10 @@
         <v>11.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT51" t="n">
         <v>6.4</v>
@@ -13432,7 +13432,7 @@
         <v>16.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX51" t="n">
         <v>9.4</v>
@@ -13441,28 +13441,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB51" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BC51" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF51" t="n">
         <v>14</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH51" t="n">
         <v>3.1</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
         <v>3.75</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
         <v>1.07</v>
@@ -13587,22 +13587,22 @@
         <v>1.34</v>
       </c>
       <c r="P52" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R52" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S52" t="n">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="T52" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="U52" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="V52" t="n">
         <v>1.36</v>
@@ -13611,176 +13611,176 @@
         <v>1.74</v>
       </c>
       <c r="X52" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC52" t="n">
         <v>9.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG52" t="n">
         <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN52" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP52" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT52" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV52" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ52" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -866,7 +866,7 @@
         <v>4.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -875,7 +875,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
@@ -998,7 +998,7 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>4</v>
@@ -1013,7 +1013,7 @@
         <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
         <v>4.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
         <v>3.65</v>
@@ -1120,10 +1120,10 @@
         <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.45</v>
@@ -1159,7 +1159,7 @@
         <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="W3" t="n">
         <v>1.38</v>
@@ -1201,7 +1201,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
         <v>50</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -1365,100 +1365,100 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
         <v>1.72</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="X4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" t="n">
         <v>22</v>
       </c>
-      <c r="Y4" t="n">
-        <v>23</v>
-      </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
         <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>70</v>
       </c>
       <c r="AJ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK4" t="n">
         <v>22</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1467,16 +1467,16 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
         <v>4.5</v>
@@ -1488,31 +1488,31 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
         <v>4.4</v>
@@ -1521,19 +1521,19 @@
         <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>5.2</v>
@@ -1545,50 +1545,50 @@
         <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
         <v>2.92</v>
@@ -1643,206 +1643,206 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>1.69</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>1.08</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>1.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>1.08</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>1.08</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>1.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.6</v>
+        <v>1.08</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>1.08</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>1.08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>1.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>1.08</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>1.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>1.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>1.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>1.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
-        <v>19</v>
+        <v>1.08</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.6</v>
@@ -1948,7 +1948,7 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
         <v>970</v>
@@ -1993,13 +1993,13 @@
         <v>8.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>8.199999999999999</v>
@@ -2011,7 +2011,7 @@
         <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>8.6</v>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
@@ -2074,7 +2074,7 @@
         <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
         <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2157,10 +2157,10 @@
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
@@ -2169,40 +2169,40 @@
         <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
         <v>14.5</v>
@@ -2211,16 +2211,16 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
         <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -2232,43 +2232,43 @@
         <v>29</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
         <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="AT7" t="n">
         <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
         <v>29</v>
@@ -2277,16 +2277,16 @@
         <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -2638,227 +2638,227 @@
         <v>1.13</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="H9" t="n">
+        <v>21</v>
+      </c>
+      <c r="I9" t="n">
+        <v>36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>340</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>590</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG9" t="n">
         <v>15</v>
       </c>
-      <c r="I9" t="n">
-        <v>110</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
         <v>1.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>1.07</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -3412,10 +3412,10 @@
         <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
@@ -3424,13 +3424,13 @@
         <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -3439,10 +3439,10 @@
         <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
@@ -3451,7 +3451,7 @@
         <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
         <v>14</v>
@@ -3502,7 +3502,7 @@
         <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AP12" t="n">
         <v>8.800000000000001</v>
@@ -3526,7 +3526,7 @@
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -3550,25 +3550,25 @@
         <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
         <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3589,10 +3589,10 @@
         <v>6.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
         <v>7.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -3675,16 +3675,16 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R13" t="n">
         <v>1.69</v>
@@ -3738,7 +3738,7 @@
         <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
         <v>14.5</v>
@@ -3747,28 +3747,28 @@
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AO13" t="n">
         <v>130</v>
       </c>
       <c r="AP13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3777,10 +3777,10 @@
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3792,25 +3792,25 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC13" t="n">
         <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
         <v>3.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="n">
         <v>4.9</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.18</v>
@@ -3941,7 +3941,7 @@
         <v>1.39</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S14" t="n">
         <v>1.96</v>
@@ -3953,10 +3953,10 @@
         <v>2.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
         <v>46</v>
@@ -3971,7 +3971,7 @@
         <v>85</v>
       </c>
       <c r="AB14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
         <v>15</v>
@@ -3995,7 +3995,7 @@
         <v>38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
         <v>18</v>
@@ -4013,25 +4013,25 @@
         <v>25</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>4.5</v>
@@ -4046,16 +4046,16 @@
         <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BE14" t="n">
         <v>4.6</v>
@@ -4064,13 +4064,13 @@
         <v>4.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="n">
         <v>5.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>110</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.26</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
         <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>1.26</v>
+        <v>2.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="O16" t="n">
         <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4461,10 +4461,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -4924,13 +4924,13 @@
         <v>8.4</v>
       </c>
       <c r="G18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J18" t="n">
         <v>6.4</v>
@@ -4957,10 +4957,10 @@
         <v>1.26</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T18" t="n">
         <v>1.55</v>
@@ -4969,7 +4969,7 @@
         <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
@@ -5002,7 +5002,7 @@
         <v>120</v>
       </c>
       <c r="AG18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AH18" t="n">
         <v>26</v>
@@ -5014,7 +5014,7 @@
         <v>290</v>
       </c>
       <c r="AK18" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL18" t="n">
         <v>80</v>
@@ -5026,13 +5026,13 @@
         <v>70</v>
       </c>
       <c r="AO18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
@@ -5041,10 +5041,10 @@
         <v>10.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
@@ -5053,40 +5053,40 @@
         <v>10</v>
       </c>
       <c r="AX18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD18" t="n">
         <v>6</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BH18" t="n">
         <v>7</v>
       </c>
       <c r="BI18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5140,11 +5140,11 @@
         <v>6.8</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="G19" t="n">
-        <v>110</v>
+        <v>2.68</v>
       </c>
       <c r="H19" t="n">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="I19" t="n">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,22 +5199,22 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.05</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
         <v>1.09</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="S19" t="n">
-        <v>1.09</v>
+        <v>1.86</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5223,10 +5223,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -5453,34 +5453,34 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.11</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>1.92</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -5707,19 +5707,19 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
         <v>1.09</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
         <v>1.09</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="S21" t="n">
         <v>1.09</v>
@@ -5731,10 +5731,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -5937,46 +5937,46 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O22" t="n">
         <v>1.02</v>
-      </c>
-      <c r="G22" t="n">
-        <v>110</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I22" t="n">
-        <v>110</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K22" t="n">
-        <v>950</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.01</v>
       </c>
       <c r="P22" t="n">
         <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -5985,10 +5985,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -6445,64 +6445,64 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>1.15</v>
       </c>
       <c r="H24" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O24" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -6511,43 +6511,43 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -6601,7 +6601,7 @@
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BG24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4.8</v>
@@ -6723,43 +6723,43 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U25" t="n">
         <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -6771,22 +6771,22 @@
         <v>970</v>
       </c>
       <c r="AD25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AG25" t="n">
         <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
         <v>970</v>
@@ -6795,7 +6795,7 @@
         <v>970</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -6807,106 +6807,106 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK25" t="n">
         <v>5</v>
       </c>
-      <c r="AS25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD25" t="n">
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU25" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>5</v>
-      </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6915,14 +6915,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA25" t="n">
         <v>6.2</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
         <v>950</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="O29" t="n">
         <v>1.06</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K30" t="n">
         <v>950</v>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="O30" t="n">
         <v>1.1</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -8226,49 +8226,49 @@
         <v>6.8</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I31" t="n">
         <v>1.45</v>
       </c>
       <c r="J31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K31" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M31" t="n">
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R31" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S31" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="T31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U31" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V31" t="n">
         <v>3.2</v>
@@ -8277,10 +8277,10 @@
         <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y31" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z31" t="n">
         <v>970</v>
@@ -8289,7 +8289,7 @@
         <v>970</v>
       </c>
       <c r="AB31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC31" t="n">
         <v>16.5</v>
@@ -8301,7 +8301,7 @@
         <v>970</v>
       </c>
       <c r="AF31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AG31" t="n">
         <v>36</v>
@@ -8331,7 +8331,7 @@
         <v>4.7</v>
       </c>
       <c r="AP31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ31" t="n">
         <v>11</v>
@@ -8343,7 +8343,7 @@
         <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU31" t="n">
         <v>11</v>
@@ -8355,31 +8355,31 @@
         <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ31" t="n">
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC31" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BD31" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD31" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG31" t="n">
         <v>3.45</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -8477,193 +8477,193 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD32" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AE32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH32" t="n">
         <v>19.5</v>
       </c>
-      <c r="Z32" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC32" t="n">
+      <c r="AI32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
+      <c r="AQ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR32" t="n">
         <v>18</v>
       </c>
-      <c r="AG32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.68</v>
-      </c>
       <c r="AS32" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.26</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.56</v>
+        <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.88</v>
+        <v>6.6</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.48</v>
+        <v>10</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.58</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.88</v>
+        <v>6.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.68</v>
+        <v>20</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.64</v>
+        <v>19.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.88</v>
+        <v>6.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.48</v>
+        <v>13</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.78</v>
+        <v>6.6</v>
       </c>
       <c r="BH32" t="n">
         <v>3.45</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ32" t="n">
         <v>10.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.52</v>
+        <v>9</v>
       </c>
       <c r="BN32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BP32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ32" t="n">
         <v>6.2</v>
@@ -8672,35 +8672,35 @@
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT32" t="n">
         <v>7.4</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
         <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -8758,7 +8758,7 @@
         <v>3.75</v>
       </c>
       <c r="O33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P33" t="n">
         <v>1.98</v>
@@ -8794,10 +8794,10 @@
         <v>70</v>
       </c>
       <c r="AA33" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC33" t="n">
         <v>11</v>
@@ -8809,7 +8809,7 @@
         <v>140</v>
       </c>
       <c r="AF33" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
@@ -8836,7 +8836,7 @@
         <v>9</v>
       </c>
       <c r="AO33" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP33" t="n">
         <v>11.5</v>
@@ -8845,10 +8845,10 @@
         <v>19</v>
       </c>
       <c r="AR33" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
@@ -8857,10 +8857,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
@@ -8869,10 +8869,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB33" t="n">
         <v>11</v>
@@ -8881,16 +8881,16 @@
         <v>14.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF33" t="n">
         <v>7</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="n">
         <v>3.7</v>
@@ -8914,7 +8914,7 @@
         <v>4.1</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP33" t="n">
         <v>10.5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="K34" t="n">
         <v>950</v>
@@ -9024,7 +9024,7 @@
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9033,7 +9033,7 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G36" t="n">
         <v>1.64</v>
@@ -9508,7 +9508,7 @@
         <v>4.7</v>
       </c>
       <c r="K36" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
         <v>1.22</v>
@@ -9523,7 +9523,7 @@
         <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q36" t="n">
         <v>1.54</v>
@@ -9538,7 +9538,7 @@
         <v>1.64</v>
       </c>
       <c r="U36" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -9547,7 +9547,7 @@
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y36" t="n">
         <v>34</v>
@@ -9562,16 +9562,16 @@
         <v>15</v>
       </c>
       <c r="AC36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD36" t="n">
         <v>27</v>
       </c>
       <c r="AE36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF36" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -9595,13 +9595,13 @@
         <v>85</v>
       </c>
       <c r="AN36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ36" t="n">
         <v>18</v>
@@ -9613,7 +9613,7 @@
         <v>42</v>
       </c>
       <c r="AT36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU36" t="n">
         <v>10</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -9753,25 +9753,25 @@
         <v>4.3</v>
       </c>
       <c r="H37" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I37" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L37" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
         <v>1.28</v>
@@ -9780,7 +9780,7 @@
         <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R37" t="n">
         <v>1.43</v>
@@ -9789,13 +9789,13 @@
         <v>3.15</v>
       </c>
       <c r="T37" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U37" t="n">
         <v>2.22</v>
       </c>
       <c r="V37" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
         <v>1.3</v>
@@ -9855,7 +9855,7 @@
         <v>13</v>
       </c>
       <c r="AP37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>9.4</v>
@@ -9912,19 +9912,19 @@
         <v>3.75</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL37" t="n">
         <v>120</v>
       </c>
       <c r="BM37" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN37" t="n">
         <v>8</v>
@@ -9936,13 +9936,13 @@
         <v>36</v>
       </c>
       <c r="BQ37" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR37" t="n">
         <v>44</v>
       </c>
       <c r="BS37" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT37" t="n">
         <v>5</v>
@@ -9951,16 +9951,16 @@
         <v>3.7</v>
       </c>
       <c r="BV37" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW37" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -10007,10 +10007,10 @@
         <v>1.73</v>
       </c>
       <c r="H38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>4.5</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
         <v>2.76</v>
       </c>
       <c r="T39" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U39" t="n">
         <v>2.34</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -10524,37 +10524,37 @@
         <v>3.8</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M40" t="n">
         <v>1.04</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O40" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P40" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R40" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="T40" t="n">
         <v>1.61</v>
       </c>
       <c r="U40" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V40" t="n">
         <v>1.33</v>
@@ -10563,7 +10563,7 @@
         <v>1.7</v>
       </c>
       <c r="X40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y40" t="n">
         <v>18.5</v>
@@ -10578,7 +10578,7 @@
         <v>13.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD40" t="n">
         <v>16</v>
@@ -10626,19 +10626,19 @@
         <v>20</v>
       </c>
       <c r="AS40" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT40" t="n">
         <v>11</v>
       </c>
       <c r="AU40" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX40" t="n">
         <v>12</v>
@@ -10650,7 +10650,7 @@
         <v>13</v>
       </c>
       <c r="BA40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB40" t="n">
         <v>20</v>
@@ -10659,10 +10659,10 @@
         <v>15.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF40" t="n">
         <v>10</v>
@@ -10671,22 +10671,22 @@
         <v>20</v>
       </c>
       <c r="BH40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK40" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN40" t="n">
         <v>5.5</v>
@@ -10698,16 +10698,16 @@
         <v>15</v>
       </c>
       <c r="BQ40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR40" t="n">
         <v>25</v>
       </c>
       <c r="BS40" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU40" t="n">
         <v>5.5</v>
@@ -10716,23 +10716,23 @@
         <v>26</v>
       </c>
       <c r="BW40" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX40" t="n">
         <v>32</v>
       </c>
       <c r="BY40" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ40" t="n">
         <v>18.5</v>
       </c>
       <c r="CA40" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
         <v>3.45</v>
       </c>
       <c r="K41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.42</v>
@@ -10787,7 +10787,7 @@
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
@@ -10796,13 +10796,13 @@
         <v>1.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
         <v>1.35</v>
       </c>
       <c r="S41" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
         <v>1.78</v>
@@ -10814,7 +10814,7 @@
         <v>1.54</v>
       </c>
       <c r="W41" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X41" t="n">
         <v>16</v>
@@ -10832,7 +10832,7 @@
         <v>14</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
         <v>13.5</v>
@@ -10880,7 +10880,7 @@
         <v>12.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT41" t="n">
         <v>10.5</v>
@@ -10904,22 +10904,22 @@
         <v>13</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG41" t="n">
         <v>17</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
         <v>6.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P42" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         <v>1.79</v>
       </c>
       <c r="S42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T42" t="n">
         <v>1.57</v>
@@ -11074,10 +11074,10 @@
         <v>40</v>
       </c>
       <c r="Y42" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z42" t="n">
         <v>16</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>14.5</v>
       </c>
       <c r="AA42" t="n">
         <v>22</v>
@@ -11140,7 +11140,7 @@
         <v>26</v>
       </c>
       <c r="AU42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV42" t="n">
         <v>9.4</v>
@@ -11173,7 +11173,7 @@
         <v>30</v>
       </c>
       <c r="BF42" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BG42" t="n">
         <v>5.3</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -11271,58 +11271,58 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G43" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H43" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I43" t="n">
         <v>4.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M43" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="O43" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="P43" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q43" t="n">
         <v>2.24</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T43" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="U43" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V43" t="n">
         <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11361,13 +11361,13 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK43" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AL43" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM43" t="n">
         <v>1000</v>
@@ -11379,122 +11379,122 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AR43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS43" t="n">
         <v>1.37</v>
       </c>
-      <c r="AS43" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AT43" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.22</v>
+        <v>7.2</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC43" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BF43" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="BH43" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BJ43" t="n">
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.09</v>
+        <v>5.8</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.08</v>
+        <v>3.6</v>
       </c>
       <c r="BN43" t="n">
         <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.19</v>
+        <v>3.35</v>
       </c>
       <c r="BT43" t="n">
         <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.19</v>
+        <v>3.3</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.18</v>
+        <v>3.35</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
         <v>1.17</v>
       </c>
       <c r="R44" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S44" t="n">
         <v>1.17</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -11803,13 +11803,13 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
       </c>
       <c r="P45" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" t="n">
         <v>1.3</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H46" t="n">
         <v>4.3</v>
@@ -12084,7 +12084,7 @@
         <v>1.26</v>
       </c>
       <c r="W46" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="X46" t="n">
         <v>10.5</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G47" t="n">
         <v>2.86</v>
@@ -12296,7 +12296,7 @@
         <v>3.3</v>
       </c>
       <c r="I47" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J47" t="n">
         <v>2.76</v>
@@ -12335,7 +12335,7 @@
         <v>1.67</v>
       </c>
       <c r="V47" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W47" t="n">
         <v>1.53</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -12544,55 +12544,55 @@
         <v>3.7</v>
       </c>
       <c r="G48" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="I48" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K48" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L48" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M48" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N48" t="n">
         <v>4.1</v>
       </c>
       <c r="O48" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P48" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U48" t="n">
         <v>2.22</v>
       </c>
-      <c r="Q48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.24</v>
-      </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="W48" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -12604,10 +12604,10 @@
         <v>970</v>
       </c>
       <c r="AA48" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB48" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC48" t="n">
         <v>970</v>
@@ -12616,19 +12616,19 @@
         <v>970</v>
       </c>
       <c r="AE48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF48" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH48" t="n">
         <v>22</v>
       </c>
       <c r="AI48" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ48" t="n">
         <v>1000</v>
@@ -12637,10 +12637,10 @@
         <v>60</v>
       </c>
       <c r="AL48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM48" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN48" t="n">
         <v>1000</v>
@@ -12649,65 +12649,65 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR48" t="n">
         <v>3.6</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AT48" t="n">
         <v>3.9</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AW48" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX48" t="n">
-        <v>2.94</v>
+        <v>2.52</v>
       </c>
       <c r="AY48" t="n">
         <v>3.85</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="BB48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BC48" t="n">
         <v>2.56</v>
       </c>
-      <c r="BC48" t="n">
-        <v>2.98</v>
-      </c>
       <c r="BD48" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BG48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI48" t="n">
         <v>3.1</v>
       </c>
-      <c r="BH48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI48" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
@@ -12724,7 +12724,7 @@
         <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
         <v>21</v>
@@ -12810,7 +12810,7 @@
         <v>5.4</v>
       </c>
       <c r="K49" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L49" t="n">
         <v>1.28</v>
@@ -12819,7 +12819,7 @@
         <v>1.06</v>
       </c>
       <c r="N49" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O49" t="n">
         <v>1.25</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <v>3.85</v>
       </c>
       <c r="L50" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
         <v>1.07</v>
@@ -13094,7 +13094,7 @@
         <v>1.71</v>
       </c>
       <c r="U50" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V50" t="n">
         <v>1.42</v>
@@ -13196,7 +13196,7 @@
         <v>1.03</v>
       </c>
       <c r="BC50" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -13303,22 +13303,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="G51" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="H51" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K51" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L51" t="n">
         <v>1.3</v>
@@ -13336,197 +13336,197 @@
         <v>2.12</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R51" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
         <v>3.1</v>
       </c>
       <c r="T51" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U51" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V51" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W51" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="X51" t="n">
         <v>16.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z51" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA51" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB51" t="n">
         <v>11.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE51" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF51" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG51" t="n">
         <v>11</v>
       </c>
       <c r="AH51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI51" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ51" t="n">
         <v>970</v>
       </c>
       <c r="AK51" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL51" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM51" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO51" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP51" t="n">
         <v>14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AR51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS51" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AT51" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU51" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV51" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW51" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AX51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY51" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ51" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BB51" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC51" t="n">
         <v>17</v>
       </c>
       <c r="BD51" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE51" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BH51" t="n">
         <v>3.7</v>
       </c>
       <c r="BI51" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ51" t="n">
         <v>9.6</v>
       </c>
       <c r="BK51" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN51" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO51" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP51" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ51" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW51" t="n">
         <v>10</v>
       </c>
-      <c r="BT51" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW51" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -13557,19 +13557,19 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H52" t="n">
         <v>4.1</v>
       </c>
       <c r="I52" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K52" t="n">
         <v>4.1</v>
@@ -13593,7 +13593,7 @@
         <v>1.86</v>
       </c>
       <c r="R52" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
         <v>3.2</v>
@@ -13605,7 +13605,7 @@
         <v>2.08</v>
       </c>
       <c r="V52" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W52" t="n">
         <v>2</v>
@@ -13716,7 +13716,7 @@
         <v>10.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH52" t="n">
         <v>3.7</v>
@@ -13740,7 +13740,7 @@
         <v>4.8</v>
       </c>
       <c r="BO52" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP52" t="n">
         <v>13.5</v>
@@ -13758,7 +13758,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU52" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G53" t="n">
         <v>5.7</v>
@@ -13910,7 +13910,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN53" t="n">
         <v>110</v>
@@ -13931,7 +13931,7 @@
         <v>7.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU53" t="n">
         <v>7.8</v>
@@ -13949,7 +13949,7 @@
         <v>15</v>
       </c>
       <c r="AZ53" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA53" t="n">
         <v>27</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -14065,13 +14065,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G54" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I54" t="n">
         <v>3.3</v>
@@ -14095,10 +14095,10 @@
         <v>1.29</v>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R54" t="n">
         <v>1.41</v>
@@ -14113,10 +14113,10 @@
         <v>2.26</v>
       </c>
       <c r="V54" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X54" t="n">
         <v>18.5</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
         <v>3.7</v>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>3.25</v>
@@ -14349,10 +14349,10 @@
         <v>1.39</v>
       </c>
       <c r="P55" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="R55" t="n">
         <v>1.28</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -14576,19 +14576,19 @@
         <v>1.81</v>
       </c>
       <c r="G56" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H56" t="n">
         <v>4.6</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K56" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L56" t="n">
         <v>1.3</v>
@@ -14603,7 +14603,7 @@
         <v>1.29</v>
       </c>
       <c r="P56" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q56" t="n">
         <v>1.86</v>
@@ -14621,10 +14621,10 @@
         <v>2.18</v>
       </c>
       <c r="V56" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W56" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X56" t="n">
         <v>20</v>
@@ -14687,13 +14687,13 @@
         <v>13</v>
       </c>
       <c r="AR56" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS56" t="n">
         <v>5.1</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AU56" t="n">
         <v>8</v>
@@ -14717,7 +14717,7 @@
         <v>5</v>
       </c>
       <c r="BB56" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC56" t="n">
         <v>13.5</v>
@@ -14729,7 +14729,7 @@
         <v>5.1</v>
       </c>
       <c r="BF56" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG56" t="n">
         <v>4.9</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G57" t="n">
         <v>1.97</v>
@@ -14836,7 +14836,7 @@
         <v>4.4</v>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>3.65</v>
@@ -14845,28 +14845,28 @@
         <v>4.2</v>
       </c>
       <c r="L57" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M57" t="n">
         <v>1.06</v>
       </c>
       <c r="N57" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O57" t="n">
         <v>1.31</v>
       </c>
       <c r="P57" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q57" t="n">
         <v>1.87</v>
       </c>
       <c r="R57" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T57" t="n">
         <v>1.81</v>
@@ -14899,13 +14899,13 @@
         <v>9</v>
       </c>
       <c r="AD57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE57" t="n">
         <v>65</v>
       </c>
       <c r="AF57" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG57" t="n">
         <v>11</v>
@@ -14944,19 +14944,19 @@
         <v>23</v>
       </c>
       <c r="AS57" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT57" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>6.6</v>
       </c>
       <c r="AU57" t="n">
         <v>6.4</v>
       </c>
       <c r="AV57" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW57" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX57" t="n">
         <v>8.6</v>
@@ -14968,7 +14968,7 @@
         <v>14</v>
       </c>
       <c r="BA57" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB57" t="n">
         <v>17.5</v>
@@ -14980,13 +14980,13 @@
         <v>26</v>
       </c>
       <c r="BE57" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF57" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG57" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH57" t="n">
         <v>3.6</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G58" t="n">
         <v>1.35</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -15347,10 +15347,10 @@
         <v>3.75</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K59" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L59" t="n">
         <v>1.44</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -15592,16 +15592,16 @@
         <v>2.26</v>
       </c>
       <c r="G60" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I60" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K60" t="n">
         <v>4.1</v>
@@ -15616,13 +15616,13 @@
         <v>4</v>
       </c>
       <c r="O60" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P60" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R60" t="n">
         <v>1.41</v>
@@ -15631,16 +15631,16 @@
         <v>2.96</v>
       </c>
       <c r="T60" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U60" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V60" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W60" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X60" t="n">
         <v>20</v>
@@ -15652,10 +15652,10 @@
         <v>27</v>
       </c>
       <c r="AA60" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB60" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC60" t="n">
         <v>9.800000000000001</v>
@@ -15670,7 +15670,7 @@
         <v>970</v>
       </c>
       <c r="AG60" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH60" t="n">
         <v>970</v>
@@ -15679,13 +15679,13 @@
         <v>48</v>
       </c>
       <c r="AJ60" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK60" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL60" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM60" t="n">
         <v>90</v>
@@ -15694,61 +15694,61 @@
         <v>970</v>
       </c>
       <c r="AO60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP60" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT60" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU60" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV60" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX60" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY60" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ60" t="n">
         <v>12.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB60" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC60" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE60" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF60" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG60" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -15843,160 +15843,160 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="G61" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="H61" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="I61" t="n">
-        <v>970</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="K61" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M61" t="n">
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P61" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="R61" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="S61" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="T61" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U61" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="V61" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="W61" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X61" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y61" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z61" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA61" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB61" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC61" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD61" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE61" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF61" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG61" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI61" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK61" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL61" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM61" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN61" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO61" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS61" t="n">
         <v>1.03</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF61" t="n">
         <v>1.01</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G62" t="n">
         <v>2.48</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BN65" t="n">
         <v>1000</v>
@@ -17054,7 +17054,7 @@
         <v>1000</v>
       </c>
       <c r="BS65" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BT65" t="n">
         <v>1000</v>
@@ -17066,23 +17066,23 @@
         <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BX65" t="n">
         <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BZ65" t="n">
         <v>1000</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -17278,65 +17278,65 @@
         <v>1000</v>
       </c>
       <c r="BI66" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BJ66" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK66" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BL66" t="n">
         <v>1000</v>
       </c>
       <c r="BM66" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BN66" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO66" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP66" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ66" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BR66" t="n">
         <v>1000</v>
       </c>
       <c r="BS66" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BT66" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU66" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BV66" t="n">
         <v>1000</v>
       </c>
       <c r="BW66" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BX66" t="n">
         <v>1000</v>
       </c>
       <c r="BY66" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BZ66" t="n">
         <v>1000</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -17621,22 +17621,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="H68" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K68" t="n">
         <v>3.5</v>
-      </c>
-      <c r="I68" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J68" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>3.25</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -17654,7 +17654,7 @@
         <v>1.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -17875,112 +17875,112 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.17</v>
+        <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>970</v>
+        <v>4.3</v>
       </c>
       <c r="H69" t="n">
-        <v>1.17</v>
+        <v>2.1</v>
       </c>
       <c r="I69" t="n">
-        <v>970</v>
+        <v>2.36</v>
       </c>
       <c r="J69" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
       </c>
       <c r="M69" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N69" t="n">
-        <v>1.33</v>
+        <v>3.35</v>
       </c>
       <c r="O69" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P69" t="n">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="R69" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S69" t="n">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U69" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W69" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X69" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA69" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB69" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC69" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD69" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE69" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF69" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG69" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH69" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI69" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ69" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK69" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL69" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM69" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN69" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO69" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP69" t="n">
         <v>1.03</v>
@@ -18034,7 +18034,7 @@
         <v>1.01</v>
       </c>
       <c r="BG69" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH69" t="n">
         <v>1000</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18144,7 @@
         <v>3.25</v>
       </c>
       <c r="K70" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L70" t="n">
         <v>1.41</v>
@@ -18162,10 +18162,10 @@
         <v>1.66</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R70" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S70" t="n">
         <v>4.3</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
         <v>2.24</v>
       </c>
       <c r="G71" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H71" t="n">
         <v>3.25</v>
@@ -18416,7 +18416,7 @@
         <v>1.88</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
         <v>1.34</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-28 10:43:26</t>
+          <t>2026-05-28 13:03:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -902,13 +902,13 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -917,22 +917,22 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -941,19 +941,19 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>170</v>
@@ -965,70 +965,70 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AZ2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BA2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
         <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,50 +1037,50 @@
         <v>130</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
         <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>9</v>
       </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
         <v>2.66</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.45</v>
@@ -1159,7 +1159,7 @@
         <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.38</v>
@@ -1171,7 +1171,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
         <v>85</v>
@@ -1183,43 +1183,43 @@
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>7.2</v>
@@ -1228,7 +1228,7 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
         <v>9</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1249,28 +1249,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG3" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.6</v>
       </c>
       <c r="BH3" t="n">
         <v>2.96</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
@@ -1377,13 +1377,13 @@
         <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1395,7 +1395,7 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
         <v>1.75</v>
@@ -1422,7 +1422,7 @@
         <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
         <v>40</v>
@@ -1437,22 +1437,22 @@
         <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ4" t="n">
         <v>24</v>
@@ -1461,10 +1461,10 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
         <v>12.5</v>
@@ -1473,70 +1473,70 @@
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>9.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC4" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC4" t="n">
-        <v>14</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
         <v>8.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>20</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1619,127 +1619,127 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.66</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>25</v>
       </c>
-      <c r="Y5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>27</v>
-      </c>
       <c r="AA5" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
@@ -1748,10 +1748,10 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
@@ -1760,46 +1760,46 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
         <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO5" t="n">
         <v>5</v>
@@ -1808,16 +1808,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
         <v>5.1</v>
@@ -1826,23 +1826,23 @@
         <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="CA5" t="n">
         <v>9.4</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>8</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
         <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
         <v>1.55</v>
@@ -1924,7 +1924,7 @@
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
         <v>7.8</v>
@@ -1948,7 +1948,7 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
         <v>26</v>
@@ -1957,7 +1957,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
         <v>240</v>
@@ -1969,16 +1969,16 @@
         <v>48</v>
       </c>
       <c r="AL6" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
         <v>60</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>4.4</v>
@@ -1987,10 +1987,10 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -2002,7 +2002,7 @@
         <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -2014,25 +2014,25 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC6" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.58</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2160,7 +2160,7 @@
         <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
         <v>1.28</v>
@@ -2175,10 +2175,10 @@
         <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
         <v>12</v>
@@ -2187,13 +2187,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
@@ -2205,7 +2205,7 @@
         <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
         <v>38</v>
@@ -2229,7 +2229,7 @@
         <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
         <v>40</v>
@@ -2241,10 +2241,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -2256,7 +2256,7 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX7" t="n">
         <v>16</v>
@@ -2265,10 +2265,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB7" t="n">
         <v>38</v>
@@ -2280,13 +2280,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
@@ -2743,7 +2743,7 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.800000000000001</v>
@@ -2788,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
         <v>2.36</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
         <v>44</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2937,7 +2937,7 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="W10" t="n">
         <v>1.23</v>
@@ -2949,46 +2949,46 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
@@ -2997,55 +2997,55 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AQ10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1.78</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AW10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BC10" t="n">
         <v>1.93</v>
       </c>
-      <c r="AT10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BD10" t="n">
         <v>1.96</v>
       </c>
-      <c r="BC10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.9</v>
+        <v>1.97</v>
       </c>
       <c r="BG10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3182,7 +3182,7 @@
         <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3299,7 +3299,7 @@
         <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
         <v>1.08</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.2</v>
@@ -3409,10 +3409,10 @@
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.49</v>
@@ -3421,16 +3421,16 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
         <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -3439,10 +3439,10 @@
         <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
@@ -3460,7 +3460,7 @@
         <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>8</v>
@@ -3472,13 +3472,13 @@
         <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="n">
         <v>14.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
@@ -3490,28 +3490,28 @@
         <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>24</v>
       </c>
       <c r="AO12" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
         <v>34</v>
@@ -3538,10 +3538,10 @@
         <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
         <v>17.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3657,13 @@
         <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I13" t="n">
         <v>9.6</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K13" t="n">
         <v>6.2</v>
@@ -3702,7 +3702,7 @@
         <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X13" t="n">
         <v>75</v>
@@ -3759,7 +3759,7 @@
         <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -3777,7 +3777,7 @@
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW13" t="n">
         <v>6.8</v>
@@ -3801,7 +3801,7 @@
         <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
         <v>6.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
         <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
         <v>5.7</v>
@@ -4034,7 +4034,7 @@
         <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
         <v>12</v>
@@ -4058,7 +4058,7 @@
         <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF14" t="n">
         <v>4.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
         <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
         <v>5.2</v>
@@ -4210,31 +4210,31 @@
         <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="n">
         <v>42</v>
       </c>
-      <c r="AD15" t="n">
-        <v>25</v>
-      </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AF15" t="n">
         <v>970</v>
@@ -4243,40 +4243,40 @@
         <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>48</v>
+        <v>6.6</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
@@ -4285,10 +4285,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -4300,7 +4300,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
         <v>12.5</v>
@@ -4309,16 +4309,16 @@
         <v>11</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF15" t="n">
         <v>4.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>3.45</v>
       </c>
       <c r="H16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I16" t="n">
         <v>2.3</v>
@@ -4476,40 +4476,40 @@
         <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AB16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AC16" t="n">
         <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
         <v>50</v>
@@ -4521,10 +4521,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP16" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -4557,16 +4557,16 @@
         <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
         <v>21</v>
       </c>
       <c r="BD16" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>44</v>
+        <v>2.88</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
         <v>110</v>
@@ -4733,28 +4733,28 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AC17" t="n">
         <v>42</v>
       </c>
       <c r="AD17" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AE17" t="n">
         <v>190</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
@@ -4763,7 +4763,7 @@
         <v>65</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>7.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>2.68</v>
       </c>
       <c r="H19" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="I19" t="n">
         <v>3.2</v>
@@ -5202,19 +5202,19 @@
         <v>1.86</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P19" t="n">
         <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R19" t="n">
         <v>1.86</v>
       </c>
       <c r="S19" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="T19" t="n">
         <v>1.05</v>
@@ -5232,46 +5232,46 @@
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="Z19" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE19" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI19" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
@@ -5301,19 +5301,19 @@
         <v>1.58</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AW19" t="n">
         <v>1.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AY19" t="n">
         <v>1.58</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BA19" t="n">
         <v>1.69</v>
@@ -5325,10 +5325,10 @@
         <v>1.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BF19" t="n">
         <v>2.06</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
         <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -5504,7 +5504,7 @@
         <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
         <v>75</v>
@@ -5516,16 +5516,16 @@
         <v>60</v>
       </c>
       <c r="AI20" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
         <v>75</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
@@ -5543,7 +5543,7 @@
         <v>5.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
         <v>6.6</v>
@@ -5555,7 +5555,7 @@
         <v>8.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW20" t="n">
         <v>6</v>
@@ -5567,7 +5567,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA20" t="n">
         <v>6.4</v>
@@ -5582,10 +5582,10 @@
         <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG20" t="n">
         <v>8</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>9.6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.81</v>
@@ -5719,7 +5719,7 @@
         <v>1.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
         <v>1.62</v>
@@ -5740,37 +5740,37 @@
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AC21" t="n">
         <v>95</v>
       </c>
       <c r="AD21" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AF21" t="n">
         <v>350</v>
       </c>
       <c r="AG21" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AH21" t="n">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="AI21" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -5821,13 +5821,13 @@
         <v>1.59</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="BA21" t="n">
         <v>1.59</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BC21" t="n">
         <v>1.64</v>
@@ -5839,7 +5839,7 @@
         <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG21" t="n">
         <v>1.55</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6000,22 +6000,22 @@
         <v>95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
         <v>95</v>
       </c>
       <c r="AD22" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AE22" t="n">
         <v>470</v>
       </c>
       <c r="AF22" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AG22" t="n">
         <v>36</v>
@@ -6048,10 +6048,10 @@
         <v>5.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AS22" t="n">
         <v>1.82</v>
@@ -6066,22 +6066,22 @@
         <v>1.75</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.69</v>
+        <v>5.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BA22" t="n">
         <v>1.81</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BC22" t="n">
         <v>1.77</v>
@@ -6096,7 +6096,7 @@
         <v>4.9</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -6227,16 +6227,16 @@
         <v>1.96</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>1.96</v>
+        <v>2.72</v>
       </c>
       <c r="T23" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.18</v>
@@ -6248,31 +6248,31 @@
         <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="n">
         <v>90</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD23" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AE23" t="n">
         <v>320</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AG23" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH23" t="n">
         <v>130</v>
@@ -6287,13 +6287,13 @@
         <v>65</v>
       </c>
       <c r="AL23" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -6302,10 +6302,10 @@
         <v>1.86</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AS23" t="n">
         <v>2.06</v>
@@ -6323,13 +6323,13 @@
         <v>2.04</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.86</v>
+        <v>5.6</v>
       </c>
       <c r="AY23" t="n">
         <v>1.83</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BA23" t="n">
         <v>2.04</v>
@@ -6341,7 +6341,7 @@
         <v>1.98</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BE23" t="n">
         <v>2.04</v>
@@ -6350,7 +6350,7 @@
         <v>3.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>36</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="K24" t="n">
         <v>18</v>
@@ -6481,7 +6481,7 @@
         <v>1.22</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
         <v>1.54</v>
@@ -6496,7 +6496,7 @@
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6562,7 +6562,7 @@
         <v>6.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
         <v>15.5</v>
@@ -6574,7 +6574,7 @@
         <v>6.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>9.800000000000001</v>
@@ -6586,7 +6586,7 @@
         <v>6.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.29</v>
@@ -6783,7 +6783,7 @@
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI25" t="n">
         <v>320</v>
@@ -6858,7 +6858,7 @@
         <v>7.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH25" t="n">
         <v>4.1</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P26" t="n">
         <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7112,71 +7112,71 @@
         <v>1.05</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         <v>1.63</v>
       </c>
       <c r="I28" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.08</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
         <v>1.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S28" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7509,7 +7509,7 @@
         <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="W28" t="n">
         <v>1.24</v>
@@ -7518,7 +7518,7 @@
         <v>250</v>
       </c>
       <c r="Y28" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z28" t="n">
         <v>50</v>
@@ -7533,7 +7533,7 @@
         <v>95</v>
       </c>
       <c r="AD28" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
         <v>85</v>
@@ -7542,7 +7542,7 @@
         <v>230</v>
       </c>
       <c r="AG28" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AH28" t="n">
         <v>80</v>
@@ -7557,7 +7557,7 @@
         <v>190</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -7569,59 +7569,59 @@
         <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BF28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG28" t="n">
         <v>1.55</v>
       </c>
-      <c r="BG28" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G29" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="I29" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J29" t="n">
         <v>3.55</v>
@@ -7748,7 +7748,7 @@
         <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="R29" t="n">
         <v>1.59</v>
@@ -7763,19 +7763,19 @@
         <v>2.42</v>
       </c>
       <c r="V29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y29" t="n">
         <v>24</v>
       </c>
       <c r="Z29" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AA29" t="n">
         <v>900</v>
@@ -7793,7 +7793,7 @@
         <v>65</v>
       </c>
       <c r="AF29" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
@@ -7802,22 +7802,22 @@
         <v>60</v>
       </c>
       <c r="AI29" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
         <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AO29" t="n">
         <v>29</v>
@@ -7847,98 +7847,98 @@
         <v>12.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA29" t="n">
         <v>13</v>
       </c>
       <c r="BB29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC29" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC29" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD29" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="BH29" t="n">
         <v>4.6</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BN29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BT29" t="n">
         <v>5.2</v>
       </c>
       <c r="BU29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7972,19 +7972,19 @@
         <v>2.28</v>
       </c>
       <c r="G30" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H30" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O30" t="n">
         <v>1.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="R30" t="n">
         <v>1.71</v>
       </c>
       <c r="S30" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,25 +8017,25 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.45</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="Z30" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AC30" t="n">
         <v>42</v>
@@ -8044,10 +8044,10 @@
         <v>970</v>
       </c>
       <c r="AE30" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
@@ -8056,16 +8056,16 @@
         <v>60</v>
       </c>
       <c r="AI30" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ30" t="n">
         <v>900</v>
       </c>
       <c r="AK30" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL30" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
         <v>580</v>
@@ -8098,7 +8098,7 @@
         <v>1.62</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AX30" t="n">
         <v>1.71</v>
@@ -8110,13 +8110,13 @@
         <v>1.64</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BD30" t="n">
         <v>1.71</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8226,19 +8226,19 @@
         <v>7.2</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.23</v>
@@ -8268,13 +8268,13 @@
         <v>1.69</v>
       </c>
       <c r="U31" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
         <v>90</v>
@@ -8286,13 +8286,13 @@
         <v>970</v>
       </c>
       <c r="AA31" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AB31" t="n">
         <v>100</v>
       </c>
       <c r="AC31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD31" t="n">
         <v>13</v>
@@ -8301,19 +8301,19 @@
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AG31" t="n">
         <v>80</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AI31" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AK31" t="n">
         <v>240</v>
@@ -8322,16 +8322,16 @@
         <v>190</v>
       </c>
       <c r="AM31" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO31" t="n">
         <v>4.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ31" t="n">
         <v>10.5</v>
@@ -8343,7 +8343,7 @@
         <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
         <v>11</v>
@@ -8355,10 +8355,10 @@
         <v>10.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ31" t="n">
         <v>16.5</v>
@@ -8367,22 +8367,22 @@
         <v>20</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC31" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF31" t="n">
         <v>15</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH31" t="n">
         <v>5.4</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G32" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H32" t="n">
         <v>3.6</v>
@@ -8489,7 +8489,7 @@
         <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
         <v>3.85</v>
@@ -8528,7 +8528,7 @@
         <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
         <v>14.5</v>
@@ -8567,7 +8567,7 @@
         <v>250</v>
       </c>
       <c r="AJ32" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK32" t="n">
         <v>25</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8734,16 +8734,16 @@
         <v>1.55</v>
       </c>
       <c r="G33" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K33" t="n">
         <v>4.6</v>
@@ -8776,13 +8776,13 @@
         <v>1.97</v>
       </c>
       <c r="U33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V33" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W33" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="X33" t="n">
         <v>16</v>
@@ -8806,10 +8806,10 @@
         <v>27</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
@@ -8833,7 +8833,7 @@
         <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO33" t="n">
         <v>170</v>
@@ -8842,25 +8842,25 @@
         <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR33" t="n">
         <v>48</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT33" t="n">
         <v>7</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV33" t="n">
         <v>21</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AX33" t="n">
         <v>7.8</v>
@@ -8872,7 +8872,7 @@
         <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
         <v>12.5</v>
@@ -8881,7 +8881,7 @@
         <v>14.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE33" t="n">
         <v>65</v>
@@ -8890,7 +8890,7 @@
         <v>7.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH33" t="n">
         <v>3.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>27</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H34" t="n">
         <v>1.02</v>
@@ -9009,25 +9009,25 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="S34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
         <v>1.76</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -9242,13 +9242,13 @@
         <v>1.14</v>
       </c>
       <c r="G35" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="H35" t="n">
         <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
@@ -9263,7 +9263,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O35" t="n">
         <v>1.1</v>
@@ -9278,19 +9278,19 @@
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
         <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9305,7 +9305,7 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC35" t="n">
         <v>1000</v>
@@ -9341,64 +9341,64 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>5.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I36" t="n">
         <v>1.63</v>
@@ -9532,13 +9532,13 @@
         <v>1.81</v>
       </c>
       <c r="S36" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T36" t="n">
         <v>1.58</v>
       </c>
       <c r="U36" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V36" t="n">
         <v>2.58</v>
@@ -9568,7 +9568,7 @@
         <v>10</v>
       </c>
       <c r="AE36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF36" t="n">
         <v>55</v>
@@ -9583,19 +9583,19 @@
         <v>23</v>
       </c>
       <c r="AJ36" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AK36" t="n">
         <v>120</v>
       </c>
       <c r="AL36" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AM36" t="n">
         <v>65</v>
       </c>
       <c r="AN36" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AO36" t="n">
         <v>5.6</v>
@@ -9616,10 +9616,10 @@
         <v>26</v>
       </c>
       <c r="AU36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW36" t="n">
         <v>13.5</v>
@@ -9628,7 +9628,7 @@
         <v>44</v>
       </c>
       <c r="AY36" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ36" t="n">
         <v>16</v>
@@ -9649,7 +9649,7 @@
         <v>50</v>
       </c>
       <c r="BF36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG36" t="n">
         <v>5.3</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
         <v>1.99</v>
       </c>
       <c r="J37" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K37" t="n">
         <v>3.9</v>
@@ -9771,10 +9771,10 @@
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P37" t="n">
         <v>2.14</v>
@@ -9789,7 +9789,7 @@
         <v>3.05</v>
       </c>
       <c r="T37" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U37" t="n">
         <v>2.28</v>
@@ -9801,19 +9801,19 @@
         <v>1.29</v>
       </c>
       <c r="X37" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB37" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC37" t="n">
         <v>8.6</v>
@@ -9834,7 +9834,7 @@
         <v>17</v>
       </c>
       <c r="AI37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ37" t="n">
         <v>95</v>
@@ -9849,7 +9849,7 @@
         <v>85</v>
       </c>
       <c r="AN37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO37" t="n">
         <v>12</v>
@@ -9858,52 +9858,52 @@
         <v>15.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR37" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT37" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV37" t="n">
         <v>9.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX37" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AY37" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ37" t="n">
         <v>15</v>
       </c>
       <c r="BA37" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BB37" t="n">
         <v>36</v>
       </c>
       <c r="BC37" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BD37" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE37" t="n">
         <v>36</v>
       </c>
       <c r="BF37" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BG37" t="n">
         <v>10.5</v>
@@ -9912,19 +9912,19 @@
         <v>3.75</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BJ37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL37" t="n">
         <v>120</v>
       </c>
       <c r="BM37" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN37" t="n">
         <v>8</v>
@@ -9936,31 +9936,31 @@
         <v>36</v>
       </c>
       <c r="BQ37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR37" t="n">
         <v>44</v>
       </c>
       <c r="BS37" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV37" t="n">
         <v>14</v>
       </c>
       <c r="BW37" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX37" t="n">
         <v>27</v>
       </c>
       <c r="BY37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G38" t="n">
         <v>1.73</v>
@@ -10010,16 +10010,16 @@
         <v>4.8</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K38" t="n">
         <v>4.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
         <v>1.03</v>
@@ -10043,19 +10043,19 @@
         <v>2.22</v>
       </c>
       <c r="T38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U38" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V38" t="n">
         <v>1.24</v>
       </c>
       <c r="W38" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X38" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y38" t="n">
         <v>32</v>
@@ -10067,13 +10067,13 @@
         <v>110</v>
       </c>
       <c r="AB38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="n">
         <v>60</v>
@@ -10085,7 +10085,7 @@
         <v>11</v>
       </c>
       <c r="AH38" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI38" t="n">
         <v>55</v>
@@ -10097,7 +10097,7 @@
         <v>15.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM38" t="n">
         <v>60</v>
@@ -10106,31 +10106,31 @@
         <v>6.4</v>
       </c>
       <c r="AO38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR38" t="n">
         <v>40</v>
       </c>
-      <c r="AP38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>32</v>
-      </c>
       <c r="AS38" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AT38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU38" t="n">
         <v>10</v>
       </c>
       <c r="AV38" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW38" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AX38" t="n">
         <v>12.5</v>
@@ -10139,13 +10139,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA38" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BB38" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC38" t="n">
         <v>14</v>
@@ -10154,13 +10154,13 @@
         <v>21</v>
       </c>
       <c r="BE38" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="BH38" t="n">
         <v>4.9</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
         <v>1.73</v>
       </c>
       <c r="U39" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
@@ -10318,7 +10318,7 @@
         <v>100</v>
       </c>
       <c r="AA39" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB39" t="n">
         <v>11</v>
@@ -10327,10 +10327,10 @@
         <v>9.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE39" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AF39" t="n">
         <v>12</v>
@@ -10360,7 +10360,7 @@
         <v>9.6</v>
       </c>
       <c r="AO39" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP39" t="n">
         <v>17.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10539,10 +10539,10 @@
         <v>1.23</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R40" t="n">
         <v>1.56</v>
@@ -10551,16 +10551,16 @@
         <v>2.74</v>
       </c>
       <c r="T40" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U40" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V40" t="n">
         <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X40" t="n">
         <v>22</v>
@@ -10578,10 +10578,10 @@
         <v>13.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE40" t="n">
         <v>38</v>
@@ -10590,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="AG40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH40" t="n">
         <v>16</v>
@@ -10602,7 +10602,7 @@
         <v>29</v>
       </c>
       <c r="AK40" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL40" t="n">
         <v>32</v>
@@ -10617,13 +10617,13 @@
         <v>28</v>
       </c>
       <c r="AP40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ40" t="n">
         <v>15</v>
       </c>
       <c r="AR40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS40" t="n">
         <v>30</v>
@@ -10632,16 +10632,16 @@
         <v>11.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AX40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY40" t="n">
         <v>10</v>
@@ -10653,7 +10653,7 @@
         <v>32</v>
       </c>
       <c r="BB40" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BC40" t="n">
         <v>18</v>
@@ -10668,7 +10668,7 @@
         <v>11</v>
       </c>
       <c r="BG40" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH40" t="n">
         <v>4.2</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10766,19 +10766,19 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H41" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I41" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J41" t="n">
         <v>3.55</v>
       </c>
       <c r="K41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.42</v>
@@ -10811,10 +10811,10 @@
         <v>2.16</v>
       </c>
       <c r="V41" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W41" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X41" t="n">
         <v>16.5</v>
@@ -10823,10 +10823,10 @@
         <v>10.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="n">
         <v>14</v>
@@ -10853,7 +10853,7 @@
         <v>46</v>
       </c>
       <c r="AJ41" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK41" t="n">
         <v>42</v>
@@ -10862,10 +10862,10 @@
         <v>55</v>
       </c>
       <c r="AM41" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN41" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AO41" t="n">
         <v>26</v>
@@ -10880,7 +10880,7 @@
         <v>12.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT41" t="n">
         <v>10.5</v>
@@ -10904,25 +10904,25 @@
         <v>13.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BG41" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BH41" t="n">
         <v>3.75</v>
@@ -10934,31 +10934,31 @@
         <v>11</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL41" t="n">
         <v>140</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BN41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO41" t="n">
         <v>4.9</v>
       </c>
       <c r="BP41" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR41" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BT41" t="n">
         <v>6.2</v>
@@ -10970,23 +10970,23 @@
         <v>22</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX41" t="n">
         <v>38</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ41" t="n">
         <v>32</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11041,25 +11041,25 @@
         <v>1.03</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
         <v>1.19</v>
       </c>
       <c r="P42" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R42" t="n">
         <v>1.66</v>
       </c>
       <c r="S42" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T42" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U42" t="n">
         <v>2.44</v>
@@ -11083,10 +11083,10 @@
         <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD42" t="n">
         <v>27</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11271,58 +11271,58 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>12</v>
+        <v>2.46</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>990</v>
       </c>
       <c r="H43" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="J43" t="n">
-        <v>5.4</v>
+        <v>2.76</v>
       </c>
       <c r="K43" t="n">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="O43" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="R43" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="T43" t="n">
-        <v>2.46</v>
+        <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>3.9</v>
+        <v>2.14</v>
       </c>
       <c r="W43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
         <v>21</v>
@@ -11331,10 +11331,10 @@
         <v>970</v>
       </c>
       <c r="Z43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA43" t="n">
         <v>970</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>10.5</v>
       </c>
       <c r="AB43" t="n">
         <v>110</v>
@@ -11379,122 +11379,122 @@
         <v>29</v>
       </c>
       <c r="AP43" t="n">
-        <v>5.4</v>
+        <v>1.35</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.85</v>
+        <v>1.33</v>
       </c>
       <c r="AR43" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.6</v>
+        <v>1.32</v>
       </c>
       <c r="AT43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF43" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG43" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="BH43" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BI43" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ43" t="n">
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BN43" t="n">
         <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BT43" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G44" t="n">
         <v>2.6</v>
@@ -11540,7 +11540,7 @@
         <v>2.8</v>
       </c>
       <c r="K44" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L44" t="n">
         <v>1.41</v>
@@ -11588,7 +11588,7 @@
         <v>70</v>
       </c>
       <c r="AA44" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
         <v>10</v>
@@ -11597,7 +11597,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD44" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AE44" t="n">
         <v>240</v>
@@ -11612,10 +11612,10 @@
         <v>55</v>
       </c>
       <c r="AI44" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AJ44" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
         <v>90</v>
@@ -11642,7 +11642,7 @@
         <v>10.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT44" t="n">
         <v>6.2</v>
@@ -11684,7 +11684,7 @@
         <v>5.9</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH44" t="n">
         <v>2.98</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11782,16 +11782,16 @@
         <v>1.07</v>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H45" t="n">
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J45" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K45" t="n">
         <v>950</v>
@@ -11809,7 +11809,7 @@
         <v>1.13</v>
       </c>
       <c r="P45" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q45" t="n">
         <v>1.15</v>
@@ -11821,10 +11821,10 @@
         <v>1.34</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
         <v>1.02</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12042,10 +12042,10 @@
         <v>1.01</v>
       </c>
       <c r="I46" t="n">
-        <v>200</v>
+        <v>870</v>
       </c>
       <c r="J46" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K46" t="n">
         <v>950</v>
@@ -12060,19 +12060,19 @@
         <v>1.25</v>
       </c>
       <c r="O46" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P46" t="n">
         <v>1.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R46" t="n">
         <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="n">
         <v>4.6</v>
@@ -12299,10 +12299,10 @@
         <v>5</v>
       </c>
       <c r="J47" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L47" t="n">
         <v>1.44</v>
@@ -12320,13 +12320,13 @@
         <v>1.66</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R47" t="n">
         <v>1.24</v>
       </c>
       <c r="S47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T47" t="n">
         <v>2.06</v>
@@ -12338,19 +12338,19 @@
         <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="X47" t="n">
         <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z47" t="n">
         <v>34</v>
       </c>
       <c r="AA47" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
         <v>8.4</v>
@@ -12362,16 +12362,16 @@
         <v>21</v>
       </c>
       <c r="AE47" t="n">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="AF47" t="n">
         <v>11</v>
       </c>
       <c r="AG47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI47" t="n">
         <v>100</v>
@@ -12386,13 +12386,13 @@
         <v>55</v>
       </c>
       <c r="AM47" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN47" t="n">
         <v>21</v>
       </c>
       <c r="AO47" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP47" t="n">
         <v>9.199999999999999</v>
@@ -12404,7 +12404,7 @@
         <v>14.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT47" t="n">
         <v>6.6</v>
@@ -12434,19 +12434,19 @@
         <v>20</v>
       </c>
       <c r="BC47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD47" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BE47" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF47" t="n">
         <v>17</v>
       </c>
       <c r="BG47" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BH47" t="n">
         <v>2.96</v>
@@ -12476,7 +12476,7 @@
         <v>16</v>
       </c>
       <c r="BQ47" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BR47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12541,230 +12541,230 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="H48" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I48" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="K48" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="L48" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="M48" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O48" t="n">
         <v>1.67</v>
       </c>
       <c r="P48" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R48" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S48" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T48" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="U48" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W48" t="n">
         <v>1.52</v>
       </c>
       <c r="X48" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="Z48" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA48" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB48" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC48" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AD48" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE48" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AF48" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG48" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH48" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AI48" t="n">
         <v>540</v>
       </c>
       <c r="AJ48" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AK48" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL48" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM48" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN48" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO48" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP48" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR48" t="n">
-        <v>19</v>
+        <v>1.61</v>
       </c>
       <c r="AS48" t="n">
-        <v>9</v>
+        <v>1.65</v>
       </c>
       <c r="AT48" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>6</v>
+        <v>1.66</v>
       </c>
       <c r="AV48" t="n">
-        <v>12.5</v>
+        <v>1.6</v>
       </c>
       <c r="AW48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY48" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX48" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BI48" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ48" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM48" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN48" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP48" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS48" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT48" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU48" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV48" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY48" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12801,25 +12801,25 @@
         <v>5.1</v>
       </c>
       <c r="H49" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="I49" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>3.45</v>
       </c>
       <c r="K49" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="L49" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O49" t="n">
         <v>1.25</v>
@@ -12843,7 +12843,7 @@
         <v>2.2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W49" t="n">
         <v>1.27</v>
@@ -12861,37 +12861,37 @@
         <v>900</v>
       </c>
       <c r="AB49" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AC49" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD49" t="n">
         <v>970</v>
       </c>
       <c r="AE49" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF49" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG49" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AH49" t="n">
         <v>60</v>
       </c>
       <c r="AI49" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ49" t="n">
         <v>900</v>
       </c>
       <c r="AK49" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AL49" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM49" t="n">
         <v>580</v>
@@ -12903,55 +12903,55 @@
         <v>85</v>
       </c>
       <c r="AP49" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR49" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT49" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AU49" t="n">
         <v>6.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX49" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AY49" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="BB49" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="BC49" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="BD49" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="BE49" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG49" t="n">
         <v>7.2</v>
@@ -12960,7 +12960,7 @@
         <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ49" t="n">
         <v>1000</v>
@@ -12978,7 +12978,7 @@
         <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
@@ -12996,7 +12996,7 @@
         <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13052,16 +13052,16 @@
         <v>1.04</v>
       </c>
       <c r="G50" t="n">
-        <v>380</v>
+        <v>600</v>
       </c>
       <c r="H50" t="n">
         <v>1.01</v>
       </c>
       <c r="I50" t="n">
-        <v>200</v>
+        <v>870</v>
       </c>
       <c r="J50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K50" t="n">
         <v>950</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="G51" t="n">
         <v>990</v>
@@ -13312,13 +13312,13 @@
         <v>1.12</v>
       </c>
       <c r="I51" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="J51" t="n">
         <v>6.2</v>
       </c>
       <c r="K51" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -13327,31 +13327,31 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O51" t="n">
         <v>1.16</v>
       </c>
       <c r="P51" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q51" t="n">
         <v>1.35</v>
       </c>
       <c r="R51" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S51" t="n">
         <v>2.26</v>
       </c>
       <c r="T51" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V51" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
@@ -13372,7 +13372,7 @@
         <v>170</v>
       </c>
       <c r="AC51" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
         <v>970</v>
@@ -13411,7 +13411,7 @@
         <v>29</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AQ51" t="n">
         <v>5.6</v>
@@ -13423,110 +13423,110 @@
         <v>4.9</v>
       </c>
       <c r="AT51" t="n">
-        <v>4.2</v>
+        <v>1.69</v>
       </c>
       <c r="AU51" t="n">
         <v>1.71</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.66</v>
+        <v>7</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.2</v>
+        <v>1.69</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BF51" t="n">
         <v>4.2</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13611,10 +13611,10 @@
         <v>1.6</v>
       </c>
       <c r="X52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="n">
         <v>26</v>
@@ -13623,10 +13623,10 @@
         <v>900</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC52" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD52" t="n">
         <v>13.5</v>
@@ -13635,7 +13635,7 @@
         <v>90</v>
       </c>
       <c r="AF52" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG52" t="n">
         <v>12.5</v>
@@ -13674,7 +13674,7 @@
         <v>17</v>
       </c>
       <c r="AS52" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT52" t="n">
         <v>9.199999999999999</v>
@@ -13686,7 +13686,7 @@
         <v>11</v>
       </c>
       <c r="AW52" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AX52" t="n">
         <v>13.5</v>
@@ -13698,25 +13698,25 @@
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB52" t="n">
         <v>16</v>
       </c>
       <c r="BC52" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD52" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE52" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF52" t="n">
         <v>15.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13811,22 +13811,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G53" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H53" t="n">
         <v>4.2</v>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K53" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L53" t="n">
         <v>1.3</v>
@@ -13835,7 +13835,7 @@
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
         <v>1.28</v>
@@ -13844,7 +13844,7 @@
         <v>2.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R53" t="n">
         <v>1.44</v>
@@ -13856,16 +13856,16 @@
         <v>1.76</v>
       </c>
       <c r="U53" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V53" t="n">
         <v>1.3</v>
       </c>
       <c r="W53" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X53" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y53" t="n">
         <v>21</v>
@@ -13889,25 +13889,25 @@
         <v>50</v>
       </c>
       <c r="AF53" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG53" t="n">
         <v>11</v>
       </c>
       <c r="AH53" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI53" t="n">
         <v>55</v>
       </c>
       <c r="AJ53" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AK53" t="n">
         <v>19</v>
       </c>
       <c r="AL53" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM53" t="n">
         <v>100</v>
@@ -13916,19 +13916,19 @@
         <v>12</v>
       </c>
       <c r="AO53" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="AP53" t="n">
         <v>14</v>
       </c>
       <c r="AQ53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR53" t="n">
         <v>28</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT53" t="n">
         <v>9.6</v>
@@ -13961,7 +13961,7 @@
         <v>17</v>
       </c>
       <c r="BD53" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BE53" t="n">
         <v>26</v>
@@ -13988,28 +13988,28 @@
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN53" t="n">
         <v>4.7</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP53" t="n">
         <v>13</v>
       </c>
       <c r="BQ53" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT53" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BR53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS53" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT53" t="n">
-        <v>7.8</v>
       </c>
       <c r="BU53" t="n">
         <v>5.5</v>
@@ -14018,23 +14018,23 @@
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14089,19 +14089,19 @@
         <v>1.06</v>
       </c>
       <c r="N54" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P54" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q54" t="n">
         <v>1.87</v>
       </c>
       <c r="R54" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
         <v>3.2</v>
@@ -14137,7 +14137,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD54" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE54" t="n">
         <v>55</v>
@@ -14149,19 +14149,19 @@
         <v>10.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI54" t="n">
         <v>60</v>
       </c>
       <c r="AJ54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM54" t="n">
         <v>100</v>
@@ -14170,7 +14170,7 @@
         <v>13</v>
       </c>
       <c r="AO54" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AP54" t="n">
         <v>13.5</v>
@@ -14182,7 +14182,7 @@
         <v>28</v>
       </c>
       <c r="AS54" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT54" t="n">
         <v>8.800000000000001</v>
@@ -14194,7 +14194,7 @@
         <v>15</v>
       </c>
       <c r="AW54" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="AX54" t="n">
         <v>11</v>
@@ -14218,7 +14218,7 @@
         <v>30</v>
       </c>
       <c r="BE54" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF54" t="n">
         <v>11.5</v>
@@ -14227,10 +14227,10 @@
         <v>11</v>
       </c>
       <c r="BH54" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ54" t="n">
         <v>10</v>
@@ -14248,7 +14248,7 @@
         <v>4.9</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP54" t="n">
         <v>14</v>
@@ -14272,23 +14272,23 @@
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA54" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
         <v>2.26</v>
       </c>
       <c r="W55" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X55" t="n">
         <v>17</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14576,22 +14576,22 @@
         <v>2.36</v>
       </c>
       <c r="G56" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H56" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I56" t="n">
         <v>3.3</v>
       </c>
       <c r="J56" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K56" t="n">
         <v>3.85</v>
       </c>
       <c r="L56" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M56" t="n">
         <v>1.06</v>
@@ -14603,19 +14603,19 @@
         <v>1.29</v>
       </c>
       <c r="P56" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R56" t="n">
         <v>1.4</v>
       </c>
       <c r="S56" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T56" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U56" t="n">
         <v>2.26</v>
@@ -14624,28 +14624,28 @@
         <v>1.43</v>
       </c>
       <c r="W56" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X56" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z56" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA56" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AB56" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC56" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE56" t="n">
         <v>40</v>
@@ -14654,25 +14654,25 @@
         <v>17.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH56" t="n">
         <v>17.5</v>
       </c>
       <c r="AI56" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AJ56" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK56" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL56" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AM56" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN56" t="n">
         <v>18.5</v>
@@ -14690,19 +14690,19 @@
         <v>17.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT56" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU56" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV56" t="n">
         <v>10.5</v>
       </c>
       <c r="AW56" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AX56" t="n">
         <v>12.5</v>
@@ -14714,31 +14714,31 @@
         <v>12.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB56" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC56" t="n">
         <v>20</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BE56" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BF56" t="n">
         <v>13.5</v>
       </c>
       <c r="BG56" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BJ56" t="n">
         <v>9.6</v>
@@ -14753,28 +14753,28 @@
         <v>9.4</v>
       </c>
       <c r="BN56" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO56" t="n">
         <v>4.3</v>
       </c>
       <c r="BP56" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ56" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BR56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS56" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT56" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU56" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV56" t="n">
         <v>25</v>
@@ -14789,14 +14789,14 @@
         <v>8</v>
       </c>
       <c r="BZ56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA56" t="n">
         <v>7.2</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
         <v>3.25</v>
       </c>
       <c r="K57" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
         <v>3.6</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BJ59" t="n">
         <v>10.5</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G60" t="n">
         <v>1.37</v>
@@ -15598,13 +15598,13 @@
         <v>10</v>
       </c>
       <c r="I60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J60" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K60" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15619,133 +15619,133 @@
         <v>1.22</v>
       </c>
       <c r="P60" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R60" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S60" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T60" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U60" t="n">
         <v>1.81</v>
       </c>
       <c r="V60" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W60" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y60" t="n">
         <v>85</v>
       </c>
       <c r="Z60" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="AA60" t="n">
         <v>470</v>
       </c>
       <c r="AB60" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC60" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD60" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AE60" t="n">
         <v>200</v>
       </c>
       <c r="AF60" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AG60" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH60" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AI60" t="n">
         <v>470</v>
       </c>
       <c r="AJ60" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK60" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL60" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM60" t="n">
         <v>390</v>
       </c>
       <c r="AN60" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO60" t="n">
         <v>260</v>
       </c>
       <c r="AP60" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AR60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS60" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT60" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU60" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV60" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AW60" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX60" t="n">
         <v>7.2</v>
       </c>
       <c r="AY60" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB60" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ60" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>8</v>
-      </c>
       <c r="BC60" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD60" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE60" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG60" t="n">
         <v>15</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
         <v>3.25</v>
       </c>
       <c r="K61" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L61" t="n">
         <v>1.43</v>
@@ -16008,7 +16008,7 @@
         <v>3.3</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ61" t="n">
         <v>10.5</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16106,13 +16106,13 @@
         <v>3.2</v>
       </c>
       <c r="I62" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K62" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -16121,7 +16121,7 @@
         <v>1.05</v>
       </c>
       <c r="N62" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O62" t="n">
         <v>1.25</v>
@@ -16133,7 +16133,7 @@
         <v>1.74</v>
       </c>
       <c r="R62" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S62" t="n">
         <v>2.84</v>
@@ -16142,7 +16142,7 @@
         <v>1.64</v>
       </c>
       <c r="U62" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V62" t="n">
         <v>1.39</v>
@@ -16160,10 +16160,10 @@
         <v>65</v>
       </c>
       <c r="AA62" t="n">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="AB62" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC62" t="n">
         <v>10</v>
@@ -16175,28 +16175,28 @@
         <v>90</v>
       </c>
       <c r="AF62" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AG62" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AH62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AI62" t="n">
         <v>150</v>
       </c>
       <c r="AJ62" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK62" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL62" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM62" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN62" t="n">
         <v>38</v>
@@ -16205,7 +16205,7 @@
         <v>50</v>
       </c>
       <c r="AP62" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ62" t="n">
         <v>7.6</v>
@@ -16214,7 +16214,7 @@
         <v>11.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT62" t="n">
         <v>9.199999999999999</v>
@@ -16226,37 +16226,37 @@
         <v>11</v>
       </c>
       <c r="AW62" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX62" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>12</v>
       </c>
       <c r="AY62" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA62" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB62" t="n">
         <v>14.5</v>
       </c>
       <c r="BC62" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BE62" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF62" t="n">
         <v>11.5</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16354,16 +16354,16 @@
         <v>1.83</v>
       </c>
       <c r="G63" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H63" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I63" t="n">
         <v>4.2</v>
       </c>
       <c r="J63" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K63" t="n">
         <v>4.9</v>
@@ -16390,7 +16390,7 @@
         <v>1.76</v>
       </c>
       <c r="S63" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="T63" t="n">
         <v>1.47</v>
@@ -16402,10 +16402,10 @@
         <v>1.31</v>
       </c>
       <c r="W63" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X63" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y63" t="n">
         <v>26</v>
@@ -16414,25 +16414,25 @@
         <v>38</v>
       </c>
       <c r="AA63" t="n">
-        <v>470</v>
+        <v>160</v>
       </c>
       <c r="AB63" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC63" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE63" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF63" t="n">
         <v>17.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH63" t="n">
         <v>16</v>
@@ -16456,61 +16456,61 @@
         <v>7.4</v>
       </c>
       <c r="AO63" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP63" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ63" t="n">
         <v>21</v>
       </c>
       <c r="AR63" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="AS63" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT63" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="AU63" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AV63" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AW63" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="AX63" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY63" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AZ63" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BA63" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="BB63" t="n">
         <v>19</v>
       </c>
       <c r="BC63" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BD63" t="n">
         <v>20</v>
       </c>
       <c r="BE63" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF63" t="n">
         <v>6</v>
       </c>
       <c r="BG63" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G64" t="n">
         <v>2.46</v>
@@ -16617,13 +16617,13 @@
         <v>3.55</v>
       </c>
       <c r="J64" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L64" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M64" t="n">
         <v>1.09</v>
@@ -16647,13 +16647,13 @@
         <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U64" t="n">
         <v>2.02</v>
       </c>
       <c r="V64" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W64" t="n">
         <v>1.68</v>
@@ -16665,7 +16665,7 @@
         <v>12.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AA64" t="n">
         <v>500</v>
@@ -16701,7 +16701,7 @@
         <v>48</v>
       </c>
       <c r="AL64" t="n">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="AM64" t="n">
         <v>580</v>
@@ -16710,7 +16710,7 @@
         <v>55</v>
       </c>
       <c r="AO64" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP64" t="n">
         <v>9.800000000000001</v>
@@ -16728,13 +16728,13 @@
         <v>7.8</v>
       </c>
       <c r="AU64" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV64" t="n">
         <v>12</v>
       </c>
       <c r="AW64" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX64" t="n">
         <v>11</v>
@@ -16758,7 +16758,7 @@
         <v>36</v>
       </c>
       <c r="BE64" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF64" t="n">
         <v>20</v>
@@ -16767,10 +16767,10 @@
         <v>8.4</v>
       </c>
       <c r="BH64" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ64" t="n">
         <v>10.5</v>
@@ -16788,13 +16788,13 @@
         <v>5.4</v>
       </c>
       <c r="BO64" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP64" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ64" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
@@ -16809,10 +16809,10 @@
         <v>4.9</v>
       </c>
       <c r="BV64" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
         <v>3.35</v>
       </c>
       <c r="H65" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I65" t="n">
         <v>2.48</v>
@@ -16874,7 +16874,7 @@
         <v>3.8</v>
       </c>
       <c r="K65" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -16886,7 +16886,7 @@
         <v>3.4</v>
       </c>
       <c r="O65" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P65" t="n">
         <v>3</v>
@@ -16895,7 +16895,7 @@
         <v>1.27</v>
       </c>
       <c r="R65" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S65" t="n">
         <v>1.96</v>
@@ -16916,49 +16916,49 @@
         <v>1000</v>
       </c>
       <c r="Y65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA65" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC65" t="n">
         <v>42</v>
       </c>
       <c r="AD65" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH65" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL65" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM65" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN65" t="n">
         <v>100</v>
@@ -16967,58 +16967,58 @@
         <v>100</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.07</v>
+        <v>1.79</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.07</v>
+        <v>1.81</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.07</v>
+        <v>1.79</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.07</v>
+        <v>1.66</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.05</v>
+        <v>1.68</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.07</v>
+        <v>1.83</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.07</v>
+        <v>1.79</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.06</v>
+        <v>1.81</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.06</v>
+        <v>2.36</v>
       </c>
       <c r="BH65" t="n">
         <v>1000</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17113,10 +17113,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G66" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H66" t="n">
         <v>2.6</v>
@@ -17128,7 +17128,7 @@
         <v>4.2</v>
       </c>
       <c r="K66" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -17137,13 +17137,13 @@
         <v>1.02</v>
       </c>
       <c r="N66" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O66" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P66" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="Q66" t="n">
         <v>1.35</v>
@@ -17152,7 +17152,7 @@
         <v>1.82</v>
       </c>
       <c r="S66" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="T66" t="n">
         <v>1.11</v>
@@ -17164,55 +17164,55 @@
         <v>1.51</v>
       </c>
       <c r="W66" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA66" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC66" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN66" t="n">
         <v>1000</v>
@@ -17221,58 +17221,58 @@
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AU66" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AV66" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="BA66" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="BC66" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="BD66" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BG66" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH66" t="n">
         <v>1000</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17367,16 +17367,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="G67" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I67" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J67" t="n">
         <v>2.76</v>
@@ -17400,7 +17400,7 @@
         <v>1.54</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R67" t="n">
         <v>1.16</v>
@@ -17415,10 +17415,10 @@
         <v>1.11</v>
       </c>
       <c r="V67" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W67" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="X67" t="n">
         <v>970</v>
@@ -17427,22 +17427,22 @@
         <v>970</v>
       </c>
       <c r="Z67" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA67" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB67" t="n">
         <v>970</v>
       </c>
       <c r="AC67" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="AD67" t="n">
         <v>970</v>
       </c>
       <c r="AE67" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF67" t="n">
         <v>970</v>
@@ -17451,82 +17451,82 @@
         <v>970</v>
       </c>
       <c r="AH67" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ67" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK67" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL67" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM67" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN67" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AO67" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP67" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AR67" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS67" t="n">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AU67" t="n">
         <v>5.7</v>
       </c>
       <c r="AV67" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW67" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AX67" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AY67" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AZ67" t="n">
         <v>4.2</v>
       </c>
       <c r="BA67" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="BB67" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC67" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD67" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="BE67" t="n">
-        <v>4.8</v>
+        <v>2.12</v>
       </c>
       <c r="BF67" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG67" t="n">
-        <v>4.6</v>
+        <v>2.14</v>
       </c>
       <c r="BH67" t="n">
         <v>4.6</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17681,7 +17681,7 @@
         <v>970</v>
       </c>
       <c r="Z68" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AA68" t="n">
         <v>900</v>
@@ -17690,13 +17690,13 @@
         <v>7</v>
       </c>
       <c r="AC68" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD68" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AE68" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF68" t="n">
         <v>19.5</v>
@@ -17708,7 +17708,7 @@
         <v>70</v>
       </c>
       <c r="AI68" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ68" t="n">
         <v>180</v>
@@ -17717,16 +17717,16 @@
         <v>65</v>
       </c>
       <c r="AL68" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM68" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN68" t="n">
         <v>48</v>
       </c>
       <c r="AO68" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP68" t="n">
         <v>9</v>
@@ -17735,7 +17735,7 @@
         <v>13.5</v>
       </c>
       <c r="AR68" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AS68" t="n">
         <v>6.4</v>
@@ -17771,13 +17771,13 @@
         <v>15.5</v>
       </c>
       <c r="BD68" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BE68" t="n">
         <v>6.4</v>
       </c>
       <c r="BF68" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG68" t="n">
         <v>6.4</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17917,7 +17917,7 @@
         <v>3.3</v>
       </c>
       <c r="T69" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U69" t="n">
         <v>2.18</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18129,13 +18129,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G70" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H70" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I70" t="n">
         <v>4.2</v>
@@ -18147,169 +18147,169 @@
         <v>3.4</v>
       </c>
       <c r="L70" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M70" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N70" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="O70" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P70" t="n">
         <v>1.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R70" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="S70" t="n">
-        <v>2.54</v>
+        <v>5.2</v>
       </c>
       <c r="T70" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U70" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V70" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W70" t="n">
         <v>1.78</v>
       </c>
       <c r="X70" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y70" t="n">
-        <v>75</v>
+        <v>11.5</v>
       </c>
       <c r="Z70" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AA70" t="n">
         <v>900</v>
       </c>
       <c r="AB70" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC70" t="n">
-        <v>95</v>
+        <v>7.6</v>
       </c>
       <c r="AD70" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="AE70" t="n">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="AF70" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="AG70" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="AH70" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AI70" t="n">
         <v>210</v>
       </c>
       <c r="AJ70" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK70" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="AL70" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="AM70" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN70" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AO70" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP70" t="n">
         <v>7</v>
       </c>
       <c r="AQ70" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.68</v>
+        <v>19.5</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.69</v>
+        <v>8.6</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.41</v>
+        <v>5.3</v>
       </c>
       <c r="AU70" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="AV70" t="n">
-        <v>1.67</v>
+        <v>13</v>
       </c>
       <c r="AW70" t="n">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX70" t="n">
-        <v>1.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY70" t="n">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="AZ70" t="n">
-        <v>1.66</v>
+        <v>17.5</v>
       </c>
       <c r="BA70" t="n">
-        <v>1.67</v>
+        <v>8.4</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.63</v>
+        <v>7.4</v>
       </c>
       <c r="BC70" t="n">
-        <v>1.66</v>
+        <v>7.2</v>
       </c>
       <c r="BD70" t="n">
-        <v>1.69</v>
+        <v>8</v>
       </c>
       <c r="BE70" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.63</v>
+        <v>7.2</v>
       </c>
       <c r="BG70" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="BH70" t="n">
         <v>1000</v>
       </c>
       <c r="BI70" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="BJ70" t="n">
         <v>16</v>
       </c>
       <c r="BK70" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BL70" t="n">
         <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BN70" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO70" t="n">
         <v>3.25</v>
@@ -18318,41 +18318,41 @@
         <v>29</v>
       </c>
       <c r="BQ70" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BR70" t="n">
         <v>1000</v>
       </c>
       <c r="BS70" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BT70" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU70" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BX70" t="n">
         <v>1000</v>
       </c>
       <c r="BY70" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA70" t="n">
         <v>1.67</v>
       </c>
-      <c r="BZ70" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA70" t="n">
-        <v>1.66</v>
-      </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18640,7 +18640,7 @@
         <v>1.92</v>
       </c>
       <c r="G72" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H72" t="n">
         <v>4.7</v>
@@ -18679,16 +18679,16 @@
         <v>4.4</v>
       </c>
       <c r="T72" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V72" t="n">
         <v>1.23</v>
       </c>
       <c r="W72" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X72" t="n">
         <v>12.5</v>
@@ -18736,13 +18736,13 @@
         <v>60</v>
       </c>
       <c r="AM72" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN72" t="n">
         <v>23</v>
       </c>
       <c r="AO72" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP72" t="n">
         <v>3.6</v>
@@ -18751,7 +18751,7 @@
         <v>11.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS72" t="n">
         <v>4.9</v>
@@ -18778,10 +18778,10 @@
         <v>4.3</v>
       </c>
       <c r="BA72" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB72" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="BC72" t="n">
         <v>20</v>
@@ -18790,7 +18790,7 @@
         <v>4.7</v>
       </c>
       <c r="BE72" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF72" t="n">
         <v>14</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18903,7 +18903,7 @@
         <v>3.6</v>
       </c>
       <c r="J73" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K73" t="n">
         <v>3.7</v>
@@ -18915,19 +18915,19 @@
         <v>1.07</v>
       </c>
       <c r="N73" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>1.34</v>
       </c>
       <c r="P73" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R73" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S73" t="n">
         <v>3.55</v>
@@ -18936,7 +18936,7 @@
         <v>1.79</v>
       </c>
       <c r="U73" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V73" t="n">
         <v>1.38</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -857,79 +857,79 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
       <c r="T2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.02</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>80</v>
@@ -938,25 +938,25 @@
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -965,64 +965,64 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
         <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1046,13 +1046,13 @@
         <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G3" t="n">
         <v>3.7</v>
@@ -1120,7 +1120,7 @@
         <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -1171,7 +1171,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
         <v>85</v>
@@ -1240,10 +1240,10 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
@@ -1252,31 +1252,31 @@
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1288,19 +1288,19 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="BN3" t="n">
         <v>6.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G4" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1383,7 +1383,7 @@
         <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1413,31 +1413,31 @@
         <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X4" t="n">
         <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
         <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1449,13 +1449,13 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
         <v>130</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>22</v>
@@ -1464,10 +1464,10 @@
         <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO4" t="n">
         <v>55</v>
@@ -1482,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
         <v>8.6</v>
@@ -1494,7 +1494,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
         <v>9.4</v>
@@ -1506,19 +1506,19 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
         <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>8.4</v>
@@ -1527,13 +1527,13 @@
         <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
         <v>3.45</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
         <v>6.8</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="BN4" t="n">
         <v>4.7</v>
@@ -1554,7 +1554,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1563,7 +1563,7 @@
         <v>7.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
         <v>5.8</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -1622,61 +1622,61 @@
         <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I5" t="n">
         <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
         <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
         <v>1.67</v>
       </c>
       <c r="X5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
         <v>25</v>
@@ -1688,58 +1688,58 @@
         <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
         <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
@@ -1748,7 +1748,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1760,31 +1760,31 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="BE5" t="n">
         <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="n">
         <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.6</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="BN5" t="n">
         <v>5.6</v>
@@ -1820,7 +1820,7 @@
         <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>21</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -1885,28 +1885,28 @@
         <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="P6" t="n">
         <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.16</v>
@@ -1915,10 +1915,10 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
         <v>1.37</v>
@@ -1927,7 +1927,7 @@
         <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y6" t="n">
         <v>9.199999999999999</v>
@@ -1936,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>7.6</v>
@@ -1948,7 +1948,7 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
         <v>26</v>
@@ -1957,7 +1957,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>240</v>
@@ -1975,34 +1975,34 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -2014,43 +2014,43 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5.3</v>
@@ -2062,7 +2062,7 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2071,7 +2071,7 @@
         <v>12</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
         <v>5</v>
@@ -2080,7 +2080,7 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.4</v>
@@ -2148,40 +2148,40 @@
         <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
         <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
         <v>9.800000000000001</v>
@@ -2193,10 +2193,10 @@
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
@@ -2211,7 +2211,7 @@
         <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>55</v>
@@ -2223,70 +2223,70 @@
         <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
         <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BB7" t="n">
         <v>38</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BF7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2298,40 +2298,40 @@
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>5.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW7" t="n">
         <v>7.6</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>2.32</v>
       </c>
       <c r="I8" t="n">
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.38</v>
@@ -2420,7 +2420,7 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2450,7 +2450,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2504,7 +2504,7 @@
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
         <v>1.03</v>
@@ -2534,77 +2534,77 @@
         <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.13</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H9" t="n">
         <v>22</v>
@@ -2650,16 +2650,16 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.11</v>
@@ -2674,25 +2674,25 @@
         <v>2.04</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>390</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>320</v>
@@ -2707,19 +2707,19 @@
         <v>32</v>
       </c>
       <c r="AD9" t="n">
-        <v>390</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>490</v>
       </c>
       <c r="AF9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>300</v>
@@ -2728,31 +2728,31 @@
         <v>9.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AM9" t="n">
         <v>260</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>11</v>
@@ -2761,10 +2761,10 @@
         <v>21</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7.4</v>
@@ -2773,92 +2773,92 @@
         <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC9" t="n">
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.32</v>
+        <v>11.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.16</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.32</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.32</v>
+        <v>11</v>
       </c>
       <c r="BZ9" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -2898,13 +2898,13 @@
         <v>1.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J10" t="n">
         <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
         <v>42</v>
@@ -2970,10 +2970,10 @@
         <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>990</v>
+        <v>44</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="I11" t="n">
-        <v>990</v>
+        <v>44</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3203,43 +3203,43 @@
         <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB11" t="n">
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -3251,122 +3251,122 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF11" t="n">
         <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
         <v>4.4</v>
@@ -3412,7 +3412,7 @@
         <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.49</v>
@@ -3421,7 +3421,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.44</v>
@@ -3436,19 +3436,19 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
         <v>1.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
@@ -3457,7 +3457,7 @@
         <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
@@ -3475,7 +3475,7 @@
         <v>140</v>
       </c>
       <c r="AF12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3493,13 +3493,13 @@
         <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AO12" t="n">
         <v>500</v>
@@ -3541,7 +3541,7 @@
         <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC12" t="n">
         <v>17.5</v>
@@ -3562,40 +3562,40 @@
         <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN12" t="n">
         <v>4.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP12" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
         <v>5.7</v>
@@ -3604,23 +3604,23 @@
         <v>40</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
         <v>38</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
         <v>5.4</v>
@@ -3702,13 +3702,13 @@
         <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="X13" t="n">
         <v>75</v>
       </c>
       <c r="Y13" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
         <v>95</v>
@@ -3723,16 +3723,16 @@
         <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AE13" t="n">
         <v>130</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
         <v>27</v>
@@ -3747,7 +3747,7 @@
         <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>120</v>
@@ -3759,31 +3759,31 @@
         <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3792,19 +3792,19 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
         <v>10</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
         <v>4.1</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>4.3</v>
@@ -3840,13 +3840,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
         <v>13</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
         <v>1.91</v>
       </c>
       <c r="T14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U14" t="n">
         <v>2.78</v>
@@ -3971,7 +3971,7 @@
         <v>100</v>
       </c>
       <c r="AB14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AC14" t="n">
         <v>15</v>
@@ -3983,7 +3983,7 @@
         <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
@@ -4019,22 +4019,22 @@
         <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
         <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX14" t="n">
         <v>12</v>
@@ -4058,7 +4058,7 @@
         <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
         <v>4.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H15" t="n">
         <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>4.4</v>
@@ -4204,19 +4204,19 @@
         <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>500</v>
@@ -4267,7 +4267,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ15" t="n">
         <v>13</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -4324,65 +4324,65 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -4578,65 +4578,65 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H17" t="n">
         <v>2.62</v>
@@ -4718,13 +4718,13 @@
         <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>240</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>230</v>
@@ -4733,13 +4733,13 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AD17" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
         <v>190</v>
@@ -4751,7 +4751,7 @@
         <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>210</v>
@@ -4832,65 +4832,65 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>7.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.11</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" t="n">
         <v>1.11</v>
@@ -5217,10 +5217,10 @@
         <v>1.86</v>
       </c>
       <c r="T19" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.45</v>
@@ -5340,65 +5340,65 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G20" t="n">
         <v>3.45</v>
@@ -5441,10 +5441,10 @@
         <v>2.46</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,7 +5453,7 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.14</v>
@@ -5465,16 +5465,16 @@
         <v>1.43</v>
       </c>
       <c r="R20" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S20" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
         <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V20" t="n">
         <v>1.69</v>
@@ -5486,7 +5486,7 @@
         <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Z20" t="n">
         <v>24</v>
@@ -5495,7 +5495,7 @@
         <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -5513,7 +5513,7 @@
         <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -5522,7 +5522,7 @@
         <v>500</v>
       </c>
       <c r="AK20" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
         <v>500</v>
@@ -5537,16 +5537,16 @@
         <v>55</v>
       </c>
       <c r="AP20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR20" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>6</v>
-      </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT20" t="n">
         <v>17</v>
@@ -5555,37 +5555,37 @@
         <v>8.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY20" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC20" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC20" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
         <v>7.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG20" t="n">
         <v>8</v>
@@ -5594,65 +5594,65 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
         <v>500</v>
@@ -5749,25 +5749,25 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="AC21" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>350</v>
       </c>
       <c r="AG21" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AH21" t="n">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
         <v>500</v>
@@ -5791,122 +5791,122 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.49</v>
+        <v>6.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="BF21" t="n">
         <v>5.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -5994,10 +5994,10 @@
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -6009,34 +6009,34 @@
         <v>95</v>
       </c>
       <c r="AD22" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>1000</v>
@@ -6051,10 +6051,10 @@
         <v>1.68</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AT22" t="n">
         <v>4.2</v>
@@ -6063,7 +6063,7 @@
         <v>4.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AW22" t="n">
         <v>1.82</v>
@@ -6075,22 +6075,22 @@
         <v>1.68</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BF22" t="n">
         <v>4.9</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -6356,65 +6356,65 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -6457,10 +6457,10 @@
         <v>36</v>
       </c>
       <c r="J24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
         <v>1.13</v>
@@ -6475,7 +6475,7 @@
         <v>1.07</v>
       </c>
       <c r="P24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q24" t="n">
         <v>1.22</v>
@@ -6487,7 +6487,7 @@
         <v>1.54</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
         <v>1.86</v>
@@ -6496,7 +6496,7 @@
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6547,34 +6547,34 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>15.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>9.800000000000001</v>
@@ -6583,10 +6583,10 @@
         <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB24" t="n">
         <v>8</v>
@@ -6595,10 +6595,10 @@
         <v>11</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF24" t="n">
         <v>1.95</v>
@@ -6610,65 +6610,65 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G25" t="n">
         <v>1.88</v>
@@ -6774,7 +6774,7 @@
         <v>38</v>
       </c>
       <c r="AE25" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AF25" t="n">
         <v>14</v>
@@ -6786,7 +6786,7 @@
         <v>32</v>
       </c>
       <c r="AI25" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ25" t="n">
         <v>22</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -7061,55 +7061,55 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
         <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
         <v>1.55</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
         <v>3.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.199999999999999</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
         <v>1.08</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R28" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S28" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7515,19 +7515,19 @@
         <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>250</v>
+        <v>950</v>
       </c>
       <c r="Y28" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>240</v>
+        <v>950</v>
       </c>
       <c r="AC28" t="n">
         <v>95</v>
@@ -7539,152 +7539,152 @@
         <v>85</v>
       </c>
       <c r="AF28" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AG28" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AH28" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
         <v>160</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK28" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO28" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS28" t="n">
         <v>1.57</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AT28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AY28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BA28" t="n">
         <v>1.54</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.53</v>
       </c>
       <c r="BB28" t="n">
         <v>1.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF28" t="n">
         <v>1.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -7769,19 +7769,19 @@
         <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y29" t="n">
         <v>24</v>
       </c>
       <c r="Z29" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AA29" t="n">
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AC29" t="n">
         <v>19</v>
@@ -7847,7 +7847,7 @@
         <v>12.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY29" t="n">
         <v>6.2</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>2.28</v>
       </c>
       <c r="G30" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H30" t="n">
         <v>2.28</v>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="O30" t="n">
         <v>1.1</v>
@@ -8020,13 +8020,13 @@
         <v>1.42</v>
       </c>
       <c r="W30" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z30" t="n">
         <v>500</v>
@@ -8035,7 +8035,7 @@
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC30" t="n">
         <v>42</v>
@@ -8053,7 +8053,7 @@
         <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI30" t="n">
         <v>500</v>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -8232,10 +8232,10 @@
         <v>1.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K31" t="n">
         <v>6.4</v>
@@ -8247,7 +8247,7 @@
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
@@ -8259,25 +8259,25 @@
         <v>1.41</v>
       </c>
       <c r="R31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
         <v>2.04</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V31" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="W31" t="n">
         <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y31" t="n">
         <v>16</v>
@@ -8289,7 +8289,7 @@
         <v>25</v>
       </c>
       <c r="AB31" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AC31" t="n">
         <v>16</v>
@@ -8304,10 +8304,10 @@
         <v>85</v>
       </c>
       <c r="AG31" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AH31" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
@@ -8331,10 +8331,10 @@
         <v>4.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -8355,10 +8355,10 @@
         <v>10.5</v>
       </c>
       <c r="AX31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY31" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>6.2</v>
       </c>
       <c r="AZ31" t="n">
         <v>16.5</v>
@@ -8367,13 +8367,13 @@
         <v>20</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC31" t="n">
         <v>6.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
         <v>6.6</v>
@@ -8388,65 +8388,65 @@
         <v>5.4</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="BT31" t="n">
         <v>4.6</v>
       </c>
       <c r="BU31" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA31" t="n">
         <v>4.9</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>2.26</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
         <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.41</v>
@@ -8507,7 +8507,7 @@
         <v>1.32</v>
       </c>
       <c r="P32" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q32" t="n">
         <v>1.96</v>
@@ -8525,7 +8525,7 @@
         <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
         <v>1.79</v>
@@ -8546,7 +8546,7 @@
         <v>9.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
         <v>17.5</v>
@@ -8579,7 +8579,7 @@
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -8594,13 +8594,13 @@
         <v>21</v>
       </c>
       <c r="AS32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT32" t="n">
         <v>7</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
         <v>12.5</v>
@@ -8618,7 +8618,7 @@
         <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
@@ -8627,10 +8627,10 @@
         <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF32" t="n">
         <v>13.5</v>
@@ -8654,7 +8654,7 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN32" t="n">
         <v>5.2</v>
@@ -8672,7 +8672,7 @@
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT32" t="n">
         <v>7.4</v>
@@ -8696,11 +8696,11 @@
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G33" t="n">
         <v>1.58</v>
       </c>
       <c r="H33" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I33" t="n">
         <v>8</v>
@@ -8746,7 +8746,7 @@
         <v>4.2</v>
       </c>
       <c r="K33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -8758,49 +8758,49 @@
         <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T33" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.97</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V33" t="n">
         <v>1.14</v>
       </c>
       <c r="W33" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z33" t="n">
         <v>65</v>
       </c>
       <c r="AA33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="n">
         <v>27</v>
@@ -8809,31 +8809,31 @@
         <v>130</v>
       </c>
       <c r="AF33" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN33" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>390</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AO33" t="n">
         <v>170</v>
@@ -8842,13 +8842,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="n">
         <v>48</v>
       </c>
       <c r="AS33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT33" t="n">
         <v>7</v>
@@ -8863,16 +8863,16 @@
         <v>29</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY33" t="n">
         <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB33" t="n">
         <v>12.5</v>
@@ -8884,13 +8884,13 @@
         <v>32</v>
       </c>
       <c r="BE33" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH33" t="n">
         <v>3.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
         <v>2.52</v>
       </c>
       <c r="S34" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9150,65 +9150,65 @@
         <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN34" t="n">
         <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT34" t="n">
         <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.14</v>
       </c>
       <c r="G35" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H35" t="n">
         <v>5</v>
@@ -9290,7 +9290,7 @@
         <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9404,65 +9404,65 @@
         <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN35" t="n">
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35" t="n">
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>5.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I36" t="n">
         <v>1.63</v>
@@ -9514,16 +9514,16 @@
         <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N36" t="n">
         <v>6.8</v>
       </c>
       <c r="O36" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
         <v>1.47</v>
@@ -9535,7 +9535,7 @@
         <v>2.18</v>
       </c>
       <c r="T36" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U36" t="n">
         <v>2.6</v>
@@ -9568,7 +9568,7 @@
         <v>10</v>
       </c>
       <c r="AE36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF36" t="n">
         <v>55</v>
@@ -9589,10 +9589,10 @@
         <v>120</v>
       </c>
       <c r="AL36" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM36" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
         <v>90</v>
@@ -9601,7 +9601,7 @@
         <v>5.6</v>
       </c>
       <c r="AP36" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AQ36" t="n">
         <v>13.5</v>
@@ -9613,7 +9613,7 @@
         <v>16</v>
       </c>
       <c r="AT36" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AU36" t="n">
         <v>11.5</v>
@@ -9628,7 +9628,7 @@
         <v>44</v>
       </c>
       <c r="AY36" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ36" t="n">
         <v>16</v>
@@ -9652,52 +9652,52 @@
         <v>30</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH36" t="n">
         <v>4.9</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BJ36" t="n">
         <v>9</v>
       </c>
       <c r="BK36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN36" t="n">
         <v>9</v>
       </c>
       <c r="BO36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP36" t="n">
         <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BR36" t="n">
         <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT36" t="n">
         <v>4.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW36" t="n">
         <v>6.6</v>
@@ -9706,17 +9706,17 @@
         <v>18.5</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA36" t="n">
         <v>7.2</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
         <v>4.2</v>
       </c>
       <c r="G37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H37" t="n">
         <v>1.95</v>
@@ -9759,7 +9759,7 @@
         <v>1.99</v>
       </c>
       <c r="J37" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K37" t="n">
         <v>3.9</v>
@@ -9777,16 +9777,16 @@
         <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
         <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
         <v>1.71</v>
@@ -9810,7 +9810,7 @@
         <v>12.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB37" t="n">
         <v>18.5</v>
@@ -9831,13 +9831,13 @@
         <v>17</v>
       </c>
       <c r="AH37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI37" t="n">
         <v>32</v>
       </c>
       <c r="AJ37" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AK37" t="n">
         <v>48</v>
@@ -9849,7 +9849,7 @@
         <v>85</v>
       </c>
       <c r="AN37" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO37" t="n">
         <v>12</v>
@@ -9870,10 +9870,10 @@
         <v>16.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV37" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW37" t="n">
         <v>17</v>
@@ -9918,13 +9918,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL37" t="n">
         <v>120</v>
       </c>
       <c r="BM37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37" t="n">
         <v>8</v>
@@ -9933,13 +9933,13 @@
         <v>5.7</v>
       </c>
       <c r="BP37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ37" t="n">
         <v>8</v>
       </c>
       <c r="BR37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS37" t="n">
         <v>8.4</v>
@@ -9954,13 +9954,13 @@
         <v>14</v>
       </c>
       <c r="BW37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX37" t="n">
         <v>27</v>
       </c>
       <c r="BY37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G38" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H38" t="n">
         <v>4.8</v>
@@ -10013,7 +10013,7 @@
         <v>5.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K38" t="n">
         <v>4.8</v>
@@ -10025,37 +10025,37 @@
         <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.16</v>
       </c>
       <c r="P38" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U38" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y38" t="n">
         <v>32</v>
@@ -10064,7 +10064,7 @@
         <v>46</v>
       </c>
       <c r="AA38" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB38" t="n">
         <v>14.5</v>
@@ -10073,13 +10073,13 @@
         <v>11</v>
       </c>
       <c r="AD38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE38" t="n">
         <v>60</v>
       </c>
       <c r="AF38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG38" t="n">
         <v>11</v>
@@ -10091,7 +10091,7 @@
         <v>55</v>
       </c>
       <c r="AJ38" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK38" t="n">
         <v>15.5</v>
@@ -10100,16 +10100,16 @@
         <v>24</v>
       </c>
       <c r="AM38" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN38" t="n">
         <v>6.4</v>
       </c>
       <c r="AO38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP38" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AQ38" t="n">
         <v>25</v>
@@ -10118,10 +10118,10 @@
         <v>40</v>
       </c>
       <c r="AS38" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AT38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU38" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
         <v>14</v>
       </c>
       <c r="BA38" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BB38" t="n">
         <v>17.5</v>
@@ -10160,25 +10160,25 @@
         <v>5.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BH38" t="n">
         <v>4.9</v>
       </c>
       <c r="BI38" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ38" t="n">
         <v>9</v>
       </c>
       <c r="BK38" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL38" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM38" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN38" t="n">
         <v>5</v>
@@ -10187,44 +10187,44 @@
         <v>3.95</v>
       </c>
       <c r="BP38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR38" t="n">
         <v>19</v>
       </c>
       <c r="BS38" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU38" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV38" t="n">
         <v>32</v>
       </c>
       <c r="BW38" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX38" t="n">
         <v>34</v>
       </c>
       <c r="BY38" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ38" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G39" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H39" t="n">
         <v>4.4</v>
@@ -10270,7 +10270,7 @@
         <v>4.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L39" t="n">
         <v>1.29</v>
@@ -10288,7 +10288,7 @@
         <v>2.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R39" t="n">
         <v>1.48</v>
@@ -10300,7 +10300,7 @@
         <v>1.73</v>
       </c>
       <c r="U39" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
@@ -10360,13 +10360,13 @@
         <v>9.6</v>
       </c>
       <c r="AO39" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AR39" t="n">
         <v>22</v>
@@ -10375,7 +10375,7 @@
         <v>38</v>
       </c>
       <c r="AT39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU39" t="n">
         <v>8.6</v>
@@ -10408,7 +10408,7 @@
         <v>20</v>
       </c>
       <c r="BE39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF39" t="n">
         <v>8.6</v>
@@ -10426,16 +10426,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK39" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO39" t="n">
         <v>3.8</v>
@@ -10444,41 +10444,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR39" t="n">
         <v>25</v>
       </c>
       <c r="BS39" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT39" t="n">
         <v>8.4</v>
       </c>
       <c r="BU39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV39" t="n">
         <v>36</v>
       </c>
       <c r="BW39" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX39" t="n">
         <v>42</v>
       </c>
       <c r="BY39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ39" t="n">
         <v>18.5</v>
       </c>
       <c r="CA39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -10509,19 +10509,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G40" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H40" t="n">
         <v>3.4</v>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J40" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K40" t="n">
         <v>4.1</v>
@@ -10539,16 +10539,16 @@
         <v>1.23</v>
       </c>
       <c r="P40" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R40" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S40" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T40" t="n">
         <v>1.61</v>
@@ -10557,10 +10557,10 @@
         <v>2.5</v>
       </c>
       <c r="V40" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X40" t="n">
         <v>22</v>
@@ -10599,7 +10599,7 @@
         <v>42</v>
       </c>
       <c r="AJ40" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK40" t="n">
         <v>26</v>
@@ -10611,19 +10611,19 @@
         <v>200</v>
       </c>
       <c r="AN40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO40" t="n">
         <v>28</v>
       </c>
       <c r="AP40" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AS40" t="n">
         <v>30</v>
@@ -10653,7 +10653,7 @@
         <v>32</v>
       </c>
       <c r="BB40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC40" t="n">
         <v>18</v>
@@ -10665,10 +10665,10 @@
         <v>32</v>
       </c>
       <c r="BF40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG40" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH40" t="n">
         <v>4.2</v>
@@ -10710,7 +10710,7 @@
         <v>7.2</v>
       </c>
       <c r="BU40" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV40" t="n">
         <v>26</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G41" t="n">
         <v>3.25</v>
       </c>
       <c r="H41" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I41" t="n">
         <v>2.52</v>
@@ -10778,7 +10778,7 @@
         <v>3.55</v>
       </c>
       <c r="K41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L41" t="n">
         <v>1.42</v>
@@ -10787,7 +10787,7 @@
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
@@ -10808,16 +10808,16 @@
         <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V41" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W41" t="n">
         <v>1.42</v>
       </c>
       <c r="X41" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y41" t="n">
         <v>10.5</v>
@@ -10826,37 +10826,37 @@
         <v>18.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE41" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AF41" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG41" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH41" t="n">
         <v>21</v>
       </c>
       <c r="AI41" t="n">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="AJ41" t="n">
         <v>900</v>
       </c>
       <c r="AK41" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL41" t="n">
         <v>55</v>
@@ -10868,22 +10868,22 @@
         <v>50</v>
       </c>
       <c r="AO41" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP41" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="AT41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU41" t="n">
         <v>7.2</v>
@@ -10895,31 +10895,31 @@
         <v>21</v>
       </c>
       <c r="AX41" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY41" t="n">
         <v>12</v>
       </c>
       <c r="AZ41" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BF41" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BG41" t="n">
         <v>19.5</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
         <v>1.65</v>
       </c>
       <c r="G42" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H42" t="n">
         <v>5.3</v>
@@ -11029,25 +11029,25 @@
         <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K42" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M42" t="n">
         <v>1.03</v>
       </c>
       <c r="N42" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O42" t="n">
         <v>1.19</v>
       </c>
       <c r="P42" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q42" t="n">
         <v>1.55</v>
@@ -11056,10 +11056,10 @@
         <v>1.66</v>
       </c>
       <c r="S42" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U42" t="n">
         <v>2.44</v>
@@ -11071,7 +11071,7 @@
         <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Y42" t="n">
         <v>34</v>
@@ -11083,7 +11083,7 @@
         <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC42" t="n">
         <v>12</v>
@@ -11104,7 +11104,7 @@
         <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AJ42" t="n">
         <v>19.5</v>
@@ -11119,28 +11119,28 @@
         <v>85</v>
       </c>
       <c r="AN42" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO42" t="n">
         <v>100</v>
       </c>
       <c r="AP42" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>20</v>
       </c>
       <c r="AR42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU42" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV42" t="n">
         <v>17.5</v>
@@ -11149,22 +11149,22 @@
         <v>28</v>
       </c>
       <c r="AX42" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
         <v>15</v>
       </c>
       <c r="BA42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD42" t="n">
         <v>19.5</v>
@@ -11173,74 +11173,74 @@
         <v>32</v>
       </c>
       <c r="BF42" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH42" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI42" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN42" t="n">
         <v>4.7</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP42" t="n">
         <v>10</v>
       </c>
       <c r="BQ42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR42" t="n">
         <v>19.5</v>
       </c>
       <c r="BS42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT42" t="n">
         <v>9</v>
       </c>
-      <c r="BT42" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BU42" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV42" t="n">
         <v>36</v>
       </c>
       <c r="BW42" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX42" t="n">
         <v>38</v>
       </c>
       <c r="BY42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ42" t="n">
         <v>12.5</v>
       </c>
       <c r="CA42" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -11271,73 +11271,73 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.46</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
-        <v>990</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="J43" t="n">
-        <v>2.76</v>
+        <v>5.7</v>
       </c>
       <c r="K43" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
         <v>1.62</v>
       </c>
       <c r="R43" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S43" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T43" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V43" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X43" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Y43" t="n">
         <v>970</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA43" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB43" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AC43" t="n">
         <v>970</v>
@@ -11352,10 +11352,10 @@
         <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="AH43" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AI43" t="n">
         <v>160</v>
@@ -11376,125 +11376,125 @@
         <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.35</v>
+        <v>5.8</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.32</v>
+        <v>4.1</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.32</v>
+        <v>3.25</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.33</v>
+        <v>2.74</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.32</v>
+        <v>3.65</v>
       </c>
       <c r="BH43" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ43" t="n">
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BN43" t="n">
         <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BT43" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G44" t="n">
         <v>2.6</v>
@@ -11537,7 +11537,7 @@
         <v>4.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K44" t="n">
         <v>3.5</v>
@@ -11603,10 +11603,10 @@
         <v>240</v>
       </c>
       <c r="AF44" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AG44" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AH44" t="n">
         <v>55</v>
@@ -11642,7 +11642,7 @@
         <v>10.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT44" t="n">
         <v>6.2</v>
@@ -11666,7 +11666,7 @@
         <v>11.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB44" t="n">
         <v>4.8</v>
@@ -11675,22 +11675,22 @@
         <v>14.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF44" t="n">
         <v>5.9</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH44" t="n">
         <v>2.98</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="BJ44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -11887,122 +11887,122 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
         <v>1.01</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN45" t="n">
         <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT45" t="n">
         <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ45" t="n">
         <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -12036,13 +12036,13 @@
         <v>1.01</v>
       </c>
       <c r="G46" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H46" t="n">
         <v>1.01</v>
       </c>
       <c r="I46" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J46" t="n">
         <v>1.09</v>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.2</v>
@@ -12075,10 +12075,10 @@
         <v>1.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V46" t="n">
         <v>1.02</v>
@@ -12192,71 +12192,71 @@
         <v>1.1</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
       </c>
       <c r="BI46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN46" t="n">
         <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G47" t="n">
         <v>2.02</v>
@@ -12296,52 +12296,52 @@
         <v>4.6</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M47" t="n">
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P47" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R47" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S47" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T47" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U47" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V47" t="n">
         <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y47" t="n">
         <v>14.5</v>
@@ -12362,7 +12362,7 @@
         <v>21</v>
       </c>
       <c r="AE47" t="n">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="AF47" t="n">
         <v>11</v>
@@ -12371,7 +12371,7 @@
         <v>10.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI47" t="n">
         <v>100</v>
@@ -12386,25 +12386,25 @@
         <v>55</v>
       </c>
       <c r="AM47" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO47" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP47" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR47" t="n">
         <v>14.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT47" t="n">
         <v>6.6</v>
@@ -12437,37 +12437,37 @@
         <v>22</v>
       </c>
       <c r="BD47" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE47" t="n">
         <v>11</v>
       </c>
       <c r="BF47" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG47" t="n">
         <v>18</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ47" t="n">
         <v>11</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>3.5</v>
+        <v>16</v>
       </c>
       <c r="BN47" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO47" t="n">
         <v>3.65</v>
@@ -12482,7 +12482,7 @@
         <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT47" t="n">
         <v>7.8</v>
@@ -12494,23 +12494,23 @@
         <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H48" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I48" t="n">
         <v>3.9</v>
@@ -12556,7 +12556,7 @@
         <v>2.4</v>
       </c>
       <c r="K48" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="L48" t="n">
         <v>1.52</v>
@@ -12589,7 +12589,7 @@
         <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W48" t="n">
         <v>1.52</v>
@@ -12625,7 +12625,7 @@
         <v>970</v>
       </c>
       <c r="AH48" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI48" t="n">
         <v>540</v>
@@ -12655,28 +12655,28 @@
         <v>4.9</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AT48" t="n">
         <v>4.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AV48" t="n">
         <v>1.6</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="AZ48" t="n">
         <v>1.62</v>
@@ -12685,7 +12685,7 @@
         <v>1.65</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BC48" t="n">
         <v>1.64</v>
@@ -12694,77 +12694,77 @@
         <v>1.65</v>
       </c>
       <c r="BE48" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="BF48" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN48" t="n">
         <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT48" t="n">
         <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BV48" t="n">
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -12795,22 +12795,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="G49" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="H49" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>3.45</v>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="L49" t="n">
         <v>1.29</v>
@@ -12819,16 +12819,16 @@
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O49" t="n">
         <v>1.25</v>
       </c>
       <c r="P49" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R49" t="n">
         <v>1.45</v>
@@ -12840,13 +12840,13 @@
         <v>1.69</v>
       </c>
       <c r="U49" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V49" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="W49" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -12861,10 +12861,10 @@
         <v>900</v>
       </c>
       <c r="AB49" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC49" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD49" t="n">
         <v>970</v>
@@ -12876,10 +12876,10 @@
         <v>500</v>
       </c>
       <c r="AG49" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH49" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI49" t="n">
         <v>500</v>
@@ -12900,125 +12900,125 @@
         <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU49" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV49" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="AX49" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="AY49" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="BB49" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="BD49" t="n">
-        <v>2.58</v>
+        <v>1.76</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="BF49" t="n">
-        <v>3.35</v>
+        <v>1.78</v>
       </c>
       <c r="BG49" t="n">
-        <v>7.2</v>
+        <v>1.97</v>
       </c>
       <c r="BH49" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BI49" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ49" t="n">
         <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BN49" t="n">
         <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BT49" t="n">
         <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ49" t="n">
         <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -13049,16 +13049,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G50" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H50" t="n">
         <v>1.01</v>
       </c>
       <c r="I50" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J50" t="n">
         <v>1.03</v>
@@ -13073,13 +13073,13 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="O50" t="n">
         <v>1.13</v>
       </c>
       <c r="P50" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Q50" t="n">
         <v>1.13</v>
@@ -13091,10 +13091,10 @@
         <v>1.13</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V50" t="n">
         <v>1.02</v>
@@ -13214,55 +13214,55 @@
         <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ50" t="n">
         <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN50" t="n">
         <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP50" t="n">
         <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT50" t="n">
         <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV50" t="n">
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -13312,10 +13312,10 @@
         <v>1.12</v>
       </c>
       <c r="I51" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
         <v>100</v>
@@ -13327,31 +13327,31 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O51" t="n">
         <v>1.16</v>
       </c>
       <c r="P51" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q51" t="n">
         <v>1.35</v>
       </c>
       <c r="R51" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="S51" t="n">
         <v>2.26</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U51" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
@@ -13369,7 +13369,7 @@
         <v>970</v>
       </c>
       <c r="AB51" t="n">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="AC51" t="n">
         <v>1000</v>
@@ -13384,10 +13384,10 @@
         <v>540</v>
       </c>
       <c r="AG51" t="n">
-        <v>250</v>
+        <v>950</v>
       </c>
       <c r="AH51" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="AI51" t="n">
         <v>250</v>
@@ -13438,13 +13438,13 @@
         <v>1.7</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AZ51" t="n">
         <v>1.69</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BB51" t="n">
         <v>1.71</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G52" t="n">
         <v>2.66</v>
@@ -13572,7 +13572,7 @@
         <v>3.5</v>
       </c>
       <c r="K52" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L52" t="n">
         <v>1.13</v>
@@ -13590,7 +13590,7 @@
         <v>1.93</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="R52" t="n">
         <v>1.35</v>
@@ -13686,7 +13686,7 @@
         <v>11</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX52" t="n">
         <v>13.5</v>
@@ -13698,7 +13698,7 @@
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB52" t="n">
         <v>16</v>
@@ -13707,7 +13707,7 @@
         <v>13</v>
       </c>
       <c r="BD52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE52" t="n">
         <v>8.800000000000001</v>
@@ -13716,71 +13716,71 @@
         <v>15.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ52" t="n">
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -13820,16 +13820,16 @@
         <v>4.2</v>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K53" t="n">
         <v>3.95</v>
       </c>
       <c r="L53" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M53" t="n">
         <v>1.06</v>
@@ -13841,25 +13841,25 @@
         <v>1.28</v>
       </c>
       <c r="P53" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T53" t="n">
         <v>1.76</v>
       </c>
       <c r="U53" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V53" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W53" t="n">
         <v>2.02</v>
@@ -13874,10 +13874,10 @@
         <v>32</v>
       </c>
       <c r="AA53" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB53" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC53" t="n">
         <v>8.6</v>
@@ -13889,7 +13889,7 @@
         <v>50</v>
       </c>
       <c r="AF53" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG53" t="n">
         <v>11</v>
@@ -13904,10 +13904,10 @@
         <v>65</v>
       </c>
       <c r="AK53" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL53" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AM53" t="n">
         <v>100</v>
@@ -13922,16 +13922,16 @@
         <v>14</v>
       </c>
       <c r="AQ53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR53" t="n">
         <v>28</v>
       </c>
       <c r="AS53" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT53" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU53" t="n">
         <v>8</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G54" t="n">
         <v>1.97</v>
@@ -14230,7 +14230,7 @@
         <v>3.7</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="BJ54" t="n">
         <v>10</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
         <v>1.89</v>
       </c>
       <c r="U55" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V55" t="n">
         <v>2.26</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G56" t="n">
         <v>2.5</v>
@@ -14738,7 +14738,7 @@
         <v>3.7</v>
       </c>
       <c r="BI56" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ56" t="n">
         <v>9.6</v>
@@ -14762,7 +14762,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ56" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BR56" t="n">
         <v>32</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -14827,13 +14827,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G57" t="n">
         <v>2.3</v>
       </c>
       <c r="H57" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I57" t="n">
         <v>4.1</v>
@@ -14857,7 +14857,7 @@
         <v>1.39</v>
       </c>
       <c r="P57" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q57" t="n">
         <v>2.16</v>
@@ -14869,25 +14869,25 @@
         <v>4.1</v>
       </c>
       <c r="T57" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U57" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V57" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W57" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X57" t="n">
         <v>14</v>
       </c>
       <c r="Y57" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z57" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA57" t="n">
         <v>100</v>
@@ -14896,19 +14896,19 @@
         <v>8.6</v>
       </c>
       <c r="AC57" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD57" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE57" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF57" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH57" t="n">
         <v>19.5</v>
@@ -14917,10 +14917,10 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL57" t="n">
         <v>55</v>
@@ -14944,7 +14944,7 @@
         <v>19.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="AT57" t="n">
         <v>6.4</v>
@@ -14956,7 +14956,7 @@
         <v>11.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX57" t="n">
         <v>9.800000000000001</v>
@@ -14968,7 +14968,7 @@
         <v>14</v>
       </c>
       <c r="BA57" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB57" t="n">
         <v>21</v>
@@ -14977,22 +14977,22 @@
         <v>19</v>
       </c>
       <c r="BD57" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BE57" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF57" t="n">
         <v>19</v>
       </c>
       <c r="BG57" t="n">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="BH57" t="n">
         <v>3.8</v>
       </c>
       <c r="BI57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         <v>1.86</v>
       </c>
       <c r="H58" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I58" t="n">
         <v>5.1</v>
@@ -15096,7 +15096,7 @@
         <v>3.8</v>
       </c>
       <c r="K58" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L58" t="n">
         <v>1.3</v>
@@ -15129,7 +15129,7 @@
         <v>2.14</v>
       </c>
       <c r="V58" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W58" t="n">
         <v>2.16</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G59" t="n">
         <v>1.96</v>
@@ -15347,7 +15347,7 @@
         <v>5.2</v>
       </c>
       <c r="J59" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K59" t="n">
         <v>4.2</v>
@@ -15500,7 +15500,7 @@
         <v>3.6</v>
       </c>
       <c r="BI59" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="BJ59" t="n">
         <v>10.5</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -15628,13 +15628,13 @@
         <v>1.52</v>
       </c>
       <c r="S60" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T60" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V60" t="n">
         <v>1.08</v>
@@ -15733,7 +15733,7 @@
         <v>8</v>
       </c>
       <c r="BB60" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC60" t="n">
         <v>12.5</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
         <v>2.4</v>
       </c>
       <c r="H61" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I61" t="n">
         <v>3.85</v>
@@ -16008,7 +16008,7 @@
         <v>3.3</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ61" t="n">
         <v>10.5</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G62" t="n">
         <v>2.4</v>
       </c>
       <c r="H62" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I62" t="n">
         <v>3.6</v>
@@ -16157,7 +16157,7 @@
         <v>970</v>
       </c>
       <c r="Z62" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA62" t="n">
         <v>900</v>
@@ -16172,7 +16172,7 @@
         <v>970</v>
       </c>
       <c r="AE62" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF62" t="n">
         <v>970</v>
@@ -16184,7 +16184,7 @@
         <v>15</v>
       </c>
       <c r="AI62" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ62" t="n">
         <v>900</v>
@@ -16193,7 +16193,7 @@
         <v>65</v>
       </c>
       <c r="AL62" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM62" t="n">
         <v>580</v>
@@ -16202,10 +16202,10 @@
         <v>38</v>
       </c>
       <c r="AO62" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AP62" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ62" t="n">
         <v>7.6</v>
@@ -16214,7 +16214,7 @@
         <v>11.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT62" t="n">
         <v>9.199999999999999</v>
@@ -16226,10 +16226,10 @@
         <v>11</v>
       </c>
       <c r="AW62" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX62" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AY62" t="n">
         <v>8.6</v>
@@ -16238,89 +16238,89 @@
         <v>9</v>
       </c>
       <c r="BA62" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB62" t="n">
         <v>14.5</v>
       </c>
       <c r="BC62" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD62" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD62" t="n">
-        <v>7</v>
-      </c>
       <c r="BE62" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF62" t="n">
         <v>11.5</v>
       </c>
       <c r="BG62" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
       </c>
       <c r="BI62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ62" t="n">
         <v>1000</v>
       </c>
       <c r="BK62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL62" t="n">
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN62" t="n">
         <v>1000</v>
       </c>
       <c r="BO62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP62" t="n">
         <v>1000</v>
       </c>
       <c r="BQ62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR62" t="n">
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT62" t="n">
         <v>1000</v>
       </c>
       <c r="BU62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -16357,16 +16357,16 @@
         <v>1.88</v>
       </c>
       <c r="H63" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J63" t="n">
         <v>4.2</v>
       </c>
-      <c r="J63" t="n">
-        <v>4.3</v>
-      </c>
       <c r="K63" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -16384,25 +16384,25 @@
         <v>2.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R63" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S63" t="n">
         <v>2.08</v>
       </c>
       <c r="T63" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U63" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V63" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W63" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X63" t="n">
         <v>34</v>
@@ -16426,7 +16426,7 @@
         <v>18</v>
       </c>
       <c r="AE63" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF63" t="n">
         <v>17.5</v>
@@ -16456,19 +16456,19 @@
         <v>7.4</v>
       </c>
       <c r="AO63" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP63" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR63" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ63" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AS63" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT63" t="n">
         <v>6</v>
@@ -16480,101 +16480,101 @@
         <v>6.2</v>
       </c>
       <c r="AW63" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX63" t="n">
         <v>6.2</v>
       </c>
       <c r="AY63" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AZ63" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA63" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB63" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BC63" t="n">
         <v>6.2</v>
       </c>
       <c r="BD63" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BE63" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF63" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BG63" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ63" t="n">
         <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN63" t="n">
         <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP63" t="n">
         <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR63" t="n">
         <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT63" t="n">
         <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV63" t="n">
         <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ63" t="n">
         <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         <v>2.46</v>
       </c>
       <c r="H64" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I64" t="n">
         <v>3.55</v>
@@ -16620,7 +16620,7 @@
         <v>3.35</v>
       </c>
       <c r="K64" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L64" t="n">
         <v>1.38</v>
@@ -16647,7 +16647,7 @@
         <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U64" t="n">
         <v>2.02</v>
@@ -16656,7 +16656,7 @@
         <v>1.4</v>
       </c>
       <c r="W64" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X64" t="n">
         <v>12.5</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -16862,16 +16862,16 @@
         <v>2.9</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H65" t="n">
         <v>2.22</v>
       </c>
       <c r="I65" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J65" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="K65" t="n">
         <v>4.9</v>
@@ -16907,7 +16907,7 @@
         <v>1.11</v>
       </c>
       <c r="V65" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W65" t="n">
         <v>1.43</v>
@@ -16916,7 +16916,7 @@
         <v>1000</v>
       </c>
       <c r="Y65" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z65" t="n">
         <v>500</v>
@@ -16925,7 +16925,7 @@
         <v>900</v>
       </c>
       <c r="AB65" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC65" t="n">
         <v>42</v>
@@ -16940,10 +16940,10 @@
         <v>500</v>
       </c>
       <c r="AG65" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH65" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI65" t="n">
         <v>500</v>
@@ -17024,65 +17024,65 @@
         <v>1000</v>
       </c>
       <c r="BI65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ65" t="n">
         <v>1000</v>
       </c>
       <c r="BK65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN65" t="n">
         <v>1000</v>
       </c>
       <c r="BO65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP65" t="n">
         <v>1000</v>
       </c>
       <c r="BQ65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR65" t="n">
         <v>1000</v>
       </c>
       <c r="BS65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT65" t="n">
         <v>1000</v>
       </c>
       <c r="BU65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV65" t="n">
         <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX65" t="n">
         <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ65" t="n">
         <v>1000</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -17113,16 +17113,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G66" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H66" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I66" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J66" t="n">
         <v>4.2</v>
@@ -17137,22 +17137,22 @@
         <v>1.02</v>
       </c>
       <c r="N66" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O66" t="n">
         <v>1.09</v>
       </c>
       <c r="P66" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="R66" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S66" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="T66" t="n">
         <v>1.11</v>
@@ -17164,13 +17164,13 @@
         <v>1.51</v>
       </c>
       <c r="W66" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X66" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y66" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z66" t="n">
         <v>500</v>
@@ -17179,13 +17179,13 @@
         <v>900</v>
       </c>
       <c r="AB66" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC66" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD66" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE66" t="n">
         <v>500</v>
@@ -17194,10 +17194,10 @@
         <v>500</v>
       </c>
       <c r="AG66" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH66" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI66" t="n">
         <v>500</v>
@@ -17278,65 +17278,65 @@
         <v>1000</v>
       </c>
       <c r="BI66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ66" t="n">
         <v>1000</v>
       </c>
       <c r="BK66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL66" t="n">
         <v>1000</v>
       </c>
       <c r="BM66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN66" t="n">
         <v>1000</v>
       </c>
       <c r="BO66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP66" t="n">
         <v>1000</v>
       </c>
       <c r="BQ66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR66" t="n">
         <v>1000</v>
       </c>
       <c r="BS66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT66" t="n">
         <v>1000</v>
       </c>
       <c r="BU66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV66" t="n">
         <v>1000</v>
       </c>
       <c r="BW66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX66" t="n">
         <v>1000</v>
       </c>
       <c r="BY66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ66" t="n">
         <v>1000</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -17367,22 +17367,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="G67" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H67" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I67" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J67" t="n">
         <v>2.76</v>
       </c>
       <c r="K67" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -17415,10 +17415,10 @@
         <v>1.11</v>
       </c>
       <c r="V67" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W67" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="X67" t="n">
         <v>970</v>
@@ -17451,7 +17451,7 @@
         <v>970</v>
       </c>
       <c r="AH67" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI67" t="n">
         <v>500</v>
@@ -17517,7 +17517,7 @@
         <v>6.6</v>
       </c>
       <c r="BD67" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE67" t="n">
         <v>2.12</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -17621,16 +17621,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G68" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H68" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I68" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J68" t="n">
         <v>3.65</v>
@@ -17669,10 +17669,10 @@
         <v>1.75</v>
       </c>
       <c r="V68" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W68" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="X68" t="n">
         <v>19.5</v>
@@ -17702,7 +17702,7 @@
         <v>19.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AH68" t="n">
         <v>70</v>
@@ -17723,7 +17723,7 @@
         <v>700</v>
       </c>
       <c r="AN68" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO68" t="n">
         <v>700</v>
@@ -17735,10 +17735,10 @@
         <v>13.5</v>
       </c>
       <c r="AR68" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS68" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT68" t="n">
         <v>4.2</v>
@@ -17750,7 +17750,7 @@
         <v>14</v>
       </c>
       <c r="AW68" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX68" t="n">
         <v>7</v>
@@ -17759,10 +17759,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ68" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA68" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>6.2</v>
       </c>
       <c r="BB68" t="n">
         <v>8.4</v>
@@ -17771,16 +17771,16 @@
         <v>15.5</v>
       </c>
       <c r="BD68" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE68" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF68" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG68" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH68" t="n">
         <v>1000</v>
@@ -17804,7 +17804,7 @@
         <v>5.3</v>
       </c>
       <c r="BO68" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="BP68" t="n">
         <v>16</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -18129,10 +18129,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G70" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H70" t="n">
         <v>3.8</v>
@@ -18180,7 +18180,7 @@
         <v>1.32</v>
       </c>
       <c r="W70" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X70" t="n">
         <v>11.5</v>
@@ -18216,7 +18216,7 @@
         <v>25</v>
       </c>
       <c r="AI70" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AJ70" t="n">
         <v>34</v>
@@ -18228,7 +18228,7 @@
         <v>130</v>
       </c>
       <c r="AM70" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN70" t="n">
         <v>32</v>
@@ -18261,7 +18261,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX70" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY70" t="n">
         <v>8.6</v>
@@ -18312,7 +18312,7 @@
         <v>6.4</v>
       </c>
       <c r="BO70" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP70" t="n">
         <v>29</v>
@@ -18330,7 +18330,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU70" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -18548,55 +18548,55 @@
         <v>1000</v>
       </c>
       <c r="BI71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ71" t="n">
         <v>1000</v>
       </c>
       <c r="BK71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL71" t="n">
         <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN71" t="n">
         <v>1000</v>
       </c>
       <c r="BO71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP71" t="n">
         <v>1000</v>
       </c>
       <c r="BQ71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR71" t="n">
         <v>1000</v>
       </c>
       <c r="BS71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT71" t="n">
         <v>1000</v>
       </c>
       <c r="BU71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV71" t="n">
         <v>1000</v>
       </c>
       <c r="BW71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX71" t="n">
         <v>1000</v>
       </c>
       <c r="BY71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ71" t="n">
         <v>0</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -18640,16 +18640,16 @@
         <v>1.92</v>
       </c>
       <c r="G72" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J72" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K72" t="n">
         <v>3.55</v>
@@ -18670,7 +18670,7 @@
         <v>1.64</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R72" t="n">
         <v>1.23</v>
@@ -18688,7 +18688,7 @@
         <v>1.23</v>
       </c>
       <c r="W72" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X72" t="n">
         <v>12.5</v>
@@ -18745,7 +18745,7 @@
         <v>140</v>
       </c>
       <c r="AP72" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ72" t="n">
         <v>11.5</v>
@@ -18754,7 +18754,7 @@
         <v>4.6</v>
       </c>
       <c r="AS72" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT72" t="n">
         <v>6.2</v>
@@ -18766,7 +18766,7 @@
         <v>4.2</v>
       </c>
       <c r="AW72" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX72" t="n">
         <v>9.4</v>
@@ -18793,28 +18793,28 @@
         <v>5</v>
       </c>
       <c r="BF72" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG72" t="n">
         <v>4.9</v>
       </c>
       <c r="BH72" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI72" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ72" t="n">
         <v>11.5</v>
       </c>
       <c r="BK72" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL72" t="n">
         <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN72" t="n">
         <v>4.6</v>
@@ -18832,7 +18832,7 @@
         <v>1000</v>
       </c>
       <c r="BS72" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT72" t="n">
         <v>8.6</v>
@@ -18844,23 +18844,23 @@
         <v>1000</v>
       </c>
       <c r="BW72" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX72" t="n">
         <v>1000</v>
       </c>
       <c r="BY72" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ72" t="n">
         <v>1000</v>
       </c>
       <c r="CA72" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
         <v>3.55</v>
       </c>
       <c r="K73" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L73" t="n">
         <v>1.36</v>
@@ -18921,7 +18921,7 @@
         <v>1.34</v>
       </c>
       <c r="P73" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q73" t="n">
         <v>1.99</v>
@@ -18954,13 +18954,13 @@
         <v>29</v>
       </c>
       <c r="AA73" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB73" t="n">
         <v>12</v>
       </c>
       <c r="AC73" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD73" t="n">
         <v>17.5</v>
@@ -19092,7 +19092,7 @@
         <v>6.6</v>
       </c>
       <c r="BU73" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV73" t="n">
         <v>1000</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-28 21:50:56</t>
+          <t>2026-05-29 00:11:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>680</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>360</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y2" t="n">
         <v>6.6</v>
       </c>
-      <c r="G2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>1000</v>
       </c>
-      <c r="Y2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
         <v>18</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AG2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1000</v>
       </c>
-      <c r="AC2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>1000</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AX2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="AY2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>310</v>
+      </c>
+      <c r="BB2" t="n">
         <v>75</v>
       </c>
-      <c r="AO2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BC2" t="n">
-        <v>36</v>
+        <v>3.85</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>430</v>
       </c>
       <c r="BF2" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38</v>
+        <v>1.41</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="I3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.6</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="X3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>990</v>
+        <v>8.6</v>
       </c>
       <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>590</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>610</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>400</v>
+      </c>
+      <c r="BF3" t="n">
         <v>32</v>
       </c>
-      <c r="AI3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>95</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG3" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>940</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,752 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.96</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.52</v>
-      </c>
       <c r="I4" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="J4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.6</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK4" t="n">
         <v>24</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>270</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="BT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU4" t="n">
         <v>5.9</v>
       </c>
-      <c r="BU4" t="n">
-        <v>5</v>
-      </c>
       <c r="BV4" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="BX4" t="n">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>America MG</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>150</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>46</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>14</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-05-29 19:49:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chilean Primera Division</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Univ de Concepcion</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>130</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>11</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
